--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1785909</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>50.8400001525879</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>49.2000007629395</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>49.9000015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>49.2700004577637</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1708763</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>50.3899993896484</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>48.6049995422363</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>49.8899993896484</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1765905</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>50.5200004577637</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>49.3699989318848</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>50.439998626709</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>50.4199981689453</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>2164083</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>51.2799987792969</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>50.1699981689453</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>51</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>50.689998626709</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1378909</v>
+        <v>1225698</v>
       </c>
       <c r="C2715" t="n">
-        <v>50.7400016784668</v>
+        <v>51.2799987792969</v>
       </c>
       <c r="D2715" t="n">
-        <v>49.4749984741211</v>
+        <v>50.2000007629395</v>
       </c>
       <c r="E2715" t="n">
+        <v>50.3899993896484</v>
+      </c>
+      <c r="F2715" t="n">
         <v>50.2000007629395</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>50.6699981689453</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>2544367</v>
+        <v>1378909</v>
       </c>
       <c r="C2716" t="n">
-        <v>50.2000007629395</v>
+        <v>50.7400016784668</v>
       </c>
       <c r="D2716" t="n">
-        <v>48.6450004577637</v>
+        <v>49.4749984741211</v>
       </c>
       <c r="E2716" t="n">
         <v>50.2000007629395</v>
       </c>
       <c r="F2716" t="n">
-        <v>48.6450004577637</v>
+        <v>50.6699981689453</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>2448492</v>
+        <v>2544367</v>
       </c>
       <c r="C2717" t="n">
-        <v>50.3600006103516</v>
+        <v>50.2000007629395</v>
       </c>
       <c r="D2717" t="n">
-        <v>48.9000015258789</v>
+        <v>48.6450004577637</v>
       </c>
       <c r="E2717" t="n">
-        <v>48.9000015258789</v>
+        <v>50.2000007629395</v>
       </c>
       <c r="F2717" t="n">
-        <v>50.0299987792969</v>
+        <v>48.6450004577637</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>2227707</v>
+        <v>2448492</v>
       </c>
       <c r="C2718" t="n">
-        <v>50.5699996948242</v>
+        <v>50.3600006103516</v>
       </c>
       <c r="D2718" t="n">
-        <v>49.9099998474121</v>
+        <v>48.9000015258789</v>
       </c>
       <c r="E2718" t="n">
-        <v>50.1800003051758</v>
+        <v>48.9000015258789</v>
       </c>
       <c r="F2718" t="n">
-        <v>50</v>
+        <v>50.0299987792969</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1785909</v>
+        <v>2227707</v>
       </c>
       <c r="C2719" t="n">
-        <v>50.8400001525879</v>
+        <v>50.5699996948242</v>
       </c>
       <c r="D2719" t="n">
-        <v>49.2000007629395</v>
+        <v>49.9099998474121</v>
       </c>
       <c r="E2719" t="n">
-        <v>49.9000015258789</v>
+        <v>50.1800003051758</v>
       </c>
       <c r="F2719" t="n">
-        <v>49.2700004577637</v>
+        <v>50</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1708763</v>
+        <v>1785909</v>
       </c>
       <c r="C2720" t="n">
-        <v>50.3899993896484</v>
+        <v>50.8400001525879</v>
       </c>
       <c r="D2720" t="n">
-        <v>48.6049995422363</v>
+        <v>49.2000007629395</v>
       </c>
       <c r="E2720" t="n">
-        <v>49</v>
+        <v>49.9000015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>49.8899993896484</v>
+        <v>49.2700004577637</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1765905</v>
+        <v>1708763</v>
       </c>
       <c r="C2721" t="n">
-        <v>50.5200004577637</v>
+        <v>50.3899993896484</v>
       </c>
       <c r="D2721" t="n">
-        <v>49.3699989318848</v>
+        <v>48.6049995422363</v>
       </c>
       <c r="E2721" t="n">
-        <v>50.439998626709</v>
+        <v>49</v>
       </c>
       <c r="F2721" t="n">
-        <v>50.4199981689453</v>
+        <v>49.8899993896484</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>2164083</v>
+        <v>1765905</v>
       </c>
       <c r="C2722" t="n">
-        <v>51.2799987792969</v>
+        <v>50.5200004577637</v>
       </c>
       <c r="D2722" t="n">
-        <v>50.1699981689453</v>
+        <v>49.3699989318848</v>
       </c>
       <c r="E2722" t="n">
-        <v>51</v>
+        <v>50.439998626709</v>
       </c>
       <c r="F2722" t="n">
-        <v>50.689998626709</v>
+        <v>50.4199981689453</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>2845521</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>51.1300010681152</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>50.1199989318848</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>50.9900016784668</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>50.4500007629395</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -447,7 +447,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3644332885742</v>
+        <v>11.3644323348999</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G4" t="n">
-        <v>11.0993223190308</v>
+        <v>11.0993213653564</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0904846191406</v>
+        <v>11.0904865264893</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>11.0021142959595</v>
+        <v>11.0021162033081</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>11.1258335113525</v>
+        <v>11.1258316040039</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G9" t="n">
-        <v>11.214204788208</v>
+        <v>11.2142028808594</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1979455947876</v>
+        <v>10.197943687439</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G12" t="n">
-        <v>10.0123672485352</v>
+        <v>10.0123662948608</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G13" t="n">
-        <v>10.2332916259766</v>
+        <v>10.2332935333252</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G14" t="n">
-        <v>9.72958087921143</v>
+        <v>9.72957992553711</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>9.92399597167969</v>
+        <v>9.92399501800537</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G17" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G18" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G19" t="n">
-        <v>9.59702396392822</v>
+        <v>9.59702491760254</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G21" t="n">
-        <v>9.65888404846191</v>
+        <v>9.65888500213623</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>9.67655944824219</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>9.39377307891846</v>
+        <v>9.39377403259277</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G24" t="n">
-        <v>9.21703433990479</v>
+        <v>9.21703243255615</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G25" t="n">
-        <v>9.0491304397583</v>
+        <v>9.04912853240967</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>8.51448822021484</v>
+        <v>8.51448917388916</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>8.13449478149414</v>
+        <v>8.13449382781982</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.87380313873291</v>
+        <v>7.87380266189575</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G29" t="n">
-        <v>8.19635486602783</v>
+        <v>8.19635391235352</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62636470794678</v>
+        <v>7.62636375427246</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G33" t="n">
-        <v>8.12123966217041</v>
+        <v>8.12123870849609</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G34" t="n">
-        <v>8.22728443145752</v>
+        <v>8.22728538513184</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G35" t="n">
-        <v>8.33332824707031</v>
+        <v>8.33332920074463</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>9.49499988555908</v>
       </c>
       <c r="G38" t="n">
-        <v>8.39076900482178</v>
+        <v>8.39076995849609</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>8.10356521606445</v>
+        <v>8.10356616973877</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G42" t="n">
-        <v>8.42611598968506</v>
+        <v>8.42611789703369</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G43" t="n">
-        <v>9.00494289398193</v>
+        <v>9.00494194030762</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>8.83703899383545</v>
+        <v>8.83704090118408</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G45" t="n">
-        <v>8.85471343994141</v>
+        <v>8.85471439361572</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G46" t="n">
-        <v>8.80169296264648</v>
+        <v>8.80169200897217</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G47" t="n">
-        <v>8.68681049346924</v>
+        <v>8.68680953979492</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G48" t="n">
-        <v>8.86355018615723</v>
+        <v>8.86355113983154</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G49" t="n">
-        <v>8.91657447814941</v>
+        <v>8.91657257080078</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G50" t="n">
-        <v>8.71332168579102</v>
+        <v>8.7133207321167</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G51" t="n">
-        <v>9.31423854827881</v>
+        <v>9.31424045562744</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G52" t="n">
-        <v>9.58818817138672</v>
+        <v>9.58819007873535</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G53" t="n">
-        <v>9.49097919464111</v>
+        <v>9.49098014831543</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G55" t="n">
-        <v>9.52632713317871</v>
+        <v>9.52632999420166</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>9.87097263336182</v>
+        <v>9.87097549438477</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G57" t="n">
-        <v>9.85329914093018</v>
+        <v>9.85329818725586</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G58" t="n">
-        <v>9.9593448638916</v>
+        <v>9.95934391021729</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>9.92399597167969</v>
+        <v>9.92399501800537</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>9.88864707946777</v>
+        <v>9.88864898681641</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G63" t="n">
-        <v>9.85329914093018</v>
+        <v>9.85329818725586</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>10.038875579834</v>
+        <v>10.0388774871826</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G68" t="n">
-        <v>9.46446990966797</v>
+        <v>9.46447086334229</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G71" t="n">
-        <v>9.39377307891846</v>
+        <v>9.39377403259277</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G72" t="n">
-        <v>9.66772270202637</v>
+        <v>9.66772079467773</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G74" t="n">
-        <v>9.59702396392822</v>
+        <v>9.59702491760254</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>9.67655944824219</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>9.67655944824219</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>9.72074413299561</v>
+        <v>9.72074317932129</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.021203994751</v>
+        <v>10.0212030410767</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G85" t="n">
-        <v>9.71190738677979</v>
+        <v>9.71190643310547</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G86" t="n">
-        <v>9.62353610992432</v>
+        <v>9.62353706359863</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G90" t="n">
-        <v>9.06680297851562</v>
+        <v>9.06680202484131</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G91" t="n">
-        <v>9.17284679412842</v>
+        <v>9.17284870147705</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G92" t="n">
-        <v>9.51749229431152</v>
+        <v>9.51749420166016</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>9.45563125610352</v>
+        <v>9.45563316345215</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G98" t="n">
-        <v>9.31423854827881</v>
+        <v>9.31424045562744</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G99" t="n">
-        <v>9.46446990966797</v>
+        <v>9.46447086334229</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G101" t="n">
-        <v>9.58818817138672</v>
+        <v>9.58819007873535</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G102" t="n">
-        <v>9.70306968688965</v>
+        <v>9.70306873321533</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G103" t="n">
-        <v>9.70306968688965</v>
+        <v>9.70306873321533</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G104" t="n">
-        <v>9.65888404846191</v>
+        <v>9.65888500213623</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G106" t="n">
-        <v>9.40261077880859</v>
+        <v>9.40260982513428</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G107" t="n">
-        <v>9.22586822509766</v>
+        <v>9.22587013244629</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.27005386352539</v>
+        <v>9.27005481719971</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>8.96959400177002</v>
+        <v>8.96959590911865</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>8.77960109710693</v>
+        <v>8.77960014343262</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G111" t="n">
-        <v>8.93424606323242</v>
+        <v>8.93424701690674</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>8.88122653961182</v>
+        <v>8.88122463226318</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.59844017028809</v>
+        <v>8.5984411239624</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>9.25</v>
       </c>
       <c r="G114" t="n">
-        <v>8.17426300048828</v>
+        <v>8.17426204681396</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G117" t="n">
-        <v>8.29356288909912</v>
+        <v>8.29356098175049</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>8.2184476852417</v>
+        <v>8.21844673156738</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>8.4305362701416</v>
+        <v>8.43053531646729</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G120" t="n">
-        <v>8.82820224761963</v>
+        <v>8.82820320129395</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G123" t="n">
-        <v>8.99610614776611</v>
+        <v>8.99610710144043</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>7.40543985366821</v>
+        <v>7.40544033050537</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G126" t="n">
-        <v>7.92682552337646</v>
+        <v>7.92682361602783</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>7.93124294281006</v>
+        <v>7.9312424659729</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.98426580429077</v>
+        <v>7.98426532745361</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G132" t="n">
-        <v>7.59985446929932</v>
+        <v>7.599853515625</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>7.75450372695923</v>
+        <v>7.75450229644775</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G134" t="n">
-        <v>8.19193649291992</v>
+        <v>8.19193553924561</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G135" t="n">
-        <v>8.4305362701416</v>
+        <v>8.43053531646729</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.75</v>
       </c>
       <c r="G136" t="n">
-        <v>8.61611366271973</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>8.47030353546143</v>
+        <v>8.47030258178711</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G138" t="n">
-        <v>8.6426248550415</v>
+        <v>8.64262390136719</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>8.51006984710693</v>
+        <v>8.51007080078125</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G144" t="n">
-        <v>8.55425453186035</v>
+        <v>8.55425548553467</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>8.53658199310303</v>
+        <v>8.53658008575439</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G148" t="n">
-        <v>8.80610942840576</v>
+        <v>8.80611038208008</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>9.02261638641357</v>
+        <v>9.02261829376221</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G150" t="n">
-        <v>8.68681049346924</v>
+        <v>8.68680953979492</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.75</v>
       </c>
       <c r="G151" t="n">
-        <v>8.61611366271973</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>8.35100269317627</v>
+        <v>8.35100364685059</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G153" t="n">
-        <v>8.30681800842285</v>
+        <v>8.30681705474854</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G155" t="n">
-        <v>8.53658199310303</v>
+        <v>8.53658008575439</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>8.58076572418213</v>
+        <v>8.58076667785645</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G157" t="n">
-        <v>8.68239212036133</v>
+        <v>8.6823902130127</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G158" t="n">
-        <v>8.90773582458496</v>
+        <v>8.90773677825928</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G159" t="n">
-        <v>8.93424606323242</v>
+        <v>8.93424701690674</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>8.72215747833252</v>
+        <v>8.72215843200684</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.75</v>
       </c>
       <c r="G161" t="n">
-        <v>8.61611366271973</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G162" t="n">
-        <v>8.77960109710693</v>
+        <v>8.77960014343262</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>8.64704513549805</v>
+        <v>8.64704322814941</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G164" t="n">
-        <v>8.78401660919189</v>
+        <v>8.78401756286621</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>9.19052124023438</v>
+        <v>9.19052028656006</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>9.12866115570068</v>
+        <v>9.128662109375</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G172" t="n">
-        <v>9.0491304397583</v>
+        <v>9.04912853240967</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>9.11098957061768</v>
+        <v>9.11098861694336</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G174" t="n">
-        <v>9.12866115570068</v>
+        <v>9.128662109375</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G175" t="n">
-        <v>9.19052124023438</v>
+        <v>9.19052028656006</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>10.75</v>
       </c>
       <c r="G176" t="n">
-        <v>9.49981784820557</v>
+        <v>9.49981880187988</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G178" t="n">
-        <v>9.51749229431152</v>
+        <v>9.51749420166016</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G179" t="n">
-        <v>9.45563125610352</v>
+        <v>9.45563316345215</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G180" t="n">
-        <v>9.42912292480469</v>
+        <v>9.42912006378174</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G182" t="n">
-        <v>9.42912292480469</v>
+        <v>9.42912006378174</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G184" t="n">
-        <v>9.21703433990479</v>
+        <v>9.21703243255615</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>8.93424606323242</v>
+        <v>8.93424701690674</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G187" t="n">
-        <v>9.12866115570068</v>
+        <v>9.128662109375</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G189" t="n">
-        <v>8.91657447814941</v>
+        <v>8.91657257080078</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>8.8105297088623</v>
+        <v>8.81053066253662</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G191" t="n">
-        <v>8.93424606323242</v>
+        <v>8.93424701690674</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>8.91657447814941</v>
+        <v>8.91657257080078</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G194" t="n">
-        <v>8.8105297088623</v>
+        <v>8.81053066253662</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G195" t="n">
-        <v>8.73541355133057</v>
+        <v>8.73541450500488</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G196" t="n">
-        <v>8.84587860107422</v>
+        <v>8.8458776473999</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G197" t="n">
-        <v>8.77960109710693</v>
+        <v>8.77960014343262</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G198" t="n">
-        <v>8.75308895111084</v>
+        <v>8.75308799743652</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G199" t="n">
-        <v>8.85471343994141</v>
+        <v>8.85471439361572</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G200" t="n">
-        <v>8.90773582458496</v>
+        <v>8.90773677825928</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G201" t="n">
-        <v>8.91657447814941</v>
+        <v>8.91657257080078</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>8.80169296264648</v>
+        <v>8.80169200897217</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G203" t="n">
-        <v>9.09331512451172</v>
+        <v>9.0933141708374</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G204" t="n">
-        <v>9.3054027557373</v>
+        <v>9.30540180206299</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G207" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G209" t="n">
-        <v>9.9593448638916</v>
+        <v>9.95934391021729</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G210" t="n">
-        <v>9.70306968688965</v>
+        <v>9.70306873321533</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>11</v>
       </c>
       <c r="G211" t="n">
-        <v>9.72074413299561</v>
+        <v>9.72074317932129</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G216" t="n">
-        <v>9.65004730224609</v>
+        <v>9.65004825592041</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>9.23470687866211</v>
+        <v>9.23470592498779</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G219" t="n">
-        <v>9.40261077880859</v>
+        <v>9.40260982513428</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G220" t="n">
-        <v>9.51749229431152</v>
+        <v>9.51749420166016</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G221" t="n">
-        <v>10.2421283721924</v>
+        <v>10.2421293258667</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.9137439727783</v>
+        <v>10.9137449264526</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G226" t="n">
-        <v>10.9756050109863</v>
+        <v>10.9756031036377</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>12.1499996185303</v>
       </c>
       <c r="G227" t="n">
-        <v>10.737003326416</v>
+        <v>10.7370042800903</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4277086257935</v>
+        <v>10.4277057647705</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>10.5602626800537</v>
+        <v>10.560263633728</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5956125259399</v>
+        <v>10.595609664917</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G235" t="n">
-        <v>10.7635154724121</v>
+        <v>10.7635145187378</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>12.25</v>
       </c>
       <c r="G236" t="n">
-        <v>10.8253746032715</v>
+        <v>10.8253736495972</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G239" t="n">
-        <v>11.3379201889038</v>
+        <v>11.3379220962524</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G242" t="n">
-        <v>12.0979070663452</v>
+        <v>12.0979089736938</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G243" t="n">
-        <v>11.7532625198364</v>
+        <v>11.7532644271851</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>11.7179145812988</v>
+        <v>11.7179136276245</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G246" t="n">
-        <v>11.6825666427612</v>
+        <v>11.6825675964355</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>11.9034938812256</v>
+        <v>11.9034929275513</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>11.8416328430176</v>
+        <v>11.8416337966919</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>11.8416328430176</v>
+        <v>11.8416337966919</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G251" t="n">
-        <v>11.8769807815552</v>
+        <v>11.8769817352295</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>11.8062858581543</v>
+        <v>11.80628490448</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>11.9123296737671</v>
+        <v>11.9123287200928</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>11.9830255508423</v>
+        <v>11.9830265045166</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G255" t="n">
-        <v>11.8593072891235</v>
+        <v>11.8593082427979</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G256" t="n">
-        <v>11.7532625198364</v>
+        <v>11.7532644271851</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>11.8504705429077</v>
+        <v>11.8504695892334</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G259" t="n">
-        <v>11.8504705429077</v>
+        <v>11.8504695892334</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8504705429077</v>
+        <v>11.8504695892334</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G264" t="n">
-        <v>11.9123296737671</v>
+        <v>11.9123287200928</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G267" t="n">
-        <v>11.550009727478</v>
+        <v>11.5500106811523</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3555965423584</v>
+        <v>11.3555955886841</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4262943267822</v>
+        <v>11.4262933731079</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>11.532338142395</v>
+        <v>11.5323362350464</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13</v>
       </c>
       <c r="G272" t="n">
-        <v>11.4881525039673</v>
+        <v>11.488151550293</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G273" t="n">
-        <v>11.15234375</v>
+        <v>11.1523456573486</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G274" t="n">
-        <v>11.2849006652832</v>
+        <v>11.2848997116089</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>11.3555965423584</v>
+        <v>11.3555955886841</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0816478729248</v>
+        <v>11.0816488265991</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G277" t="n">
-        <v>11.0816478729248</v>
+        <v>11.0816488265991</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G278" t="n">
-        <v>10.7811889648438</v>
+        <v>10.7811870574951</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G279" t="n">
-        <v>10.5337514877319</v>
+        <v>10.5337524414062</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>12.3299999237061</v>
       </c>
       <c r="G280" t="n">
-        <v>10.896071434021</v>
+        <v>10.8960695266724</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>12.5</v>
       </c>
       <c r="G281" t="n">
-        <v>11.0462999343872</v>
+        <v>11.0462989807129</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5337514877319</v>
+        <v>10.5337524414062</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>10.5956125259399</v>
+        <v>10.595609664917</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G287" t="n">
-        <v>10.4630546569824</v>
+        <v>10.4630556106567</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G288" t="n">
-        <v>10.5425891876221</v>
+        <v>10.5425882339478</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G289" t="n">
-        <v>10.5514249801636</v>
+        <v>10.5514259338379</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>11.75</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3835210800171</v>
+        <v>10.3835220336914</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G291" t="n">
-        <v>10.5337514877319</v>
+        <v>10.5337524414062</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G293" t="n">
-        <v>10.49840259552</v>
+        <v>10.4984016418457</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G295" t="n">
-        <v>10.4100332260132</v>
+        <v>10.4100322723389</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G296" t="n">
-        <v>10.4277086257935</v>
+        <v>10.4277057647705</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>12.25</v>
       </c>
       <c r="G297" t="n">
-        <v>10.8253746032715</v>
+        <v>10.8253736495972</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G298" t="n">
-        <v>11.3555965423584</v>
+        <v>11.3555955886841</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>11.4616422653198</v>
+        <v>11.4616403579712</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.8593072891235</v>
+        <v>11.8593082427979</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G301" t="n">
-        <v>12.124418258667</v>
+        <v>12.1244201660156</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G302" t="n">
-        <v>12.1597681045532</v>
+        <v>12.1597671508789</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G303" t="n">
-        <v>11.8946561813354</v>
+        <v>11.8946552276611</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G304" t="n">
-        <v>11.6295461654663</v>
+        <v>11.6295442581177</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G307" t="n">
-        <v>11.4528036117554</v>
+        <v>11.4528045654297</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>13</v>
       </c>
       <c r="G308" t="n">
-        <v>11.4881525039673</v>
+        <v>11.488151550293</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>13.9300003051758</v>
       </c>
       <c r="G311" t="n">
-        <v>12.3099956512451</v>
+        <v>12.3099966049194</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.0183734893799</v>
+        <v>12.0183744430542</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G314" t="n">
-        <v>11.390944480896</v>
+        <v>11.3909454345703</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>11.6648921966553</v>
+        <v>11.6648931503296</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.6648921966553</v>
+        <v>11.6648931503296</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G318" t="n">
-        <v>11.4704780578613</v>
+        <v>11.4704761505127</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5411729812622</v>
+        <v>11.5411748886108</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G320" t="n">
-        <v>11.7532625198364</v>
+        <v>11.7532644271851</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G321" t="n">
-        <v>11.9034938812256</v>
+        <v>11.9034929275513</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G322" t="n">
-        <v>11.7444267272949</v>
+        <v>11.7444257736206</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.7267513275146</v>
+        <v>11.7267532348633</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G325" t="n">
-        <v>11.6737289428711</v>
+        <v>11.6737308502197</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>11.885817527771</v>
+        <v>11.8858184814453</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G327" t="n">
-        <v>11.965350151062</v>
+        <v>11.9653520584106</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G329" t="n">
-        <v>11.7179145812988</v>
+        <v>11.7179136276245</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G332" t="n">
-        <v>12.0272102355957</v>
+        <v>12.0272130966187</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G340" t="n">
-        <v>12.7518472671509</v>
+        <v>12.7518482208252</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G342" t="n">
-        <v>12.7165002822876</v>
+        <v>12.7165031433105</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G344" t="n">
-        <v>13.55601978302</v>
+        <v>13.5560188293457</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G346" t="n">
-        <v>13.6267137527466</v>
+        <v>13.6267147064209</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G349" t="n">
-        <v>13.8653154373169</v>
+        <v>13.8653163909912</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>13.7857837677002</v>
+        <v>13.7857828140259</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G351" t="n">
-        <v>13.7150869369507</v>
+        <v>13.7150859832764</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.1671886444092</v>
+        <v>13.1671895980835</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G353" t="n">
-        <v>13.158353805542</v>
+        <v>13.1583528518677</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3425397872925</v>
+        <v>13.3425407409668</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G357" t="n">
-        <v>13.5476732254028</v>
+        <v>13.5476722717285</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>13.5565919876099</v>
+        <v>13.5565910339355</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.8419952392578</v>
+        <v>13.8419933319092</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G362" t="n">
-        <v>13.984694480896</v>
+        <v>13.9846954345703</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G363" t="n">
-        <v>14.2165832519531</v>
+        <v>14.2165842056274</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G364" t="n">
-        <v>14.100640296936</v>
+        <v>14.1006393432617</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>14.0025310516357</v>
+        <v>14.0025320053101</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G366" t="n">
-        <v>14.0738830566406</v>
+        <v>14.073881149292</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>13.9133462905884</v>
+        <v>13.9133443832397</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G368" t="n">
-        <v>14.1987457275391</v>
+        <v>14.1987476348877</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G369" t="n">
-        <v>14.3057727813721</v>
+        <v>14.3057737350464</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G371" t="n">
-        <v>13.984694480896</v>
+        <v>13.9846954345703</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G373" t="n">
-        <v>13.6814556121826</v>
+        <v>13.6814546585083</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G374" t="n">
-        <v>13.984694480896</v>
+        <v>13.9846954345703</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G375" t="n">
-        <v>13.9757766723633</v>
+        <v>13.9757747650146</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5119962692261</v>
+        <v>13.5119981765747</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G377" t="n">
-        <v>13.8776693344116</v>
+        <v>13.8776702880859</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G378" t="n">
-        <v>13.7349681854248</v>
+        <v>13.7349672317505</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G379" t="n">
-        <v>13.6814556121826</v>
+        <v>13.6814546585083</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G380" t="n">
-        <v>13.5565919876099</v>
+        <v>13.5565910339355</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G381" t="n">
-        <v>13.3514585494995</v>
+        <v>13.3514595031738</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>13.0660572052002</v>
+        <v>13.0660562515259</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G387" t="n">
-        <v>13.3157835006714</v>
+        <v>13.31578540802</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>13.2890272140503</v>
+        <v>13.2890281677246</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G391" t="n">
-        <v>13.4763212203979</v>
+        <v>13.4763221740723</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298366546631</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>13.8687505722046</v>
+        <v>13.8687515258789</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G397" t="n">
-        <v>13.7349681854248</v>
+        <v>13.7349672317505</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>13.6457786560059</v>
+        <v>13.6457796096802</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G399" t="n">
-        <v>13.4317302703857</v>
+        <v>13.4317274093628</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G401" t="n">
-        <v>13.8330755233765</v>
+        <v>13.8330745697021</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>13.6814556121826</v>
+        <v>13.6814546585083</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G403" t="n">
-        <v>13.7260494232178</v>
+        <v>13.7260484695435</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>13.3960542678833</v>
+        <v>13.396053314209</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G406" t="n">
-        <v>13.1641635894775</v>
+        <v>13.1641645431519</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>13.021463394165</v>
+        <v>13.0214643478394</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G412" t="n">
-        <v>12.9947071075439</v>
+        <v>12.9947080612183</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>12.8876810073853</v>
+        <v>12.8876819610596</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G414" t="n">
-        <v>12.6914682388306</v>
+        <v>12.6914663314819</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G416" t="n">
-        <v>13.0571374893188</v>
+        <v>13.0571393966675</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>12.914436340332</v>
+        <v>12.9144382476807</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G418" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G420" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G421" t="n">
-        <v>12.8609266281128</v>
+        <v>12.8609256744385</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G422" t="n">
-        <v>12.8787622451782</v>
+        <v>12.8787612915039</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G423" t="n">
-        <v>12.7984943389893</v>
+        <v>12.7984933853149</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G424" t="n">
-        <v>12.7360610961914</v>
+        <v>12.7360601425171</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G425" t="n">
-        <v>12.5487661361694</v>
+        <v>12.5487651824951</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5755233764648</v>
+        <v>12.5755224227905</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6736297607422</v>
+        <v>12.6736288070679</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G428" t="n">
-        <v>12.7539005279541</v>
+        <v>12.7538995742798</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>14.75</v>
       </c>
       <c r="G431" t="n">
-        <v>13.1552457809448</v>
+        <v>13.1552467346191</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G432" t="n">
-        <v>12.9947071075439</v>
+        <v>12.9947080612183</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G433" t="n">
-        <v>13.1284894943237</v>
+        <v>13.1284885406494</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1998405456543</v>
+        <v>13.19983959198</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>13.2890272140503</v>
+        <v>13.2890281677246</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G439" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298366546631</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G440" t="n">
-        <v>13.5476732254028</v>
+        <v>13.5476722717285</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G441" t="n">
-        <v>13.6279430389404</v>
+        <v>13.6279411315918</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G443" t="n">
-        <v>13.6814556121826</v>
+        <v>13.6814546585083</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G444" t="n">
-        <v>13.7438869476318</v>
+        <v>13.7438879013062</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G445" t="n">
-        <v>13.9490203857422</v>
+        <v>13.9490194320679</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>14.2165832519531</v>
+        <v>14.2165842056274</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>14.1363153457642</v>
+        <v>14.1363143920898</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>14.1630716323853</v>
+        <v>14.1630706787109</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G451" t="n">
-        <v>13.9311819076538</v>
+        <v>13.9311828613281</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G452" t="n">
-        <v>13.8419952392578</v>
+        <v>13.8419933319092</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G453" t="n">
-        <v>13.9311819076538</v>
+        <v>13.9311828613281</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G454" t="n">
-        <v>13.8776693344116</v>
+        <v>13.8776702880859</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G455" t="n">
-        <v>13.7349681854248</v>
+        <v>13.7349672317505</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>15.25</v>
       </c>
       <c r="G457" t="n">
-        <v>13.6011867523193</v>
+        <v>13.601185798645</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298366546631</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>13.4674034118652</v>
+        <v>13.4674024581909</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>13.3425397872925</v>
+        <v>13.3425407409668</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>13.5922660827637</v>
+        <v>13.592267036438</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G467" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298366546631</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>13.2890272140503</v>
+        <v>13.2890281677246</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G470" t="n">
-        <v>13.2265968322754</v>
+        <v>13.2265958786011</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G471" t="n">
-        <v>13.3960542678833</v>
+        <v>13.396053314209</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G473" t="n">
-        <v>13.2265968322754</v>
+        <v>13.2265958786011</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>14.75</v>
       </c>
       <c r="G474" t="n">
-        <v>13.1552457809448</v>
+        <v>13.1552467346191</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G476" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G477" t="n">
-        <v>12.5844411849976</v>
+        <v>12.5844402313232</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>9.87312412261963</v>
+        <v>9.873122215271</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G479" t="n">
-        <v>9.44501972198486</v>
+        <v>9.44502067565918</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>9.39150714874268</v>
+        <v>9.39150619506836</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G482" t="n">
-        <v>9.0615119934082</v>
+        <v>9.06151008605957</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G483" t="n">
-        <v>9.03475570678711</v>
+        <v>9.03475475311279</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G484" t="n">
-        <v>8.94556617736816</v>
+        <v>8.9455680847168</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>9.20421123504639</v>
+        <v>9.20421314239502</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.45393943786621</v>
+        <v>9.45394039154053</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G487" t="n">
-        <v>9.38258934020996</v>
+        <v>9.38259029388428</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G488" t="n">
-        <v>9.24880599975586</v>
+        <v>9.24880695343018</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G490" t="n">
-        <v>9.07043075561523</v>
+        <v>9.07042980194092</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G491" t="n">
-        <v>8.94556617736816</v>
+        <v>8.9455680847168</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>8.84746074676514</v>
+        <v>8.84745979309082</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>8.77611064910889</v>
+        <v>8.77610969543457</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G496" t="n">
-        <v>8.85637950897217</v>
+        <v>8.85638046264648</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>8.88313674926758</v>
+        <v>8.88313484191895</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>10</v>
       </c>
       <c r="G499" t="n">
-        <v>8.91880989074707</v>
+        <v>8.9188117980957</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G501" t="n">
-        <v>8.91435241699219</v>
+        <v>8.91435146331787</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>8.84299945831299</v>
+        <v>8.84300136566162</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G504" t="n">
-        <v>9.10610389709473</v>
+        <v>9.10610675811768</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G506" t="n">
-        <v>8.93664741516113</v>
+        <v>8.93664836883545</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G507" t="n">
-        <v>8.93664741516113</v>
+        <v>8.93664836883545</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>8.84299945831299</v>
+        <v>8.84300136566162</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G509" t="n">
-        <v>8.93664741516113</v>
+        <v>8.93664836883545</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G510" t="n">
-        <v>8.89651489257812</v>
+        <v>8.89651298522949</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>8.84746074676514</v>
+        <v>8.84745979309082</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G516" t="n">
-        <v>9.4271821975708</v>
+        <v>9.42718315124512</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G517" t="n">
-        <v>9.64123439788818</v>
+        <v>9.6412353515625</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>9.69474601745605</v>
+        <v>9.69474697113037</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G520" t="n">
-        <v>9.67690944671631</v>
+        <v>9.67691040039062</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>11</v>
       </c>
       <c r="G521" t="n">
-        <v>9.81069183349609</v>
+        <v>9.81069087982178</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G522" t="n">
-        <v>9.87312412261963</v>
+        <v>9.873122215271</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G523" t="n">
-        <v>10.0515003204346</v>
+        <v>10.0514993667603</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>11.25</v>
       </c>
       <c r="G524" t="n">
-        <v>10.0336608886719</v>
+        <v>10.0336618423462</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.25</v>
       </c>
       <c r="G525" t="n">
-        <v>10.0336608886719</v>
+        <v>10.0336618423462</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G526" t="n">
-        <v>10.0693368911743</v>
+        <v>10.0693378448486</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G527" t="n">
-        <v>9.95339202880859</v>
+        <v>9.95339298248291</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G529" t="n">
-        <v>9.70366764068604</v>
+        <v>9.70366668701172</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>10.0559597015381</v>
+        <v>10.0559587478638</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G533" t="n">
-        <v>8.66908359527588</v>
+        <v>8.66908264160156</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G534" t="n">
-        <v>8.76719093322754</v>
+        <v>8.76718997955322</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G536" t="n">
-        <v>8.17141437530518</v>
+        <v>8.17141342163086</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>7.94666051864624</v>
+        <v>7.94666004180908</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G539" t="n">
-        <v>7.87352657318115</v>
+        <v>7.87352561950684</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G540" t="n">
-        <v>7.75044536590576</v>
+        <v>7.75044631958008</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G541" t="n">
-        <v>7.7058539390564</v>
+        <v>7.70585298538208</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.85033798217773</v>
+        <v>7.85033702850342</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>8.92199993133545</v>
       </c>
       <c r="G544" t="n">
-        <v>7.95736217498779</v>
+        <v>7.95736312866211</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>9.0620002746582</v>
       </c>
       <c r="G545" t="n">
-        <v>8.08222770690918</v>
+        <v>8.08222579956055</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>9.07199954986572</v>
       </c>
       <c r="G546" t="n">
-        <v>8.09114551544189</v>
+        <v>8.09114360809326</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>9.07800006866455</v>
       </c>
       <c r="G547" t="n">
-        <v>8.09649467468262</v>
+        <v>8.09649562835693</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G548" t="n">
-        <v>8.12325286865234</v>
+        <v>8.12325096130371</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G549" t="n">
-        <v>7.85747194290161</v>
+        <v>7.85747241973877</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G551" t="n">
-        <v>7.89671421051025</v>
+        <v>7.89671516418457</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85747194290161</v>
+        <v>7.85747241973877</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G554" t="n">
-        <v>7.88244438171387</v>
+        <v>7.88244390487671</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G555" t="n">
-        <v>7.6541223526001</v>
+        <v>7.65412282943726</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>8.63399982452393</v>
       </c>
       <c r="G556" t="n">
-        <v>7.70050048828125</v>
+        <v>7.70050096511841</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>8.79800033569336</v>
       </c>
       <c r="G557" t="n">
-        <v>7.84676837921143</v>
+        <v>7.84677028656006</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>8.8120002746582</v>
       </c>
       <c r="G558" t="n">
-        <v>7.85925531387329</v>
+        <v>7.85925579071045</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>9.18599987030029</v>
       </c>
       <c r="G560" t="n">
-        <v>8.19281768798828</v>
+        <v>8.19282054901123</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G561" t="n">
-        <v>8.25703430175781</v>
+        <v>8.25703525543213</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>9.47799968719482</v>
       </c>
       <c r="G565" t="n">
-        <v>8.45324897766113</v>
+        <v>8.45324802398682</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>9.41800022125244</v>
       </c>
       <c r="G566" t="n">
-        <v>8.39973640441895</v>
+        <v>8.39973545074463</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G568" t="n">
-        <v>8.37476348876953</v>
+        <v>8.37476253509521</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.21399974822998</v>
       </c>
       <c r="G569" t="n">
-        <v>8.21779155731201</v>
+        <v>8.21779251098633</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.40200042724609</v>
       </c>
       <c r="G570" t="n">
-        <v>8.38546657562256</v>
+        <v>8.38546562194824</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G571" t="n">
-        <v>8.3266019821167</v>
+        <v>8.32660388946533</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G572" t="n">
-        <v>8.48713970184326</v>
+        <v>8.48714160919189</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.39599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>8.38011360168457</v>
+        <v>8.3801155090332</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>9.37800025939941</v>
       </c>
       <c r="G574" t="n">
-        <v>8.3640604019165</v>
+        <v>8.36406135559082</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>9.16800022125244</v>
       </c>
       <c r="G575" t="n">
-        <v>8.17676639556885</v>
+        <v>8.17676448822021</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G577" t="n">
-        <v>8.41043758392334</v>
+        <v>8.41043853759766</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G578" t="n">
-        <v>8.4461145401001</v>
+        <v>8.44611167907715</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G580" t="n">
-        <v>8.49427604675293</v>
+        <v>8.49427509307861</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.33800029754639</v>
       </c>
       <c r="G581" t="n">
-        <v>8.32838439941406</v>
+        <v>8.3283863067627</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G583" t="n">
-        <v>8.36941242218018</v>
+        <v>8.36941051483154</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.52999973297119</v>
       </c>
       <c r="G584" t="n">
-        <v>8.49962520599365</v>
+        <v>8.49962615966797</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.5939998626709</v>
       </c>
       <c r="G585" t="n">
-        <v>8.55670642852783</v>
+        <v>8.55670547485352</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.76599979400635</v>
       </c>
       <c r="G586" t="n">
-        <v>8.71011066436768</v>
+        <v>8.71010875701904</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>9.91600036621094</v>
       </c>
       <c r="G587" t="n">
-        <v>8.84389400482178</v>
+        <v>8.84389305114746</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.92599964141846</v>
       </c>
       <c r="G588" t="n">
-        <v>8.85280990600586</v>
+        <v>8.85280895233154</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.6540002822876</v>
       </c>
       <c r="G591" t="n">
-        <v>8.6102180480957</v>
+        <v>8.61021995544434</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G592" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>9.5</v>
       </c>
       <c r="G593" t="n">
-        <v>8.47286891937256</v>
+        <v>8.47286987304688</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G594" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G595" t="n">
-        <v>8.72081279754639</v>
+        <v>8.7208137512207</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>9.72799968719482</v>
       </c>
       <c r="G596" t="n">
-        <v>8.67621803283691</v>
+        <v>8.67621898651123</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>9.71399974822998</v>
       </c>
       <c r="G597" t="n">
-        <v>8.66373252868652</v>
+        <v>8.66373157501221</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>9.64599990844727</v>
       </c>
       <c r="G598" t="n">
-        <v>8.6030855178833</v>
+        <v>8.60308361053467</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>9.65200042724609</v>
       </c>
       <c r="G599" t="n">
-        <v>8.60843563079834</v>
+        <v>8.60843753814697</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.94400024414062</v>
       </c>
       <c r="G600" t="n">
-        <v>8.86886501312256</v>
+        <v>8.86886596679688</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G601" t="n">
-        <v>8.57276153564453</v>
+        <v>8.57276058197021</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G602" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G603" t="n">
-        <v>8.41043758392334</v>
+        <v>8.41043853759766</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G604" t="n">
-        <v>8.41043758392334</v>
+        <v>8.41043853759766</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G605" t="n">
-        <v>8.23919773101807</v>
+        <v>8.23919677734375</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G609" t="n">
-        <v>8.09499263763428</v>
+        <v>8.09499168395996</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>8.79800033569336</v>
       </c>
       <c r="G610" t="n">
-        <v>7.96997928619385</v>
+        <v>7.96998119354248</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G611" t="n">
-        <v>7.98991012573242</v>
+        <v>7.98990964889526</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G612" t="n">
-        <v>8.16383934020996</v>
+        <v>8.16384029388428</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>7.96273326873779</v>
+        <v>7.96273422241211</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>8.72399997711182</v>
       </c>
       <c r="G616" t="n">
-        <v>7.90294504165649</v>
+        <v>7.90294361114502</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G618" t="n">
-        <v>7.99715757369995</v>
+        <v>7.99715566635132</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.97179269790649</v>
+        <v>7.97179126739502</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G621" t="n">
-        <v>7.99715757369995</v>
+        <v>7.99715566635132</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G622" t="n">
-        <v>7.82503843307495</v>
+        <v>7.82503795623779</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G623" t="n">
-        <v>8.12398147583008</v>
+        <v>8.12398242950439</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G624" t="n">
-        <v>8.17108821868896</v>
+        <v>8.17108631134033</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G626" t="n">
-        <v>8.15115737915039</v>
+        <v>8.15115642547607</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.91800022125244</v>
       </c>
       <c r="G629" t="n">
-        <v>8.07868671417236</v>
+        <v>8.07868576049805</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G631" t="n">
-        <v>7.83590841293335</v>
+        <v>7.83590936660767</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.7480001449585</v>
       </c>
       <c r="G632" t="n">
-        <v>7.92468643188477</v>
+        <v>7.92468595504761</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G633" t="n">
-        <v>7.72539043426514</v>
+        <v>7.72539138793945</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>8.35599994659424</v>
       </c>
       <c r="G634" t="n">
-        <v>7.56957864761353</v>
+        <v>7.56957817077637</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>8.35400009155273</v>
       </c>
       <c r="G636" t="n">
-        <v>7.56776714324951</v>
+        <v>7.56776809692383</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G637" t="n">
-        <v>7.66922616958618</v>
+        <v>7.66922569274902</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>8.36800003051758</v>
       </c>
       <c r="G638" t="n">
-        <v>7.58044958114624</v>
+        <v>7.58044910430908</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>8.59200000762939</v>
       </c>
       <c r="G639" t="n">
-        <v>7.78336811065674</v>
+        <v>7.7833685874939</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>8.55200004577637</v>
       </c>
       <c r="G640" t="n">
-        <v>7.74713182449341</v>
+        <v>7.74713230133057</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G641" t="n">
-        <v>7.81416845321655</v>
+        <v>7.81416893005371</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>8.57600021362305</v>
       </c>
       <c r="G642" t="n">
-        <v>7.76887464523315</v>
+        <v>7.768874168396</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>8.60599994659424</v>
       </c>
       <c r="G643" t="n">
-        <v>7.79605054855347</v>
+        <v>7.79605102539062</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>7.77249765396118</v>
+        <v>7.77249670028687</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>8.61400032043457</v>
       </c>
       <c r="G645" t="n">
-        <v>7.80329704284668</v>
+        <v>7.80329656600952</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>9</v>
       </c>
       <c r="G647" t="n">
-        <v>8.15296840667725</v>
+        <v>8.15296936035156</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.30799961090088</v>
       </c>
       <c r="G649" t="n">
-        <v>8.43198013305664</v>
+        <v>8.43198108673096</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.32600021362305</v>
       </c>
       <c r="G650" t="n">
-        <v>8.44828701019287</v>
+        <v>8.44828796386719</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.25399971008301</v>
       </c>
       <c r="G651" t="n">
-        <v>8.38306427001953</v>
+        <v>8.38306522369385</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G653" t="n">
-        <v>8.33233451843262</v>
+        <v>8.3323335647583</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G654" t="n">
-        <v>8.36857032775879</v>
+        <v>8.36856842041016</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G655" t="n">
-        <v>8.3160285949707</v>
+        <v>8.31603050231934</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>8.34320640563965</v>
+        <v>8.34320449829102</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>9.26799964904785</v>
       </c>
       <c r="G658" t="n">
-        <v>8.3957462310791</v>
+        <v>8.39574718475342</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.25</v>
       </c>
       <c r="G659" t="n">
-        <v>9.285325050354</v>
+        <v>9.28532600402832</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>9.41667938232422</v>
+        <v>9.41668033599854</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.375</v>
       </c>
       <c r="G661" t="n">
-        <v>9.39856243133545</v>
+        <v>9.39856147766113</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G663" t="n">
-        <v>9.62956142425537</v>
+        <v>9.62956237792969</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G664" t="n">
-        <v>9.66579914093018</v>
+        <v>9.66579723358154</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.4849996566772</v>
       </c>
       <c r="G666" t="n">
-        <v>9.49820804595947</v>
+        <v>9.49820899963379</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G667" t="n">
-        <v>9.21738433837891</v>
+        <v>9.21738529205322</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G670" t="n">
-        <v>8.98819446563721</v>
+        <v>8.98819541931152</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>9.68400001525879</v>
       </c>
       <c r="G671" t="n">
-        <v>8.7725944519043</v>
+        <v>8.77259540557861</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9.8439998626709</v>
       </c>
       <c r="G674" t="n">
-        <v>8.91753578186035</v>
+        <v>8.91753673553467</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.02262020111084</v>
+        <v>9.02261829376221</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G678" t="n">
-        <v>8.96464252471924</v>
+        <v>8.96464157104492</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G683" t="n">
-        <v>8.82876014709473</v>
+        <v>8.82875823974609</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G684" t="n">
-        <v>8.93203067779541</v>
+        <v>8.93203163146973</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G685" t="n">
-        <v>8.84869003295898</v>
+        <v>8.84868907928467</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G687" t="n">
-        <v>9.44838714599609</v>
+        <v>9.44838523864746</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G688" t="n">
-        <v>9.27626800537109</v>
+        <v>9.27626609802246</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G689" t="n">
-        <v>9.4393253326416</v>
+        <v>9.43932723999023</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>10.2849998474121</v>
       </c>
       <c r="G690" t="n">
-        <v>9.31703090667725</v>
+        <v>9.31703186035156</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G692" t="n">
-        <v>9.21738433837891</v>
+        <v>9.21738529205322</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>10.6450004577637</v>
       </c>
       <c r="G696" t="n">
-        <v>9.64315128326416</v>
+        <v>9.64315032958984</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>10.7150001525879</v>
       </c>
       <c r="G698" t="n">
-        <v>9.70656204223633</v>
+        <v>9.70656299591064</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>10.7650003433228</v>
       </c>
       <c r="G700" t="n">
-        <v>9.75185775756836</v>
+        <v>9.75185680389404</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G702" t="n">
-        <v>9.45744228363037</v>
+        <v>9.457444190979</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>10.5649995803833</v>
       </c>
       <c r="G703" t="n">
-        <v>9.5706787109375</v>
+        <v>9.57067966461182</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>10.3649997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>9.38950157165527</v>
+        <v>9.38950252532959</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>9.89599990844727</v>
       </c>
       <c r="G711" t="n">
-        <v>8.96464252471924</v>
+        <v>8.96464157104492</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G712" t="n">
-        <v>8.89036083221436</v>
+        <v>8.89035892486572</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G714" t="n">
-        <v>9.31250381469727</v>
+        <v>9.31250190734863</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.93200016021729</v>
       </c>
       <c r="G716" t="n">
-        <v>8.99725532531738</v>
+        <v>8.99725437164307</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>8.90485382080078</v>
+        <v>8.9048547744751</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G719" t="n">
-        <v>8.84869003295898</v>
+        <v>8.84868907928467</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03711223602295</v>
+        <v>9.03711318969727</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.70800018310547</v>
       </c>
       <c r="G721" t="n">
-        <v>8.79433631896973</v>
+        <v>8.79433727264404</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G723" t="n">
-        <v>8.50082969665527</v>
+        <v>8.50082874298096</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.52200031280518</v>
       </c>
       <c r="G725" t="n">
-        <v>8.62584209442139</v>
+        <v>8.62584114074707</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.65120506286621</v>
+        <v>8.65120601654053</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>9.01399993896484</v>
       </c>
       <c r="G732" t="n">
-        <v>8.16565036773682</v>
+        <v>8.16565132141113</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>9.06400012969971</v>
       </c>
       <c r="G733" t="n">
-        <v>8.21094608306885</v>
+        <v>8.21094512939453</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G734" t="n">
-        <v>8.06237983703613</v>
+        <v>8.06238079071045</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>8.60799980163574</v>
       </c>
       <c r="G735" t="n">
-        <v>7.7978630065918</v>
+        <v>7.79786109924316</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G737" t="n">
-        <v>7.5405912399292</v>
+        <v>7.54059076309204</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>8.22799968719482</v>
       </c>
       <c r="G738" t="n">
-        <v>7.45362520217896</v>
+        <v>7.45362567901611</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>8.25800037384033</v>
       </c>
       <c r="G740" t="n">
-        <v>7.4808030128479</v>
+        <v>7.48080253601074</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>8.61800003051758</v>
       </c>
       <c r="G743" t="n">
-        <v>7.80692052841187</v>
+        <v>7.80692148208618</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>8.65799999237061</v>
       </c>
       <c r="G745" t="n">
-        <v>7.8431568145752</v>
+        <v>7.84315490722656</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>8.70600032806396</v>
       </c>
       <c r="G746" t="n">
-        <v>7.88663959503174</v>
+        <v>7.88663864135742</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>8.9379997253418</v>
       </c>
       <c r="G747" t="n">
-        <v>8.09680557250977</v>
+        <v>8.09680366516113</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>8.75599956512451</v>
       </c>
       <c r="G748" t="n">
-        <v>7.93193244934082</v>
+        <v>7.93193387985229</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G749" t="n">
-        <v>7.84677934646606</v>
+        <v>7.84677886962891</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>8.28400039672852</v>
       </c>
       <c r="G750" t="n">
-        <v>7.50435495376587</v>
+        <v>7.50435447692871</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>8.32400035858154</v>
       </c>
       <c r="G751" t="n">
-        <v>7.5405912399292</v>
+        <v>7.54059076309204</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>8.05399990081787</v>
       </c>
       <c r="G752" t="n">
-        <v>7.29600143432617</v>
+        <v>7.29600191116333</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>8.25599956512451</v>
       </c>
       <c r="G754" t="n">
-        <v>7.47899103164673</v>
+        <v>7.47898960113525</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G755" t="n">
-        <v>7.41014289855957</v>
+        <v>7.41014337539673</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>8.25599956512451</v>
       </c>
       <c r="G759" t="n">
-        <v>7.47899103164673</v>
+        <v>7.47898960113525</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>7.9980001449585</v>
       </c>
       <c r="G760" t="n">
-        <v>7.24527215957642</v>
+        <v>7.24527168273926</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>7.73799991607666</v>
       </c>
       <c r="G761" t="n">
-        <v>7.00974178314209</v>
+        <v>7.00974130630493</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>7.58400011062622</v>
       </c>
       <c r="G762" t="n">
-        <v>6.87023544311523</v>
+        <v>6.87023496627808</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>7.81599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>7.08040046691895</v>
+        <v>7.0804009437561</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>7.81599998474121</v>
       </c>
       <c r="G767" t="n">
-        <v>7.08040046691895</v>
+        <v>7.0804009437561</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>8.04399967193604</v>
       </c>
       <c r="G769" t="n">
-        <v>7.28694248199463</v>
+        <v>7.28694200515747</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G773" t="n">
-        <v>6.76696443557739</v>
+        <v>6.76696395874023</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>8.08399963378906</v>
       </c>
       <c r="G777" t="n">
-        <v>7.32317733764648</v>
+        <v>7.32317781448364</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G778" t="n">
-        <v>7.2344012260437</v>
+        <v>7.23440170288086</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G779" t="n">
-        <v>7.22715425491333</v>
+        <v>7.22715473175049</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G780" t="n">
-        <v>7.41014289855957</v>
+        <v>7.41014337539673</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>8.25399971008301</v>
       </c>
       <c r="G781" t="n">
-        <v>7.47717809677124</v>
+        <v>7.4771785736084</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>8.31799983978271</v>
       </c>
       <c r="G783" t="n">
-        <v>7.53515434265137</v>
+        <v>7.53515529632568</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>8.45800018310547</v>
       </c>
       <c r="G785" t="n">
-        <v>7.66197967529297</v>
+        <v>7.66197919845581</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>8.65200042724609</v>
       </c>
       <c r="G787" t="n">
-        <v>7.83772134780884</v>
+        <v>7.83772087097168</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G789" t="n">
-        <v>7.99715757369995</v>
+        <v>7.99715566635132</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G790" t="n">
-        <v>7.72539043426514</v>
+        <v>7.72539138793945</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>8.55200004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>7.74713182449341</v>
+        <v>7.74713230133057</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>8.66600036621094</v>
       </c>
       <c r="G792" t="n">
-        <v>7.85040378570557</v>
+        <v>7.85040426254272</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G793" t="n">
-        <v>7.93555784225464</v>
+        <v>7.93555593490601</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>8.9040002822876</v>
       </c>
       <c r="G796" t="n">
-        <v>8.06600379943848</v>
+        <v>8.06600475311279</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G797" t="n">
-        <v>8.09136772155762</v>
+        <v>8.09136962890625</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>7.97179269790649</v>
+        <v>7.97179126739502</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>8.91800022125244</v>
       </c>
       <c r="G799" t="n">
-        <v>8.07868671417236</v>
+        <v>8.07868576049805</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G800" t="n">
-        <v>7.83590841293335</v>
+        <v>7.83590936660767</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G802" t="n">
-        <v>8.03520488739014</v>
+        <v>8.0352029800415</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>8.92800045013428</v>
       </c>
       <c r="G803" t="n">
-        <v>8.08774471282959</v>
+        <v>8.08774662017822</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>8.86600017547607</v>
       </c>
       <c r="G805" t="n">
-        <v>8.03157997131348</v>
+        <v>8.03158283233643</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>8.8120002746582</v>
       </c>
       <c r="G806" t="n">
-        <v>7.98266220092773</v>
+        <v>7.98266363143921</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>7.88120412826538</v>
+        <v>7.88120365142822</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G809" t="n">
-        <v>7.95367383956909</v>
+        <v>7.95367336273193</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G810" t="n">
-        <v>7.81779098510742</v>
+        <v>7.81779050827026</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G813" t="n">
-        <v>7.89932107925415</v>
+        <v>7.89932155609131</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G815" t="n">
-        <v>8.85593605041504</v>
+        <v>8.85593700408936</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G817" t="n">
-        <v>9.25814914703369</v>
+        <v>9.25815010070801</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G819" t="n">
-        <v>9.41215133666992</v>
+        <v>9.41214942932129</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G821" t="n">
-        <v>9.18114852905273</v>
+        <v>9.18114948272705</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>10.0950002670288</v>
       </c>
       <c r="G822" t="n">
-        <v>9.1449146270752</v>
+        <v>9.14491367340088</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G823" t="n">
-        <v>9.27173805236816</v>
+        <v>9.27173709869385</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>10.2550001144409</v>
       </c>
       <c r="G825" t="n">
-        <v>9.28985595703125</v>
+        <v>9.28985500335693</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>9.4347972869873</v>
+        <v>9.43479824066162</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>10.5</v>
       </c>
       <c r="G832" t="n">
-        <v>9.51179790496826</v>
+        <v>9.51179695129395</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>9.30797290802002</v>
+        <v>9.3079719543457</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G834" t="n">
-        <v>9.25814914703369</v>
+        <v>9.25815010070801</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G835" t="n">
-        <v>9.26720809936523</v>
+        <v>9.26720714569092</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G836" t="n">
-        <v>9.50273704528809</v>
+        <v>9.50273895263672</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G837" t="n">
-        <v>9.67938709259033</v>
+        <v>9.67938613891602</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>10.6850004196167</v>
       </c>
       <c r="G839" t="n">
-        <v>9.67938709259033</v>
+        <v>9.67938613891602</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G840" t="n">
-        <v>9.61597442626953</v>
+        <v>9.6159725189209</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G841" t="n">
-        <v>9.62956142425537</v>
+        <v>9.62956237792969</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>9.55709171295166</v>
+        <v>9.55709266662598</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G845" t="n">
-        <v>9.4347972869873</v>
+        <v>9.43479824066162</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G847" t="n">
-        <v>9.22191333770752</v>
+        <v>9.22191429138184</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G848" t="n">
-        <v>9.13132572174072</v>
+        <v>9.13132476806641</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>9.88799953460693</v>
       </c>
       <c r="G849" t="n">
-        <v>8.95739555358887</v>
+        <v>8.95739364624023</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.75599956512451</v>
       </c>
       <c r="G851" t="n">
-        <v>8.83781719207764</v>
+        <v>8.83781909942627</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.67599964141846</v>
       </c>
       <c r="G855" t="n">
-        <v>8.76534748077393</v>
+        <v>8.76534652709961</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G856" t="n">
-        <v>8.92840671539307</v>
+        <v>8.92840766906738</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G857" t="n">
-        <v>9.08603000640869</v>
+        <v>9.08603096008301</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>9.94200038909912</v>
       </c>
       <c r="G859" t="n">
-        <v>9.13386917114258</v>
+        <v>9.13386821746826</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>9.27902507781982</v>
+        <v>9.27902603149414</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G863" t="n">
-        <v>9.26983833312988</v>
+        <v>9.26983737945557</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G864" t="n">
-        <v>9.07323265075684</v>
+        <v>9.07323360443115</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.78600025177002</v>
       </c>
       <c r="G867" t="n">
-        <v>8.99054908752441</v>
+        <v>8.9905481338501</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>9.94200038909912</v>
       </c>
       <c r="G868" t="n">
-        <v>9.13386917114258</v>
+        <v>9.13386821746826</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G869" t="n">
-        <v>9.34792900085449</v>
+        <v>9.34792995452881</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G874" t="n">
-        <v>9.7475700378418</v>
+        <v>9.74756908416748</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>10.6549997329712</v>
       </c>
       <c r="G876" t="n">
-        <v>9.78891277313232</v>
+        <v>9.78891181945801</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G877" t="n">
-        <v>9.99562454223633</v>
+        <v>9.99562358856201</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G878" t="n">
-        <v>9.9037504196167</v>
+        <v>9.90375137329102</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.9650001525879</v>
       </c>
       <c r="G881" t="n">
-        <v>10.0737142562866</v>
+        <v>10.0737133026123</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G883" t="n">
-        <v>10.0966825485229</v>
+        <v>10.0966815948486</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>11.2849998474121</v>
       </c>
       <c r="G884" t="n">
-        <v>10.3677024841309</v>
+        <v>10.3677034378052</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>11.25</v>
       </c>
       <c r="G886" t="n">
-        <v>10.3355474472046</v>
+        <v>10.3355484008789</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>11.0550003051758</v>
       </c>
       <c r="G887" t="n">
-        <v>10.1563987731934</v>
+        <v>10.156397819519</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>11.2849998474121</v>
       </c>
       <c r="G889" t="n">
-        <v>10.3677024841309</v>
+        <v>10.3677034378052</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>10.2804250717163</v>
+        <v>10.280424118042</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>11.4650001525879</v>
       </c>
       <c r="G892" t="n">
-        <v>10.5330715179443</v>
+        <v>10.53307056427</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>11.4650001525879</v>
       </c>
       <c r="G893" t="n">
-        <v>10.5330715179443</v>
+        <v>10.53307056427</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G894" t="n">
-        <v>10.4549827575684</v>
+        <v>10.454981803894</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>11.6549997329712</v>
       </c>
       <c r="G898" t="n">
-        <v>10.7076263427734</v>
+        <v>10.7076282501221</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G899" t="n">
-        <v>10.6387233734131</v>
+        <v>10.6387243270874</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>11.664999961853</v>
       </c>
       <c r="G900" t="n">
-        <v>10.7168140411377</v>
+        <v>10.716814994812</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>11.5550003051758</v>
       </c>
       <c r="G901" t="n">
-        <v>10.6157569885254</v>
+        <v>10.6157560348511</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>11.2849998474121</v>
       </c>
       <c r="G904" t="n">
-        <v>10.3677024841309</v>
+        <v>10.3677034378052</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G905" t="n">
-        <v>10.6892547607422</v>
+        <v>10.6892538070679</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>10.748969078064</v>
+        <v>10.7489700317383</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G907" t="n">
-        <v>10.6662864685059</v>
+        <v>10.6662855148315</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G909" t="n">
-        <v>10.5101041793823</v>
+        <v>10.510103225708</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G910" t="n">
-        <v>10.1701793670654</v>
+        <v>10.1701784133911</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G911" t="n">
-        <v>10.142617225647</v>
+        <v>10.1426162719727</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G912" t="n">
-        <v>10.2069282531738</v>
+        <v>10.2069292068481</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>10.7150001525879</v>
       </c>
       <c r="G913" t="n">
-        <v>9.84403514862061</v>
+        <v>9.84403610229492</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>10.4250001907349</v>
       </c>
       <c r="G914" t="n">
-        <v>9.57760906219482</v>
+        <v>9.57760810852051</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>10.25</v>
       </c>
       <c r="G915" t="n">
-        <v>9.41683197021484</v>
+        <v>9.41683387756348</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G916" t="n">
-        <v>9.49032878875732</v>
+        <v>9.49032974243164</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>9.58220291137695</v>
+        <v>9.58220100402832</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G918" t="n">
-        <v>9.16877841949463</v>
+        <v>9.16877937316895</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>10.0950002670288</v>
       </c>
       <c r="G922" t="n">
-        <v>9.27443313598633</v>
+        <v>9.27443218231201</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>9.34792900085449</v>
+        <v>9.34792995452881</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G925" t="n">
-        <v>9.46736335754395</v>
+        <v>9.46736240386963</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G926" t="n">
-        <v>9.30658721923828</v>
+        <v>9.30658626556396</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>9.99400043487549</v>
       </c>
       <c r="G927" t="n">
-        <v>9.18164157867432</v>
+        <v>9.18164253234863</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G928" t="n">
-        <v>9.21930885314941</v>
+        <v>9.2193078994751</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>10.3149995803833</v>
       </c>
       <c r="G929" t="n">
-        <v>9.47654914855957</v>
+        <v>9.47654819488525</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>11.1850004196167</v>
       </c>
       <c r="G931" t="n">
-        <v>10.2758321762085</v>
+        <v>10.2758331298828</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G934" t="n">
-        <v>10.1380252838135</v>
+        <v>10.1380243301392</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>11.25</v>
       </c>
       <c r="G935" t="n">
-        <v>10.3355474472046</v>
+        <v>10.3355484008789</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G936" t="n">
-        <v>10.3079872131348</v>
+        <v>10.3079862594604</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G939" t="n">
-        <v>10.5560398101807</v>
+        <v>10.5560388565063</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G941" t="n">
-        <v>10.7995004653931</v>
+        <v>10.7994995117188</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G942" t="n">
-        <v>10.9051523208618</v>
+        <v>10.9051513671875</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>10.4044504165649</v>
+        <v>10.4044513702393</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G946" t="n">
-        <v>10.2896118164062</v>
+        <v>10.2896137237549</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>10.1518058776855</v>
+        <v>10.1518049240112</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>10.8850002288818</v>
       </c>
       <c r="G948" t="n">
-        <v>10.0002183914185</v>
+        <v>10.0002174377441</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>10.7349996566772</v>
       </c>
       <c r="G950" t="n">
-        <v>9.86240863800049</v>
+        <v>9.8624095916748</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G951" t="n">
-        <v>9.9404993057251</v>
+        <v>9.94050121307373</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G952" t="n">
-        <v>9.9404993057251</v>
+        <v>9.94050121307373</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G953" t="n">
-        <v>9.91294002532959</v>
+        <v>9.91293811798096</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>10.664999961853</v>
       </c>
       <c r="G954" t="n">
-        <v>9.79809856414795</v>
+        <v>9.79809951782227</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G956" t="n">
-        <v>9.46736335754395</v>
+        <v>9.46736240386963</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>10.3450002670288</v>
       </c>
       <c r="G957" t="n">
-        <v>9.50411033630371</v>
+        <v>9.50411128997803</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>10.2950000762939</v>
       </c>
       <c r="G958" t="n">
-        <v>9.45817470550537</v>
+        <v>9.45817565917969</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>9.91600036621094</v>
       </c>
       <c r="G961" t="n">
-        <v>9.10998249053955</v>
+        <v>9.10998344421387</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>9.60057544708252</v>
+        <v>9.6005744934082</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G965" t="n">
-        <v>9.52707767486572</v>
+        <v>9.52707862854004</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G966" t="n">
-        <v>9.7291955947876</v>
+        <v>9.72919654846191</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>10.2449998855591</v>
       </c>
       <c r="G967" t="n">
-        <v>9.4122371673584</v>
+        <v>9.41224002838135</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G968" t="n">
-        <v>9.49032878875732</v>
+        <v>9.49032974243164</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G970" t="n">
-        <v>9.35711669921875</v>
+        <v>9.35711574554443</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>10.2950000762939</v>
       </c>
       <c r="G971" t="n">
-        <v>9.45817470550537</v>
+        <v>9.45817565917969</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G972" t="n">
-        <v>9.67407321929932</v>
+        <v>9.674072265625</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G973" t="n">
-        <v>9.76594352722168</v>
+        <v>9.76594257354736</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G974" t="n">
-        <v>9.72460269927979</v>
+        <v>9.72460174560547</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G979" t="n">
-        <v>10.0415592193604</v>
+        <v>10.0415601730347</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>11.2550001144409</v>
       </c>
       <c r="G982" t="n">
-        <v>10.3401412963867</v>
+        <v>10.340142250061</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G983" t="n">
-        <v>10.4320125579834</v>
+        <v>10.4320116043091</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>10.5192909240723</v>
+        <v>10.5192918777466</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>10.5192909240723</v>
+        <v>10.5192918777466</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G990" t="n">
-        <v>10.142617225647</v>
+        <v>10.1426162719727</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>10.8950004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>10.0094041824341</v>
+        <v>10.0094051361084</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G993" t="n">
-        <v>9.9404993057251</v>
+        <v>9.94050121307373</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G997" t="n">
-        <v>9.75216388702393</v>
+        <v>9.75216197967529</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>10.3649997711182</v>
       </c>
       <c r="G1000" t="n">
-        <v>9.52248382568359</v>
+        <v>9.52248477935791</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.66488647460938</v>
+        <v>9.66488552093506</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G1002" t="n">
-        <v>9.75216388702393</v>
+        <v>9.75216197967529</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1010" t="n">
-        <v>9.79350471496582</v>
+        <v>9.79350662231445</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1011" t="n">
-        <v>9.76594352722168</v>
+        <v>9.76594257354736</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>10.6549997329712</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.78891277313232</v>
+        <v>9.78891181945801</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.60057544708252</v>
+        <v>9.6005744934082</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>10.875</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.99102973937988</v>
+        <v>9.99102878570557</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>10.372296333313</v>
+        <v>10.3722982406616</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G1024" t="n">
-        <v>10.2069282531738</v>
+        <v>10.2069292068481</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1025" t="n">
-        <v>10.1609926223755</v>
+        <v>10.1609916687012</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>11</v>
       </c>
       <c r="G1026" t="n">
-        <v>10.1058702468872</v>
+        <v>10.1058692932129</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>10.2115201950073</v>
+        <v>10.2115211486816</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>11.085000038147</v>
       </c>
       <c r="G1028" t="n">
-        <v>10.1839599609375</v>
+        <v>10.1839590072632</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>10.9849996566772</v>
       </c>
       <c r="G1029" t="n">
-        <v>10.0920886993408</v>
+        <v>10.0920877456665</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>10.9650001525879</v>
       </c>
       <c r="G1030" t="n">
-        <v>10.0737142562866</v>
+        <v>10.0737133026123</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G1031" t="n">
-        <v>10.0231857299805</v>
+        <v>10.0231847763062</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G1036" t="n">
-        <v>10.0783071517944</v>
+        <v>10.0783081054688</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1037" t="n">
-        <v>10.2712383270264</v>
+        <v>10.2712392807007</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>11.5</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.5652275085449</v>
+        <v>10.5652265548706</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.5514469146729</v>
+        <v>10.5514450073242</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.8592157363892</v>
+        <v>10.8592138290405</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1044" t="n">
-        <v>10.6846599578857</v>
+        <v>10.6846609115601</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>11.7550001144409</v>
       </c>
       <c r="G1045" t="n">
-        <v>10.7995004653931</v>
+        <v>10.7994995117188</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.6892547607422</v>
+        <v>10.6892538070679</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1049" t="n">
-        <v>10.464168548584</v>
+        <v>10.4641675949097</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>11.2550001144409</v>
       </c>
       <c r="G1050" t="n">
-        <v>10.3401412963867</v>
+        <v>10.340142250061</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>10.1518058776855</v>
+        <v>10.1518049240112</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.45358180999756</v>
+        <v>9.45358085632324</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>10</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.18715381622314</v>
+        <v>9.18715286254883</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1057" t="n">
-        <v>8.48709297180176</v>
+        <v>8.48709201812744</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>8.79800033569336</v>
       </c>
       <c r="G1060" t="n">
-        <v>8.08285713195801</v>
+        <v>8.08285903930664</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1063" t="n">
-        <v>6.90873956680298</v>
+        <v>6.90874004364014</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>7.56799983978271</v>
       </c>
       <c r="G1064" t="n">
-        <v>6.95283699035645</v>
+        <v>6.95283842086792</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.38600015640259</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.78563261032104</v>
+        <v>6.78563213348389</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>5.75</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.28261375427246</v>
+        <v>5.2826132774353</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1068" t="n">
-        <v>4.9096155166626</v>
+        <v>4.90961503982544</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G1069" t="n">
-        <v>4.79385662078857</v>
+        <v>4.79385709762573</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.33541822433472</v>
+        <v>4.33541774749756</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G1071" t="n">
-        <v>4.37859678268433</v>
+        <v>4.37859725952148</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>6.19600009918213</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.69235992431641</v>
+        <v>5.69236040115356</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.5490403175354</v>
+        <v>5.54904079437256</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>6.31400012969971</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.80076932907104</v>
+        <v>5.80076837539673</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.39425897598267</v>
+        <v>6.39425945281982</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.5688157081604</v>
+        <v>6.56881523132324</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.50818014144897</v>
+        <v>6.50817966461182</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>6.66200017929077</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.12048292160034</v>
+        <v>6.12048196792603</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>6.57600021362305</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.04147243499756</v>
+        <v>6.04147291183472</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.69603538513184</v>
+        <v>5.69603586196899</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.64642477035522</v>
+        <v>5.64642429351807</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.61702537536621</v>
+        <v>5.61702585220337</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>6.44600009918213</v>
       </c>
       <c r="G1098" t="n">
-        <v>5.92203950881958</v>
+        <v>5.92203903198242</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>6.29400014877319</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.78239488601685</v>
+        <v>5.78239440917969</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>6</v>
       </c>
       <c r="G1100" t="n">
-        <v>5.51229190826416</v>
+        <v>5.51229238510132</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.40755844116211</v>
+        <v>5.40755891799927</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>6</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.51229190826416</v>
+        <v>5.51229238510132</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.50310516357422</v>
+        <v>5.50310468673706</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.42960786819458</v>
+        <v>5.42960691452026</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.42042112350464</v>
+        <v>5.42042064666748</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.39200019836426</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.95371341705322</v>
+        <v>4.95371294021606</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.99781227111816</v>
+        <v>4.99781179428101</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.81958055496216</v>
+        <v>4.81958103179932</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.76078319549561</v>
+        <v>4.76078367233276</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.04374742507935</v>
+        <v>5.04374694824219</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.71199989318848</v>
       </c>
       <c r="G1117" t="n">
-        <v>5.24770212173462</v>
+        <v>5.24770259857178</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.3561110496521</v>
+        <v>5.35611057281494</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1119" t="n">
-        <v>5.14480590820312</v>
+        <v>5.14480686187744</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>5.91200017929077</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.43144559860229</v>
+        <v>5.43144512176514</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.50450420379639</v>
+        <v>6.50450563430786</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>7.14200019836426</v>
       </c>
       <c r="G1125" t="n">
-        <v>6.56146574020386</v>
+        <v>6.5614652633667</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>6.19600009918213</v>
       </c>
       <c r="G1129" t="n">
-        <v>5.69235992431641</v>
+        <v>5.69236040115356</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1131" t="n">
-        <v>6.01207304000854</v>
+        <v>6.0120735168457</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>6.23400020599365</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.85474634170532</v>
+        <v>5.85474681854248</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.49410724639893</v>
+        <v>5.49410772323608</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.62183380126953</v>
+        <v>5.62183332443237</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.91200017929077</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.5523362159729</v>
+        <v>5.55233573913574</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1155" t="n">
-        <v>6.0576057434082</v>
+        <v>6.05760622024536</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>6.22200012207031</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.84347677230835</v>
+        <v>5.84347629547119</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G1158" t="n">
-        <v>5.80590963363647</v>
+        <v>5.80591011047363</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.53355312347412</v>
+        <v>5.53355264663696</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1164" t="n">
-        <v>5.08087491989136</v>
+        <v>5.08087539672852</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.20108842849731</v>
+        <v>5.20108890533447</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.52979564666748</v>
+        <v>5.52979612350464</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.64249467849731</v>
+        <v>5.64249515533447</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.62183380126953</v>
+        <v>5.62183332443237</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G1185" t="n">
-        <v>5.32318019866943</v>
+        <v>5.32318067550659</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.18042755126953</v>
+        <v>5.18042707443237</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.13534736633301</v>
+        <v>5.13534688949585</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.18042755126953</v>
+        <v>5.18042707443237</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.23865556716919</v>
+        <v>5.23865509033203</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>5.1560001373291</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.8423285484314</v>
+        <v>4.84232807159424</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>5</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.69581842422485</v>
+        <v>4.69581890106201</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>5</v>
       </c>
       <c r="G1207" t="n">
-        <v>4.69581842422485</v>
+        <v>4.69581890106201</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.58124017715454</v>
+        <v>4.5812406539917</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.91558313369751</v>
+        <v>4.91558265686035</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.78973531723022</v>
+        <v>4.78973484039307</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.47417593002319</v>
+        <v>4.47417640686035</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.40186023712158</v>
+        <v>4.40185976028442</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.4760537147522</v>
+        <v>4.47605419158936</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>4.42700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.1576771736145</v>
+        <v>4.15767765045166</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.98393297195435</v>
+        <v>3.98393249511719</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.39340782165527</v>
+        <v>4.39340734481812</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.07597064971924</v>
+        <v>4.0759711265564</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1240" t="n">
-        <v>5.32881498336792</v>
+        <v>5.32881450653076</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1248" t="n">
-        <v>5.71762800216675</v>
+        <v>5.71762847900391</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.62183380126953</v>
+        <v>5.62183332443237</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>6.08599996566772</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.71575021743774</v>
+        <v>5.7157506942749</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1253" t="n">
-        <v>5.94490623474121</v>
+        <v>5.94490671157837</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.14213132858276</v>
+        <v>6.14213085174561</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>6.33199977874756</v>
       </c>
       <c r="G1256" t="n">
-        <v>5.94678449630737</v>
+        <v>5.94678401947021</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1257" t="n">
-        <v>5.94490623474121</v>
+        <v>5.94490671157837</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1260" t="n">
-        <v>5.49598550796509</v>
+        <v>5.49598598480225</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.86399984359741</v>
       </c>
       <c r="G1263" t="n">
-        <v>5.50725650787354</v>
+        <v>5.50725603103638</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G1266" t="n">
-        <v>5.40206956863403</v>
+        <v>5.40206909179688</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G1268" t="n">
-        <v>5.56172752380371</v>
+        <v>5.56172800064087</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>5.61619853973389</v>
+        <v>5.61619901657104</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.55045747756958</v>
+        <v>5.55045700073242</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.64437389373779</v>
+        <v>5.64437437057495</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1278" t="n">
-        <v>5.51289081573486</v>
+        <v>5.51289129257202</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G1279" t="n">
-        <v>5.5542140007019</v>
+        <v>5.55421447753906</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1284" t="n">
-        <v>5.50913429260254</v>
+        <v>5.5091347694397</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1285" t="n">
-        <v>5.30627536773682</v>
+        <v>5.30627584457397</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.15225267410278</v>
+        <v>5.15225219726562</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1288" t="n">
-        <v>5.33444929122925</v>
+        <v>5.33444976806641</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>5.81799983978271</v>
       </c>
       <c r="G1292" t="n">
-        <v>5.46405458450317</v>
+        <v>5.46405410766602</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.54482221603394</v>
+        <v>5.54482269287109</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G1294" t="n">
-        <v>5.63686084747314</v>
+        <v>5.63686037063599</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>6.66200017929077</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.25670957565308</v>
+        <v>6.25670909881592</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G1314" t="n">
-        <v>6.46896028518677</v>
+        <v>6.46895980834961</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.48022985458374</v>
+        <v>6.48022937774658</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1317" t="n">
-        <v>6.65867137908936</v>
+        <v>6.6586709022522</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>6.98737764358521</v>
+        <v>6.98737812042236</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1320" t="n">
-        <v>6.97798633575439</v>
+        <v>6.97798681259155</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>7.57200002670288</v>
       </c>
       <c r="G1325" t="n">
-        <v>7.11134767532349</v>
+        <v>7.11134815216064</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G1326" t="n">
-        <v>6.97798633575439</v>
+        <v>6.97798681259155</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G1327" t="n">
-        <v>6.87467813491821</v>
+        <v>6.87467861175537</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>6.87400007247925</v>
       </c>
       <c r="G1328" t="n">
-        <v>6.45581102371216</v>
+        <v>6.45581150054932</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1330" t="n">
-        <v>6.38631296157837</v>
+        <v>6.38631343841553</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1338" t="n">
-        <v>6.63988780975342</v>
+        <v>6.63988733291626</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G1345" t="n">
-        <v>6.45393371582031</v>
+        <v>6.45393323898315</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>6.64400005340576</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.23980379104614</v>
+        <v>6.23980331420898</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>6.79400014877319</v>
       </c>
       <c r="G1353" t="n">
-        <v>6.38067865371704</v>
+        <v>6.38067817687988</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>6.87599992752075</v>
       </c>
       <c r="G1354" t="n">
-        <v>6.45768928527832</v>
+        <v>6.45768976211548</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G1355" t="n">
-        <v>6.4407844543457</v>
+        <v>6.44078493118286</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1359" t="n">
-        <v>6.54597091674805</v>
+        <v>6.54597139358521</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>6.82600021362305</v>
       </c>
       <c r="G1367" t="n">
-        <v>6.41073131561279</v>
+        <v>6.41073179244995</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>6.89400005340576</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.4745945930481</v>
+        <v>6.47459506988525</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.67745399475098</v>
+        <v>6.67745447158813</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.76761293411255</v>
+        <v>6.76761341094971</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.7206563949585</v>
+        <v>6.72065591812134</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>6.99200010299683</v>
       </c>
       <c r="G1390" t="n">
-        <v>6.56663274765015</v>
+        <v>6.56663227081299</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G1393" t="n">
-        <v>6.54784917831421</v>
+        <v>6.54784965515137</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>6.85799980163574</v>
       </c>
       <c r="G1395" t="n">
-        <v>6.4407844543457</v>
+        <v>6.44078493118286</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1397" t="n">
-        <v>6.54597091674805</v>
+        <v>6.54597139358521</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>6.77600002288818</v>
       </c>
       <c r="G1403" t="n">
-        <v>6.36377382278442</v>
+        <v>6.36377334594727</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.32800006866455</v>
       </c>
       <c r="G1408" t="n">
-        <v>5.94302797317505</v>
+        <v>5.94302845001221</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>6.31599998474121</v>
       </c>
       <c r="G1412" t="n">
-        <v>5.93175840377808</v>
+        <v>5.93175792694092</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.14588689804077</v>
+        <v>6.14588737487793</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>6.63600015640259</v>
       </c>
       <c r="G1418" t="n">
-        <v>6.23229074478149</v>
+        <v>6.23229026794434</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>6.63600015640259</v>
       </c>
       <c r="G1420" t="n">
-        <v>6.23229074478149</v>
+        <v>6.23229026794434</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>7.01200008392334</v>
       </c>
       <c r="G1428" t="n">
-        <v>6.58541584014893</v>
+        <v>6.58541536331177</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G1432" t="n">
-        <v>6.34686851501465</v>
+        <v>6.34686803817749</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1437" t="n">
-        <v>6.45205497741699</v>
+        <v>6.45205450057983</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G1443" t="n">
-        <v>6.53470087051392</v>
+        <v>6.53470039367676</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>7.00799989700317</v>
       </c>
       <c r="G1445" t="n">
-        <v>6.5816593170166</v>
+        <v>6.58165979385376</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1446" t="n">
-        <v>6.49901294708252</v>
+        <v>6.49901247024536</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.48022985458374</v>
+        <v>6.48022937774658</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>6.77799987792969</v>
       </c>
       <c r="G1448" t="n">
-        <v>6.36565160751343</v>
+        <v>6.36565113067627</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.45393371582031</v>
+        <v>6.45393323898315</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>6.64599990844727</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.2416820526123</v>
+        <v>6.24168157577515</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.44266271591187</v>
+        <v>6.44266319274902</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>6.44266271591187</v>
+        <v>6.44266319274902</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>7.12799978256226</v>
       </c>
       <c r="G1467" t="n">
-        <v>6.69435882568359</v>
+        <v>6.69435930252075</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>6.62400007247925</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.22102022171021</v>
+        <v>6.22102069854736</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1478" t="n">
-        <v>6.14588689804077</v>
+        <v>6.14588737487793</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.13649606704712</v>
+        <v>6.13649559020996</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>6.56400012969971</v>
       </c>
       <c r="G1480" t="n">
-        <v>6.16467046737671</v>
+        <v>6.16467094421387</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>6.33799982070923</v>
       </c>
       <c r="G1483" t="n">
-        <v>5.95241928100586</v>
+        <v>5.95241975784302</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.04257917404175</v>
+        <v>6.04257965087891</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.0576057434082</v>
+        <v>6.05760622024536</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>6.5479998588562</v>
       </c>
       <c r="G1490" t="n">
-        <v>6.14964389801025</v>
+        <v>6.14964437484741</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>6.62799978256226</v>
       </c>
       <c r="G1491" t="n">
-        <v>6.22477722167969</v>
+        <v>6.22477674484253</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>6.5479998588562</v>
       </c>
       <c r="G1494" t="n">
-        <v>6.14964389801025</v>
+        <v>6.14964437484741</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>6.41800022125244</v>
       </c>
       <c r="G1497" t="n">
-        <v>6.02755260467529</v>
+        <v>6.02755308151245</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>6.19399976730347</v>
       </c>
       <c r="G1498" t="n">
-        <v>5.81718015670776</v>
+        <v>5.81717967987061</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1499" t="n">
-        <v>5.83220720291138</v>
+        <v>5.83220672607422</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.96556854248047</v>
+        <v>5.96556806564331</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1512" t="n">
-        <v>5.66879224777222</v>
+        <v>5.66879272460938</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>5.9980001449585</v>
       </c>
       <c r="G1513" t="n">
-        <v>5.63310432434082</v>
+        <v>5.63310480117798</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G1514" t="n">
-        <v>5.52979564666748</v>
+        <v>5.52979612350464</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G1528" t="n">
-        <v>6.04257917404175</v>
+        <v>6.04257965087891</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1531" t="n">
-        <v>5.96368980407715</v>
+        <v>5.96368932723999</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>6.63600015640259</v>
       </c>
       <c r="G1535" t="n">
-        <v>6.23229074478149</v>
+        <v>6.23229026794434</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>6.77799987792969</v>
       </c>
       <c r="G1537" t="n">
-        <v>6.36565160751343</v>
+        <v>6.36565113067627</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1541" t="n">
-        <v>6.38631296157837</v>
+        <v>6.38631343841553</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G1544" t="n">
-        <v>5.95054149627686</v>
+        <v>5.9505410194397</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G1550" t="n">
-        <v>5.95993328094482</v>
+        <v>5.95993375778198</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>6.08199977874756</v>
       </c>
       <c r="G1552" t="n">
-        <v>5.71199369430542</v>
+        <v>5.71199321746826</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>6.31599998474121</v>
       </c>
       <c r="G1554" t="n">
-        <v>5.93175840377808</v>
+        <v>5.93175792694092</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1556" t="n">
-        <v>6.13273859024048</v>
+        <v>6.13273906707764</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>6.46199989318848</v>
       </c>
       <c r="G1557" t="n">
-        <v>6.06887578964233</v>
+        <v>6.06887531280518</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1558" t="n">
-        <v>6.36752986907959</v>
+        <v>6.36753034591675</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>6.64599990844727</v>
       </c>
       <c r="G1560" t="n">
-        <v>6.2416820526123</v>
+        <v>6.24168157577515</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>6.67799997329712</v>
       </c>
       <c r="G1565" t="n">
-        <v>6.27173471450806</v>
+        <v>6.27173519134521</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>8.11600017547607</v>
       </c>
       <c r="G1568" t="n">
-        <v>7.62225294113159</v>
+        <v>7.62225246429443</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>7.98400020599365</v>
       </c>
       <c r="G1570" t="n">
-        <v>7.49828338623047</v>
+        <v>7.49828290939331</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>8.06799983978271</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.57717323303223</v>
+        <v>7.57717275619507</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>9.13199996948242</v>
       </c>
       <c r="G1576" t="n">
-        <v>8.57644271850586</v>
+        <v>8.57644367218018</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>8.68400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>8.1556978225708</v>
+        <v>8.15569877624512</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>9.05399990081787</v>
       </c>
       <c r="G1583" t="n">
-        <v>8.50318813323975</v>
+        <v>8.50318717956543</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>9.29399967193604</v>
       </c>
       <c r="G1584" t="n">
-        <v>8.72858619689941</v>
+        <v>8.72858715057373</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1588" t="n">
-        <v>8.42430019378662</v>
+        <v>8.4242992401123</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G1592" t="n">
-        <v>8.76239776611328</v>
+        <v>8.7623987197876</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>9.48799991607666</v>
       </c>
       <c r="G1597" t="n">
-        <v>8.91078567504883</v>
+        <v>8.91078472137451</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>10.1549997329712</v>
       </c>
       <c r="G1602" t="n">
-        <v>9.53720760345459</v>
+        <v>9.53720664978027</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G1616" t="n">
-        <v>9.0479040145874</v>
+        <v>9.04790306091309</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G1618" t="n">
-        <v>8.95586490631104</v>
+        <v>8.95586585998535</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.99718856811523</v>
+        <v>8.99718761444092</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>9.85400009155273</v>
       </c>
       <c r="G1622" t="n">
-        <v>9.25452041625977</v>
+        <v>9.25451946258545</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>10.25</v>
       </c>
       <c r="G1630" t="n">
-        <v>9.62642765045166</v>
+        <v>9.62642860412598</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1633" t="n">
-        <v>9.59355735778809</v>
+        <v>9.5935583114624</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G1634" t="n">
-        <v>9.78139114379883</v>
+        <v>9.78139019012451</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>10.0490503311157</v>
+        <v>10.04905128479</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1638" t="n">
-        <v>9.83304500579834</v>
+        <v>9.83304595947266</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>9.82800006866455</v>
       </c>
       <c r="G1642" t="n">
-        <v>9.23010063171387</v>
+        <v>9.23010158538818</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>9.70199966430664</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.11176586151123</v>
+        <v>9.11176681518555</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1880" t="n">
-        <v>10.8073101043701</v>
+        <v>10.8073110580444</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1882" t="n">
-        <v>10.1029062271118</v>
+        <v>10.1029052734375</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1883" t="n">
-        <v>10.1222047805786</v>
+        <v>10.1222038269043</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G1884" t="n">
-        <v>10.2379961013794</v>
+        <v>10.2379970550537</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1885" t="n">
-        <v>10.2669458389282</v>
+        <v>10.2669448852539</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1887" t="n">
-        <v>9.67833137512207</v>
+        <v>9.6783332824707</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G1891" t="n">
-        <v>9.87131977081299</v>
+        <v>9.87131881713867</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>10.4849996566772</v>
       </c>
       <c r="G1896" t="n">
-        <v>10.1173791885376</v>
+        <v>10.1173782348633</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>10.5</v>
       </c>
       <c r="G1899" t="n">
-        <v>10.1318531036377</v>
+        <v>10.131854057312</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G1902" t="n">
-        <v>10.2428207397461</v>
+        <v>10.2428216934204</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1903" t="n">
-        <v>10.276593208313</v>
+        <v>10.2765941619873</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>10.6750001907349</v>
       </c>
       <c r="G1904" t="n">
-        <v>10.3007173538208</v>
+        <v>10.3007183074951</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>10.5249996185303</v>
       </c>
       <c r="G1912" t="n">
-        <v>10.1559762954712</v>
+        <v>10.1559772491455</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>10.6450004577637</v>
       </c>
       <c r="G1914" t="n">
-        <v>10.2717695236206</v>
+        <v>10.2717704772949</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1917" t="n">
-        <v>10.8652076721191</v>
+        <v>10.8652067184448</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1918" t="n">
-        <v>10.9038047790527</v>
+        <v>10.9038038253784</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1920" t="n">
-        <v>11.1739873886108</v>
+        <v>11.1739864349365</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G1921" t="n">
-        <v>11.4152221679688</v>
+        <v>11.4152212142944</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50367,7 +50367,7 @@
         <v>11.7150001525879</v>
       </c>
       <c r="G1923" t="n">
-        <v>11.304253578186</v>
+        <v>11.3042545318604</v>
       </c>
       <c r="H1923" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>11.5150003433228</v>
       </c>
       <c r="G1924" t="n">
-        <v>11.1112670898438</v>
+        <v>11.1112661361694</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G1925" t="n">
-        <v>11.1691627502441</v>
+        <v>11.1691617965698</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>11.5749998092651</v>
       </c>
       <c r="G1927" t="n">
-        <v>11.1691627502441</v>
+        <v>11.1691617965698</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G1929" t="n">
-        <v>11.4634675979614</v>
+        <v>11.4634685516357</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>12.3149995803833</v>
       </c>
       <c r="G1930" t="n">
-        <v>11.8832168579102</v>
+        <v>11.8832159042358</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1932" t="n">
-        <v>12.1196269989014</v>
+        <v>12.1196260452271</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G1939" t="n">
-        <v>12.722713470459</v>
+        <v>12.7227144241333</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>12.8149995803833</v>
       </c>
       <c r="G1942" t="n">
-        <v>12.3656854629517</v>
+        <v>12.365686416626</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G1943" t="n">
-        <v>12.3801593780518</v>
+        <v>12.3801603317261</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1950" t="n">
-        <v>12.6503429412842</v>
+        <v>12.6503419876099</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>13.25</v>
       </c>
       <c r="G1951" t="n">
-        <v>12.7854347229004</v>
+        <v>12.7854337692261</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>13.3149995803833</v>
       </c>
       <c r="G1952" t="n">
-        <v>12.8481540679932</v>
+        <v>12.8481550216675</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>13.3149995803833</v>
       </c>
       <c r="G1953" t="n">
-        <v>12.8481540679932</v>
+        <v>12.8481550216675</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>13.375</v>
       </c>
       <c r="G1954" t="n">
-        <v>12.9060506820679</v>
+        <v>12.9060516357422</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1957" t="n">
-        <v>13.3740453720093</v>
+        <v>13.3740472793579</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G1958" t="n">
-        <v>13.2582530975342</v>
+        <v>13.2582540512085</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1959" t="n">
-        <v>13.3740453720093</v>
+        <v>13.3740472793579</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G1962" t="n">
-        <v>13.282377243042</v>
+        <v>13.2823781967163</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G1963" t="n">
-        <v>13.4898386001587</v>
+        <v>13.489839553833</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G1964" t="n">
-        <v>13.3740453720093</v>
+        <v>13.3740472793579</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G1966" t="n">
-        <v>13.5380868911743</v>
+        <v>13.5380859375</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>13.6750001907349</v>
       </c>
       <c r="G1971" t="n">
-        <v>13.1955327987671</v>
+        <v>13.1955337524414</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51745,7 +51745,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1976" t="n">
-        <v>12.7371864318848</v>
+        <v>12.7371873855591</v>
       </c>
       <c r="H1976" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1979" t="n">
-        <v>13.084566116333</v>
+        <v>13.0845651626587</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51979,7 +51979,7 @@
         <v>14.3950004577637</v>
       </c>
       <c r="G1985" t="n">
-        <v>13.8902893066406</v>
+        <v>13.8902883529663</v>
       </c>
       <c r="H1985" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G1986" t="n">
-        <v>13.846866607666</v>
+        <v>13.8468675613403</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52057,7 +52057,7 @@
         <v>13.8649997711182</v>
       </c>
       <c r="G1988" t="n">
-        <v>13.3788709640503</v>
+        <v>13.3788719177246</v>
       </c>
       <c r="H1988" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>13.6750001907349</v>
       </c>
       <c r="G1989" t="n">
-        <v>13.1955327987671</v>
+        <v>13.1955337524414</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G1993" t="n">
-        <v>13.3643980026245</v>
+        <v>13.3643970489502</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52291,7 +52291,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1997" t="n">
-        <v>13.9144124984741</v>
+        <v>13.9144115447998</v>
       </c>
       <c r="H1997" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G1999" t="n">
-        <v>13.7069501876831</v>
+        <v>13.7069511413574</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G2002" t="n">
-        <v>13.7069501876831</v>
+        <v>13.7069511413574</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G2003" t="n">
-        <v>14.3486337661743</v>
+        <v>14.3486347198486</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>14.3950004577637</v>
       </c>
       <c r="G2005" t="n">
-        <v>13.8902893066406</v>
+        <v>13.8902883529663</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G2006" t="n">
-        <v>13.8516902923584</v>
+        <v>13.8516912460327</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>14.6549997329712</v>
       </c>
       <c r="G2008" t="n">
-        <v>14.1411714553833</v>
+        <v>14.1411724090576</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G2009" t="n">
-        <v>14.3968820571899</v>
+        <v>14.3968811035156</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G2010" t="n">
-        <v>14.1508226394653</v>
+        <v>14.150821685791</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G2011" t="n">
-        <v>13.8854646682739</v>
+        <v>13.8854637145996</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52733,7 +52733,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G2014" t="n">
-        <v>13.5187873840332</v>
+        <v>13.5187883377075</v>
       </c>
       <c r="H2014" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G2015" t="n">
-        <v>13.6731767654419</v>
+        <v>13.6731777191162</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G2017" t="n">
-        <v>13.5766839981079</v>
+        <v>13.5766830444336</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2022" t="n">
-        <v>13.1038646697998</v>
+        <v>13.1038637161255</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G2023" t="n">
-        <v>13.3643980026245</v>
+        <v>13.3643970489502</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G2024" t="n">
-        <v>13.3306245803833</v>
+        <v>13.330623626709</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G2025" t="n">
-        <v>13.3547468185425</v>
+        <v>13.3547477722168</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G2026" t="n">
-        <v>13.9240617752075</v>
+        <v>13.9240608215332</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G2027" t="n">
-        <v>13.9288864135742</v>
+        <v>13.9288854598999</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G2029" t="n">
-        <v>14.0495042800903</v>
+        <v>14.049503326416</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2031" t="n">
-        <v>14.1073999404907</v>
+        <v>14.1073989868164</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>14.6850004196167</v>
       </c>
       <c r="G2032" t="n">
-        <v>14.1701211929321</v>
+        <v>14.1701221466064</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>14.75</v>
       </c>
       <c r="G2033" t="n">
-        <v>14.2328424453735</v>
+        <v>14.2328414916992</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>15.4449996948242</v>
       </c>
       <c r="G2038" t="n">
-        <v>14.9034738540649</v>
+        <v>14.9034729003906</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G2039" t="n">
-        <v>15.7574443817139</v>
+        <v>15.7574434280396</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G2041" t="n">
-        <v>15.7960433959961</v>
+        <v>15.7960443496704</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G2043" t="n">
-        <v>16.0517501831055</v>
+        <v>16.0517520904541</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G2045" t="n">
-        <v>16.6693096160889</v>
+        <v>16.6693115234375</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>17.0949993133545</v>
       </c>
       <c r="G2047" t="n">
-        <v>16.4956207275391</v>
+        <v>16.4956226348877</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G2050" t="n">
-        <v>15.8635873794556</v>
+        <v>15.8635892868042</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>16.5</v>
       </c>
       <c r="G2051" t="n">
-        <v>15.9214839935303</v>
+        <v>15.921483039856</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G2053" t="n">
-        <v>15.7863931655884</v>
+        <v>15.7863941192627</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G2054" t="n">
-        <v>15.824990272522</v>
+        <v>15.8249912261963</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G2057" t="n">
-        <v>15.6657762527466</v>
+        <v>15.6657752990723</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>16.0149993896484</v>
       </c>
       <c r="G2059" t="n">
-        <v>15.4534873962402</v>
+        <v>15.4534883499146</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G2062" t="n">
-        <v>16.2592144012451</v>
+        <v>16.2592124938965</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G2063" t="n">
-        <v>16.0806980133057</v>
+        <v>16.0806999206543</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>17.2049999237061</v>
       </c>
       <c r="G2066" t="n">
-        <v>16.6017665863037</v>
+        <v>16.6017646789551</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54215,7 +54215,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G2071" t="n">
-        <v>18.5171699523926</v>
+        <v>18.5171680450439</v>
       </c>
       <c r="H2071" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G2073" t="n">
-        <v>18.3627777099609</v>
+        <v>18.3627796173096</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G2074" t="n">
-        <v>18.4110240936279</v>
+        <v>18.4110260009766</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54397,7 +54397,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G2078" t="n">
-        <v>18.9513893127441</v>
+        <v>18.9513912200928</v>
       </c>
       <c r="H2078" t="s">
         <v>8</v>
@@ -54501,7 +54501,7 @@
         <v>20.7099990844727</v>
       </c>
       <c r="G2082" t="n">
-        <v>19.9838752746582</v>
+        <v>19.9838733673096</v>
       </c>
       <c r="H2082" t="s">
         <v>8</v>
@@ -54579,7 +54579,7 @@
         <v>20.6900005340576</v>
       </c>
       <c r="G2085" t="n">
-        <v>19.9645748138428</v>
+        <v>19.9645767211914</v>
       </c>
       <c r="H2085" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G2090" t="n">
-        <v>20.5338916778564</v>
+        <v>20.5338897705078</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G2093" t="n">
-        <v>21.4409332275391</v>
+        <v>21.4409313201904</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G2102" t="n">
-        <v>22.2707786560059</v>
+        <v>22.2707805633545</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55047,7 +55047,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G2103" t="n">
-        <v>22.4541187286377</v>
+        <v>22.4541168212891</v>
       </c>
       <c r="H2103" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>21.5799999237061</v>
       </c>
       <c r="G2105" t="n">
-        <v>20.823371887207</v>
+        <v>20.8233699798584</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55177,7 +55177,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G2108" t="n">
-        <v>21.3444385528564</v>
+        <v>21.3444366455078</v>
       </c>
       <c r="H2108" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G2109" t="n">
-        <v>21.836555480957</v>
+        <v>21.8365573883057</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>21.9699993133545</v>
       </c>
       <c r="G2112" t="n">
-        <v>21.1996955871582</v>
+        <v>21.1996974945068</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G2115" t="n">
-        <v>21.4505786895752</v>
+        <v>21.4505805969238</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>21.4200000762939</v>
       </c>
       <c r="G2117" t="n">
-        <v>20.6689796447754</v>
+        <v>20.668981552124</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>21.5300006866455</v>
       </c>
       <c r="G2121" t="n">
-        <v>20.7751235961914</v>
+        <v>20.77512550354</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>22.4599990844727</v>
       </c>
       <c r="G2123" t="n">
-        <v>21.6725177764893</v>
+        <v>21.6725158691406</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>21.9300003051758</v>
       </c>
       <c r="G2129" t="n">
-        <v>21.1610984802246</v>
+        <v>21.1611003875732</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55749,7 +55749,7 @@
         <v>22.5</v>
       </c>
       <c r="G2130" t="n">
-        <v>21.7111148834229</v>
+        <v>21.7111129760742</v>
       </c>
       <c r="H2130" t="s">
         <v>8</v>
@@ -55853,7 +55853,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2134" t="n">
-        <v>22.5795574188232</v>
+        <v>22.5795593261719</v>
       </c>
       <c r="H2134" t="s">
         <v>8</v>
@@ -55931,7 +55931,7 @@
         <v>23.4699993133545</v>
       </c>
       <c r="G2137" t="n">
-        <v>22.6471042633057</v>
+        <v>22.647102355957</v>
       </c>
       <c r="H2137" t="s">
         <v>8</v>
@@ -55957,7 +55957,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2138" t="n">
-        <v>22.9655323028564</v>
+        <v>22.9655342102051</v>
       </c>
       <c r="H2138" t="s">
         <v>8</v>
@@ -55983,7 +55983,7 @@
         <v>23.5300006866455</v>
       </c>
       <c r="G2139" t="n">
-        <v>22.7050018310547</v>
+        <v>22.7049999237061</v>
       </c>
       <c r="H2139" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>23.0900001525879</v>
       </c>
       <c r="G2141" t="n">
-        <v>22.2804279327393</v>
+        <v>22.2804298400879</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56087,7 +56087,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G2143" t="n">
-        <v>23.2936134338379</v>
+        <v>23.2936115264893</v>
       </c>
       <c r="H2143" t="s">
         <v>8</v>
@@ -56139,7 +56139,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2145" t="n">
-        <v>22.9655323028564</v>
+        <v>22.9655342102051</v>
       </c>
       <c r="H2145" t="s">
         <v>8</v>
@@ -56191,7 +56191,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G2147" t="n">
-        <v>23.3225631713867</v>
+        <v>23.3225612640381</v>
       </c>
       <c r="H2147" t="s">
         <v>8</v>
@@ -56243,7 +56243,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G2149" t="n">
-        <v>22.4927139282227</v>
+        <v>22.4927158355713</v>
       </c>
       <c r="H2149" t="s">
         <v>8</v>
@@ -56347,7 +56347,7 @@
         <v>21.7900009155273</v>
       </c>
       <c r="G2153" t="n">
-        <v>21.0260105133057</v>
+        <v>21.026008605957</v>
       </c>
       <c r="H2153" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>22.4099998474121</v>
       </c>
       <c r="G2154" t="n">
-        <v>21.6242694854736</v>
+        <v>21.6242713928223</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56425,7 +56425,7 @@
         <v>22.8400001525879</v>
       </c>
       <c r="G2156" t="n">
-        <v>22.0391941070557</v>
+        <v>22.039192199707</v>
       </c>
       <c r="H2156" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>49.185001373291</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>1525231</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>49.9599990844727</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>48.3899993896484</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>49.2700004577637</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>49</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>49</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>47.3899993896484</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>48.2999992370605</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2613517</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>48.4049987792969</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>46.5849990844727</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>48.1599998474121</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>48.1599998474121</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>47.2200012207031</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1644628</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>47.4900016784668</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>46.0050010681152</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>47.1500015258789</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>47.1500015258789</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>46.0050010681152</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1623920</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>46.3800010681152</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>45.2799987792969</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>45.9150009155273</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>45.9150009155273</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>45.7999992370605</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1521411</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>46.814998626709</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>45.6199989318848</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>45.6599998474121</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>1278971</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>47.6399993896484</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>46.3849983215332</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>46.5699996948242</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>47.6399993896484</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LDO.MI.xlsx
+++ b/data/LDO.MI.xlsx
@@ -427,7 +427,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G2" t="n">
-        <v>10.93141746521</v>
+        <v>10.9314184188843</v>
       </c>
       <c r="H2" t="n">
         <v>3029330</v>
@@ -456,7 +456,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3644332885742</v>
+        <v>11.3644323348999</v>
       </c>
       <c r="H3" t="n">
         <v>2590152</v>
@@ -514,7 +514,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G5" t="n">
-        <v>11.0904836654663</v>
+        <v>11.0904855728149</v>
       </c>
       <c r="H5" t="n">
         <v>3547508</v>
@@ -572,7 +572,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G7" t="n">
-        <v>11.0021152496338</v>
+        <v>11.0021142959595</v>
       </c>
       <c r="H7" t="n">
         <v>2083558</v>
@@ -601,7 +601,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G8" t="n">
-        <v>11.1258354187012</v>
+        <v>11.1258335113525</v>
       </c>
       <c r="H8" t="n">
         <v>2648260</v>
@@ -630,7 +630,7 @@
         <v>12.6899995803833</v>
       </c>
       <c r="G9" t="n">
-        <v>11.2142019271851</v>
+        <v>11.2142028808594</v>
       </c>
       <c r="H9" t="n">
         <v>2658365</v>
@@ -659,7 +659,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G10" t="n">
-        <v>10.7104921340942</v>
+        <v>10.7104940414429</v>
       </c>
       <c r="H10" t="n">
         <v>3511227</v>
@@ -688,7 +688,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1979427337646</v>
+        <v>10.1979455947876</v>
       </c>
       <c r="H11" t="n">
         <v>6827144</v>
@@ -775,7 +775,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G14" t="n">
-        <v>9.72958087921143</v>
+        <v>9.72957992553711</v>
       </c>
       <c r="H14" t="n">
         <v>3295984</v>
@@ -804,7 +804,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G15" t="n">
-        <v>9.92399406433105</v>
+        <v>9.92399597167969</v>
       </c>
       <c r="H15" t="n">
         <v>3850427</v>
@@ -862,7 +862,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G17" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H17" t="n">
         <v>2559720</v>
@@ -891,7 +891,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G18" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H18" t="n">
         <v>3290589</v>
@@ -949,7 +949,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G20" t="n">
-        <v>9.5086555480957</v>
+        <v>9.50865459442139</v>
       </c>
       <c r="H20" t="n">
         <v>6623601</v>
@@ -978,7 +978,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G21" t="n">
-        <v>9.65888500213623</v>
+        <v>9.65888595581055</v>
       </c>
       <c r="H21" t="n">
         <v>3821281</v>
@@ -1007,7 +1007,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G22" t="n">
-        <v>9.67655754089355</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H22" t="n">
         <v>2737677</v>
@@ -1036,7 +1036,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G23" t="n">
-        <v>9.39377403259277</v>
+        <v>9.39377117156982</v>
       </c>
       <c r="H23" t="n">
         <v>3166705</v>
@@ -1094,7 +1094,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G25" t="n">
-        <v>9.04912948608398</v>
+        <v>9.04912853240967</v>
       </c>
       <c r="H25" t="n">
         <v>4769473</v>
@@ -1123,7 +1123,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G26" t="n">
-        <v>8.51448726654053</v>
+        <v>8.51448822021484</v>
       </c>
       <c r="H26" t="n">
         <v>10233516</v>
@@ -1152,7 +1152,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>8.13449668884277</v>
+        <v>8.13449478149414</v>
       </c>
       <c r="H27" t="n">
         <v>5939406</v>
@@ -1181,7 +1181,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G28" t="n">
-        <v>7.87380266189575</v>
+        <v>7.87380170822144</v>
       </c>
       <c r="H28" t="n">
         <v>6602091</v>
@@ -1210,7 +1210,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G29" t="n">
-        <v>8.1963529586792</v>
+        <v>8.19635391235352</v>
       </c>
       <c r="H29" t="n">
         <v>4659460</v>
@@ -1239,7 +1239,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G30" t="n">
-        <v>7.62636518478394</v>
+        <v>7.62636613845825</v>
       </c>
       <c r="H30" t="n">
         <v>4858455</v>
@@ -1268,7 +1268,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G31" t="n">
-        <v>7.82961702346802</v>
+        <v>7.82961940765381</v>
       </c>
       <c r="H31" t="n">
         <v>4416877</v>
@@ -1326,7 +1326,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G33" t="n">
-        <v>8.12123966217041</v>
+        <v>8.12124061584473</v>
       </c>
       <c r="H33" t="n">
         <v>6009029</v>
@@ -1355,7 +1355,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G34" t="n">
-        <v>8.2272834777832</v>
+        <v>8.22728538513184</v>
       </c>
       <c r="H34" t="n">
         <v>4436826</v>
@@ -1384,7 +1384,7 @@
         <v>9.43000030517578</v>
       </c>
       <c r="G35" t="n">
-        <v>8.333327293396</v>
+        <v>8.33332920074463</v>
       </c>
       <c r="H35" t="n">
         <v>5424764</v>
@@ -1500,7 +1500,7 @@
         <v>9.125</v>
       </c>
       <c r="G39" t="n">
-        <v>8.06379890441895</v>
+        <v>8.06379795074463</v>
       </c>
       <c r="H39" t="n">
         <v>4898758</v>
@@ -1587,7 +1587,7 @@
         <v>9.53499984741211</v>
       </c>
       <c r="G42" t="n">
-        <v>8.42611694335938</v>
+        <v>8.42611789703369</v>
       </c>
       <c r="H42" t="n">
         <v>4645972</v>
@@ -1674,7 +1674,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G45" t="n">
-        <v>8.85471343994141</v>
+        <v>8.85471439361572</v>
       </c>
       <c r="H45" t="n">
         <v>3329860</v>
@@ -1761,7 +1761,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G48" t="n">
-        <v>8.86355018615723</v>
+        <v>8.86355113983154</v>
       </c>
       <c r="H48" t="n">
         <v>5095073</v>
@@ -1790,7 +1790,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G49" t="n">
-        <v>8.91657257080078</v>
+        <v>8.91657447814941</v>
       </c>
       <c r="H49" t="n">
         <v>2835933</v>
@@ -1819,7 +1819,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G50" t="n">
-        <v>8.71332168579102</v>
+        <v>8.7133207321167</v>
       </c>
       <c r="H50" t="n">
         <v>5729693</v>
@@ -1848,7 +1848,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G51" t="n">
-        <v>9.31424045562744</v>
+        <v>9.31424140930176</v>
       </c>
       <c r="H51" t="n">
         <v>6630970</v>
@@ -1935,7 +1935,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G54" t="n">
-        <v>9.68539714813232</v>
+        <v>9.68539524078369</v>
       </c>
       <c r="H54" t="n">
         <v>4506665</v>
@@ -1964,7 +1964,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G55" t="n">
-        <v>9.52632808685303</v>
+        <v>9.52632999420166</v>
       </c>
       <c r="H55" t="n">
         <v>6478789</v>
@@ -1993,7 +1993,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>9.87097263336182</v>
+        <v>9.87097358703613</v>
       </c>
       <c r="H56" t="n">
         <v>6160258</v>
@@ -2080,7 +2080,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>9.93283271789551</v>
+        <v>9.93283176422119</v>
       </c>
       <c r="H59" t="n">
         <v>3544682</v>
@@ -2109,7 +2109,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G60" t="n">
-        <v>9.92399406433105</v>
+        <v>9.92399597167969</v>
       </c>
       <c r="H60" t="n">
         <v>2337035</v>
@@ -2167,7 +2167,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G62" t="n">
-        <v>9.9946928024292</v>
+        <v>9.99469184875488</v>
       </c>
       <c r="H62" t="n">
         <v>2409532</v>
@@ -2225,7 +2225,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G64" t="n">
-        <v>9.74725532531738</v>
+        <v>9.7472562789917</v>
       </c>
       <c r="H64" t="n">
         <v>3662180</v>
@@ -2254,7 +2254,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G65" t="n">
-        <v>10.0388765335083</v>
+        <v>10.0388774871826</v>
       </c>
       <c r="H65" t="n">
         <v>4656804</v>
@@ -2312,7 +2312,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G67" t="n">
-        <v>9.81795024871826</v>
+        <v>9.81795215606689</v>
       </c>
       <c r="H67" t="n">
         <v>3228692</v>
@@ -2370,7 +2370,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G69" t="n">
-        <v>9.68539714813232</v>
+        <v>9.68539524078369</v>
       </c>
       <c r="H69" t="n">
         <v>2717499</v>
@@ -2399,7 +2399,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G70" t="n">
-        <v>9.73841857910156</v>
+        <v>9.73841762542725</v>
       </c>
       <c r="H70" t="n">
         <v>2468827</v>
@@ -2428,7 +2428,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G71" t="n">
-        <v>9.39377403259277</v>
+        <v>9.39377117156982</v>
       </c>
       <c r="H71" t="n">
         <v>3799459</v>
@@ -2457,7 +2457,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G72" t="n">
-        <v>9.66771984100342</v>
+        <v>9.66772079467773</v>
       </c>
       <c r="H72" t="n">
         <v>3176037</v>
@@ -2486,7 +2486,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G73" t="n">
-        <v>9.60586166381836</v>
+        <v>9.60586261749268</v>
       </c>
       <c r="H73" t="n">
         <v>3723505</v>
@@ -2544,7 +2544,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G75" t="n">
-        <v>9.77376651763916</v>
+        <v>9.77376747131348</v>
       </c>
       <c r="H75" t="n">
         <v>3759867</v>
@@ -2573,7 +2573,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G76" t="n">
-        <v>9.77376651763916</v>
+        <v>9.77376747131348</v>
       </c>
       <c r="H76" t="n">
         <v>5381825</v>
@@ -2602,7 +2602,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G77" t="n">
-        <v>9.75609397888184</v>
+        <v>9.75609302520752</v>
       </c>
       <c r="H77" t="n">
         <v>2213600</v>
@@ -2631,7 +2631,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G78" t="n">
-        <v>9.67655754089355</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H78" t="n">
         <v>2402474</v>
@@ -2660,7 +2660,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>9.67655754089355</v>
+        <v>9.67655849456787</v>
       </c>
       <c r="H79" t="n">
         <v>1506370</v>
@@ -2689,7 +2689,7 @@
         <v>11</v>
       </c>
       <c r="G80" t="n">
-        <v>9.72074317932129</v>
+        <v>9.72074413299561</v>
       </c>
       <c r="H80" t="n">
         <v>2053615</v>
@@ -2718,7 +2718,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G81" t="n">
-        <v>9.76492977142334</v>
+        <v>9.76492881774902</v>
       </c>
       <c r="H81" t="n">
         <v>2292025</v>
@@ -2747,7 +2747,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G82" t="n">
-        <v>10.021203994751</v>
+        <v>10.0212030410767</v>
       </c>
       <c r="H82" t="n">
         <v>2269936</v>
@@ -2776,7 +2776,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G83" t="n">
-        <v>10.0477142333984</v>
+        <v>10.0477132797241</v>
       </c>
       <c r="H83" t="n">
         <v>2558895</v>
@@ -2805,7 +2805,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G84" t="n">
-        <v>9.74725532531738</v>
+        <v>9.7472562789917</v>
       </c>
       <c r="H84" t="n">
         <v>2548659</v>
@@ -2834,7 +2834,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G85" t="n">
-        <v>9.71190643310547</v>
+        <v>9.7119083404541</v>
       </c>
       <c r="H85" t="n">
         <v>2025319</v>
@@ -2892,7 +2892,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G87" t="n">
-        <v>9.73841857910156</v>
+        <v>9.73841762542725</v>
       </c>
       <c r="H87" t="n">
         <v>3212289</v>
@@ -2921,7 +2921,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G88" t="n">
-        <v>9.44679546356201</v>
+        <v>9.4467945098877</v>
       </c>
       <c r="H88" t="n">
         <v>6287450</v>
@@ -2950,7 +2950,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G89" t="n">
-        <v>9.18168354034424</v>
+        <v>9.18168449401855</v>
       </c>
       <c r="H89" t="n">
         <v>4604031</v>
@@ -3095,7 +3095,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G94" t="n">
-        <v>9.44679546356201</v>
+        <v>9.4467945098877</v>
       </c>
       <c r="H94" t="n">
         <v>1847337</v>
@@ -3124,7 +3124,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G95" t="n">
-        <v>9.43795967102051</v>
+        <v>9.43795871734619</v>
       </c>
       <c r="H95" t="n">
         <v>1697962</v>
@@ -3182,7 +3182,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G97" t="n">
-        <v>9.3407506942749</v>
+        <v>9.34075260162354</v>
       </c>
       <c r="H97" t="n">
         <v>1938908</v>
@@ -3211,7 +3211,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G98" t="n">
-        <v>9.31424045562744</v>
+        <v>9.31424140930176</v>
       </c>
       <c r="H98" t="n">
         <v>1455992</v>
@@ -3269,7 +3269,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>9.32307910919189</v>
+        <v>9.32307720184326</v>
       </c>
       <c r="H100" t="n">
         <v>2057915</v>
@@ -3385,7 +3385,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G104" t="n">
-        <v>9.65888500213623</v>
+        <v>9.65888595581055</v>
       </c>
       <c r="H104" t="n">
         <v>1058067</v>
@@ -3414,7 +3414,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G105" t="n">
-        <v>9.5086555480957</v>
+        <v>9.50865459442139</v>
       </c>
       <c r="H105" t="n">
         <v>2339951</v>
@@ -3443,7 +3443,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G106" t="n">
-        <v>9.40260982513428</v>
+        <v>9.40261077880859</v>
       </c>
       <c r="H106" t="n">
         <v>2179859</v>
@@ -3530,7 +3530,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G109" t="n">
-        <v>8.96959400177002</v>
+        <v>8.96959495544434</v>
       </c>
       <c r="H109" t="n">
         <v>2176830</v>
@@ -3559,7 +3559,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G110" t="n">
-        <v>8.77960014343262</v>
+        <v>8.77959823608398</v>
       </c>
       <c r="H110" t="n">
         <v>2933612</v>
@@ -3617,7 +3617,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>8.88122463226318</v>
+        <v>8.8812255859375</v>
       </c>
       <c r="H112" t="n">
         <v>1048603</v>
@@ -3646,7 +3646,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G113" t="n">
-        <v>8.59844017028809</v>
+        <v>8.59843921661377</v>
       </c>
       <c r="H113" t="n">
         <v>3301203</v>
@@ -3675,7 +3675,7 @@
         <v>9.25</v>
       </c>
       <c r="G114" t="n">
-        <v>8.17426013946533</v>
+        <v>8.17426204681396</v>
       </c>
       <c r="H114" t="n">
         <v>5058824</v>
@@ -3704,7 +3704,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G115" t="n">
-        <v>8.16542530059814</v>
+        <v>8.16542434692383</v>
       </c>
       <c r="H115" t="n">
         <v>3204890</v>
@@ -3733,7 +3733,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G116" t="n">
-        <v>7.97984552383423</v>
+        <v>7.97984743118286</v>
       </c>
       <c r="H116" t="n">
         <v>3768496</v>
@@ -3791,7 +3791,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>8.2184476852417</v>
+        <v>8.21844673156738</v>
       </c>
       <c r="H118" t="n">
         <v>3225035</v>
@@ -3849,7 +3849,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G120" t="n">
-        <v>8.82820224761963</v>
+        <v>8.82820320129395</v>
       </c>
       <c r="H120" t="n">
         <v>3886915</v>
@@ -3936,7 +3936,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G123" t="n">
-        <v>8.99610710144043</v>
+        <v>8.99610614776611</v>
       </c>
       <c r="H123" t="n">
         <v>2143433</v>
@@ -3965,7 +3965,7 @@
         <v>8.96500015258789</v>
       </c>
       <c r="G124" t="n">
-        <v>7.92240571975708</v>
+        <v>7.92240715026855</v>
       </c>
       <c r="H124" t="n">
         <v>7828810</v>
@@ -4052,7 +4052,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>7.9312424659729</v>
+        <v>7.93124294281006</v>
       </c>
       <c r="H127" t="n">
         <v>4233344</v>
@@ -4081,7 +4081,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G128" t="n">
-        <v>8.00635814666748</v>
+        <v>8.0063591003418</v>
       </c>
       <c r="H128" t="n">
         <v>5113253</v>
@@ -4110,7 +4110,7 @@
         <v>9.03499984741211</v>
       </c>
       <c r="G129" t="n">
-        <v>7.9842643737793</v>
+        <v>7.98426580429077</v>
       </c>
       <c r="H129" t="n">
         <v>2377104</v>
@@ -4139,7 +4139,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G130" t="n">
-        <v>8.02845191955566</v>
+        <v>8.02845001220703</v>
       </c>
       <c r="H130" t="n">
         <v>2073437</v>
@@ -4168,7 +4168,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G131" t="n">
-        <v>7.76775884628296</v>
+        <v>7.7677583694458</v>
       </c>
       <c r="H131" t="n">
         <v>2876700</v>
@@ -4226,7 +4226,7 @@
         <v>8.77499961853027</v>
       </c>
       <c r="G133" t="n">
-        <v>7.75450086593628</v>
+        <v>7.75450372695923</v>
       </c>
       <c r="H133" t="n">
         <v>2080137</v>
@@ -4255,7 +4255,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G134" t="n">
-        <v>8.19193744659424</v>
+        <v>8.19193649291992</v>
       </c>
       <c r="H134" t="n">
         <v>2804835</v>
@@ -4313,7 +4313,7 @@
         <v>9.75</v>
       </c>
       <c r="G136" t="n">
-        <v>8.61611461639404</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H136" t="n">
         <v>3357023</v>
@@ -4342,7 +4342,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G137" t="n">
-        <v>8.47030258178711</v>
+        <v>8.47030353546143</v>
       </c>
       <c r="H137" t="n">
         <v>2354788</v>
@@ -4400,7 +4400,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G139" t="n">
-        <v>8.56309127807617</v>
+        <v>8.56309032440186</v>
       </c>
       <c r="H139" t="n">
         <v>1249727</v>
@@ -4429,7 +4429,7 @@
         <v>9.74499988555908</v>
       </c>
       <c r="G140" t="n">
-        <v>8.61169624328613</v>
+        <v>8.61169528961182</v>
       </c>
       <c r="H140" t="n">
         <v>1554602</v>
@@ -4458,7 +4458,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>8.54983806610107</v>
+        <v>8.54983711242676</v>
       </c>
       <c r="H141" t="n">
         <v>2188326</v>
@@ -4516,7 +4516,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G143" t="n">
-        <v>8.52774238586426</v>
+        <v>8.52774333953857</v>
       </c>
       <c r="H143" t="n">
         <v>2470005</v>
@@ -4545,7 +4545,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G144" t="n">
-        <v>8.55425453186035</v>
+        <v>8.55425548553467</v>
       </c>
       <c r="H144" t="n">
         <v>2362874</v>
@@ -4574,7 +4574,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>8.53658103942871</v>
+        <v>8.53658008575439</v>
       </c>
       <c r="H145" t="n">
         <v>2163535</v>
@@ -4603,7 +4603,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G146" t="n">
-        <v>8.51890659332275</v>
+        <v>8.51890754699707</v>
       </c>
       <c r="H146" t="n">
         <v>1732831</v>
@@ -4690,7 +4690,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G149" t="n">
-        <v>9.02261734008789</v>
+        <v>9.02261924743652</v>
       </c>
       <c r="H149" t="n">
         <v>4001116</v>
@@ -4748,7 +4748,7 @@
         <v>9.75</v>
       </c>
       <c r="G151" t="n">
-        <v>8.61611461639404</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H151" t="n">
         <v>2776890</v>
@@ -4777,7 +4777,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G152" t="n">
-        <v>8.35100269317627</v>
+        <v>8.35100364685059</v>
       </c>
       <c r="H152" t="n">
         <v>2275926</v>
@@ -4864,7 +4864,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G155" t="n">
-        <v>8.53658103942871</v>
+        <v>8.53658008575439</v>
       </c>
       <c r="H155" t="n">
         <v>1727750</v>
@@ -4893,7 +4893,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>8.58076572418213</v>
+        <v>8.58076477050781</v>
       </c>
       <c r="H156" t="n">
         <v>1530350</v>
@@ -4951,7 +4951,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G158" t="n">
-        <v>8.90773677825928</v>
+        <v>8.90773487091064</v>
       </c>
       <c r="H158" t="n">
         <v>1867997</v>
@@ -5038,7 +5038,7 @@
         <v>9.75</v>
       </c>
       <c r="G161" t="n">
-        <v>8.61611461639404</v>
+        <v>8.61611270904541</v>
       </c>
       <c r="H161" t="n">
         <v>1737728</v>
@@ -5067,7 +5067,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G162" t="n">
-        <v>8.77960014343262</v>
+        <v>8.77959823608398</v>
       </c>
       <c r="H162" t="n">
         <v>1195079</v>
@@ -5096,7 +5096,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>8.64704322814941</v>
+        <v>8.64704418182373</v>
       </c>
       <c r="H163" t="n">
         <v>1618524</v>
@@ -5125,7 +5125,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G164" t="n">
-        <v>8.78401756286621</v>
+        <v>8.78401565551758</v>
       </c>
       <c r="H164" t="n">
         <v>1268967</v>
@@ -5154,7 +5154,7 @@
         <v>10.25</v>
       </c>
       <c r="G165" t="n">
-        <v>9.05796718597412</v>
+        <v>9.05796527862549</v>
       </c>
       <c r="H165" t="n">
         <v>3109195</v>
@@ -5183,7 +5183,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G166" t="n">
-        <v>9.19052124023438</v>
+        <v>9.19051933288574</v>
       </c>
       <c r="H166" t="n">
         <v>2423483</v>
@@ -5212,7 +5212,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G167" t="n">
-        <v>9.04029178619385</v>
+        <v>9.04029083251953</v>
       </c>
       <c r="H167" t="n">
         <v>2244293</v>
@@ -5241,7 +5241,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G168" t="n">
-        <v>9.13749885559082</v>
+        <v>9.13749980926514</v>
       </c>
       <c r="H168" t="n">
         <v>1151195</v>
@@ -5328,7 +5328,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G171" t="n">
-        <v>9.04029178619385</v>
+        <v>9.04029083251953</v>
       </c>
       <c r="H171" t="n">
         <v>1188440</v>
@@ -5357,7 +5357,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G172" t="n">
-        <v>9.04912948608398</v>
+        <v>9.04912853240967</v>
       </c>
       <c r="H172" t="n">
         <v>1740241</v>
@@ -5386,7 +5386,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G173" t="n">
-        <v>9.11098861694336</v>
+        <v>9.11098766326904</v>
       </c>
       <c r="H173" t="n">
         <v>1503734</v>
@@ -5444,7 +5444,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G175" t="n">
-        <v>9.19052124023438</v>
+        <v>9.19051933288574</v>
       </c>
       <c r="H175" t="n">
         <v>2742507</v>
@@ -5473,7 +5473,7 @@
         <v>10.75</v>
       </c>
       <c r="G176" t="n">
-        <v>9.49981784820557</v>
+        <v>9.49981689453125</v>
       </c>
       <c r="H176" t="n">
         <v>3615822</v>
@@ -5502,7 +5502,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G177" t="n">
-        <v>9.57935237884521</v>
+        <v>9.5793514251709</v>
       </c>
       <c r="H177" t="n">
         <v>2905891</v>
@@ -5589,7 +5589,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G180" t="n">
-        <v>9.42912101745605</v>
+        <v>9.42912292480469</v>
       </c>
       <c r="H180" t="n">
         <v>2022865</v>
@@ -5618,7 +5618,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>9.36726188659668</v>
+        <v>9.36726379394531</v>
       </c>
       <c r="H181" t="n">
         <v>1688071</v>
@@ -5647,7 +5647,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G182" t="n">
-        <v>9.42912101745605</v>
+        <v>9.42912292480469</v>
       </c>
       <c r="H182" t="n">
         <v>1699744</v>
@@ -5676,7 +5676,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G183" t="n">
-        <v>9.13749885559082</v>
+        <v>9.13749980926514</v>
       </c>
       <c r="H183" t="n">
         <v>3515793</v>
@@ -5763,7 +5763,7 @@
         <v>10.25</v>
       </c>
       <c r="G186" t="n">
-        <v>9.05796718597412</v>
+        <v>9.05796527862549</v>
       </c>
       <c r="H186" t="n">
         <v>1386316</v>
@@ -5821,7 +5821,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G188" t="n">
-        <v>9.03145408630371</v>
+        <v>9.03145503997803</v>
       </c>
       <c r="H188" t="n">
         <v>1184807</v>
@@ -5850,7 +5850,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G189" t="n">
-        <v>8.91657257080078</v>
+        <v>8.91657447814941</v>
       </c>
       <c r="H189" t="n">
         <v>2240774</v>
@@ -5879,7 +5879,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>8.81052875518799</v>
+        <v>8.81052780151367</v>
       </c>
       <c r="H190" t="n">
         <v>2105735</v>
@@ -5937,7 +5937,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G192" t="n">
-        <v>8.89890098571777</v>
+        <v>8.89889812469482</v>
       </c>
       <c r="H192" t="n">
         <v>1162858</v>
@@ -5966,7 +5966,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G193" t="n">
-        <v>8.91657257080078</v>
+        <v>8.91657447814941</v>
       </c>
       <c r="H193" t="n">
         <v>2475501</v>
@@ -5995,7 +5995,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G194" t="n">
-        <v>8.81052875518799</v>
+        <v>8.81052780151367</v>
       </c>
       <c r="H194" t="n">
         <v>1598511</v>
@@ -6053,7 +6053,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G196" t="n">
-        <v>8.8458776473999</v>
+        <v>8.84587669372559</v>
       </c>
       <c r="H196" t="n">
         <v>2006985</v>
@@ -6082,7 +6082,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G197" t="n">
-        <v>8.77960014343262</v>
+        <v>8.77959823608398</v>
       </c>
       <c r="H197" t="n">
         <v>1646942</v>
@@ -6111,7 +6111,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G198" t="n">
-        <v>8.75308704376221</v>
+        <v>8.75308799743652</v>
       </c>
       <c r="H198" t="n">
         <v>3052549</v>
@@ -6140,7 +6140,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G199" t="n">
-        <v>8.85471343994141</v>
+        <v>8.85471439361572</v>
       </c>
       <c r="H199" t="n">
         <v>1494588</v>
@@ -6169,7 +6169,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G200" t="n">
-        <v>8.90773677825928</v>
+        <v>8.90773487091064</v>
       </c>
       <c r="H200" t="n">
         <v>1791539</v>
@@ -6198,7 +6198,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G201" t="n">
-        <v>8.91657257080078</v>
+        <v>8.91657447814941</v>
       </c>
       <c r="H201" t="n">
         <v>1105293</v>
@@ -6256,7 +6256,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G203" t="n">
-        <v>9.09331512451172</v>
+        <v>9.0933141708374</v>
       </c>
       <c r="H203" t="n">
         <v>1939844</v>
@@ -6314,7 +6314,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>9.60586166381836</v>
+        <v>9.60586261749268</v>
       </c>
       <c r="H205" t="n">
         <v>3653941</v>
@@ -6372,7 +6372,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G207" t="n">
-        <v>9.97701835632324</v>
+        <v>9.97701930999756</v>
       </c>
       <c r="H207" t="n">
         <v>3906339</v>
@@ -6401,7 +6401,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.0300407409668</v>
+        <v>10.0300416946411</v>
       </c>
       <c r="H208" t="n">
         <v>3390112</v>
@@ -6488,7 +6488,7 @@
         <v>11</v>
       </c>
       <c r="G211" t="n">
-        <v>9.72074317932129</v>
+        <v>9.72074413299561</v>
       </c>
       <c r="H211" t="n">
         <v>1645246</v>
@@ -6517,7 +6517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G212" t="n">
-        <v>9.79143905639648</v>
+        <v>9.79143810272217</v>
       </c>
       <c r="H212" t="n">
         <v>1829589</v>
@@ -6604,7 +6604,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G215" t="n">
-        <v>9.82678890228271</v>
+        <v>9.8267879486084</v>
       </c>
       <c r="H215" t="n">
         <v>1488234</v>
@@ -6720,7 +6720,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G219" t="n">
-        <v>9.40260982513428</v>
+        <v>9.40261077880859</v>
       </c>
       <c r="H219" t="n">
         <v>2857422</v>
@@ -6778,7 +6778,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G221" t="n">
-        <v>10.2421283721924</v>
+        <v>10.242130279541</v>
       </c>
       <c r="H221" t="n">
         <v>9522603</v>
@@ -6836,7 +6836,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G223" t="n">
-        <v>10.7104921340942</v>
+        <v>10.7104940414429</v>
       </c>
       <c r="H223" t="n">
         <v>4019546</v>
@@ -6865,7 +6865,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>10.9137449264526</v>
+        <v>10.913745880127</v>
       </c>
       <c r="H224" t="n">
         <v>3192238</v>
@@ -6894,7 +6894,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G225" t="n">
-        <v>10.8342113494873</v>
+        <v>10.8342094421387</v>
       </c>
       <c r="H225" t="n">
         <v>2531880</v>
@@ -6923,7 +6923,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G226" t="n">
-        <v>10.9756031036377</v>
+        <v>10.975604057312</v>
       </c>
       <c r="H226" t="n">
         <v>3172699</v>
@@ -7010,7 +7010,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G229" t="n">
-        <v>10.5602598190308</v>
+        <v>10.5602617263794</v>
       </c>
       <c r="H229" t="n">
         <v>2619382</v>
@@ -7039,7 +7039,7 @@
         <v>12</v>
       </c>
       <c r="G230" t="n">
-        <v>10.6044492721558</v>
+        <v>10.6044483184814</v>
       </c>
       <c r="H230" t="n">
         <v>2041926</v>
@@ -7126,7 +7126,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G233" t="n">
-        <v>10.7104921340942</v>
+        <v>10.7104940414429</v>
       </c>
       <c r="H233" t="n">
         <v>1126558</v>
@@ -7155,7 +7155,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5956106185913</v>
+        <v>10.5956115722656</v>
       </c>
       <c r="H234" t="n">
         <v>1817124</v>
@@ -7184,7 +7184,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G235" t="n">
-        <v>10.7635154724121</v>
+        <v>10.7635145187378</v>
       </c>
       <c r="H235" t="n">
         <v>2986862</v>
@@ -7213,7 +7213,7 @@
         <v>12.25</v>
       </c>
       <c r="G236" t="n">
-        <v>10.8253726959229</v>
+        <v>10.8253746032715</v>
       </c>
       <c r="H236" t="n">
         <v>4147765</v>
@@ -7271,7 +7271,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G238" t="n">
-        <v>10.93141746521</v>
+        <v>10.9314184188843</v>
       </c>
       <c r="H238" t="n">
         <v>3810726</v>
@@ -7300,7 +7300,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G239" t="n">
-        <v>11.3379211425781</v>
+        <v>11.3379230499268</v>
       </c>
       <c r="H239" t="n">
         <v>4810891</v>
@@ -7329,7 +7329,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G240" t="n">
-        <v>11.5765218734741</v>
+        <v>11.5765228271484</v>
       </c>
       <c r="H240" t="n">
         <v>3990228</v>
@@ -7387,7 +7387,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G242" t="n">
-        <v>12.0979070663452</v>
+        <v>12.0979061126709</v>
       </c>
       <c r="H242" t="n">
         <v>3064071</v>
@@ -7474,7 +7474,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>11.7179155349731</v>
+        <v>11.7179136276245</v>
       </c>
       <c r="H245" t="n">
         <v>2678624</v>
@@ -7503,7 +7503,7 @@
         <v>13.2200002670288</v>
       </c>
       <c r="G246" t="n">
-        <v>11.6825656890869</v>
+        <v>11.6825685501099</v>
       </c>
       <c r="H246" t="n">
         <v>2100381</v>
@@ -7561,7 +7561,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>11.8416347503662</v>
+        <v>11.8416337966919</v>
       </c>
       <c r="H248" t="n">
         <v>2232999</v>
@@ -7590,7 +7590,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G249" t="n">
-        <v>11.8416347503662</v>
+        <v>11.8416337966919</v>
       </c>
       <c r="H249" t="n">
         <v>1455800</v>
@@ -7619,7 +7619,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G250" t="n">
-        <v>11.9211673736572</v>
+        <v>11.9211654663086</v>
       </c>
       <c r="H250" t="n">
         <v>1741925</v>
@@ -7648,7 +7648,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G251" t="n">
-        <v>11.8769807815552</v>
+        <v>11.8769817352295</v>
       </c>
       <c r="H251" t="n">
         <v>1444254</v>
@@ -7677,7 +7677,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G252" t="n">
-        <v>11.8062858581543</v>
+        <v>11.80628490448</v>
       </c>
       <c r="H252" t="n">
         <v>1542041</v>
@@ -7706,7 +7706,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G253" t="n">
-        <v>11.9123287200928</v>
+        <v>11.9123296737671</v>
       </c>
       <c r="H253" t="n">
         <v>872131</v>
@@ -7735,7 +7735,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>11.9830265045166</v>
+        <v>11.9830274581909</v>
       </c>
       <c r="H254" t="n">
         <v>793819</v>
@@ -7764,7 +7764,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G255" t="n">
-        <v>11.8593072891235</v>
+        <v>11.8593063354492</v>
       </c>
       <c r="H255" t="n">
         <v>774515</v>
@@ -7822,7 +7822,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G257" t="n">
-        <v>11.7886114120483</v>
+        <v>11.7886123657227</v>
       </c>
       <c r="H257" t="n">
         <v>1138655</v>
@@ -7851,7 +7851,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G258" t="n">
-        <v>11.8504695892334</v>
+        <v>11.850471496582</v>
       </c>
       <c r="H258" t="n">
         <v>1093354</v>
@@ -7880,7 +7880,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G259" t="n">
-        <v>11.8504695892334</v>
+        <v>11.850471496582</v>
       </c>
       <c r="H259" t="n">
         <v>1208429</v>
@@ -7909,7 +7909,7 @@
         <v>13.5299997329712</v>
       </c>
       <c r="G260" t="n">
-        <v>11.9565153121948</v>
+        <v>11.9565143585205</v>
       </c>
       <c r="H260" t="n">
         <v>1413349</v>
@@ -7938,7 +7938,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G261" t="n">
-        <v>12.0802335739136</v>
+        <v>12.0802354812622</v>
       </c>
       <c r="H261" t="n">
         <v>1693151</v>
@@ -7967,7 +7967,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G262" t="n">
-        <v>12.0625591278076</v>
+        <v>12.0625581741333</v>
       </c>
       <c r="H262" t="n">
         <v>1244253</v>
@@ -7996,7 +7996,7 @@
         <v>13.4099998474121</v>
       </c>
       <c r="G263" t="n">
-        <v>11.8504695892334</v>
+        <v>11.850471496582</v>
       </c>
       <c r="H263" t="n">
         <v>2284028</v>
@@ -8025,7 +8025,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G264" t="n">
-        <v>11.9123287200928</v>
+        <v>11.9123296737671</v>
       </c>
       <c r="H264" t="n">
         <v>1479095</v>
@@ -8054,7 +8054,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>11.9741897583008</v>
+        <v>11.9741888046265</v>
       </c>
       <c r="H265" t="n">
         <v>1179098</v>
@@ -8083,7 +8083,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>11.5765218734741</v>
+        <v>11.5765228271484</v>
       </c>
       <c r="H266" t="n">
         <v>3655476</v>
@@ -8141,7 +8141,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G268" t="n">
-        <v>11.3555955886841</v>
+        <v>11.3555965423584</v>
       </c>
       <c r="H268" t="n">
         <v>1779254</v>
@@ -8170,7 +8170,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G269" t="n">
-        <v>11.4262933731079</v>
+        <v>11.4262914657593</v>
       </c>
       <c r="H269" t="n">
         <v>1714652</v>
@@ -8199,7 +8199,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>11.5323362350464</v>
+        <v>11.5323371887207</v>
       </c>
       <c r="H270" t="n">
         <v>1636226</v>
@@ -8228,7 +8228,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G271" t="n">
-        <v>11.5765218734741</v>
+        <v>11.5765228271484</v>
       </c>
       <c r="H271" t="n">
         <v>1339891</v>
@@ -8257,7 +8257,7 @@
         <v>13</v>
       </c>
       <c r="G272" t="n">
-        <v>11.4881505966187</v>
+        <v>11.488151550293</v>
       </c>
       <c r="H272" t="n">
         <v>2173068</v>
@@ -8286,7 +8286,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G273" t="n">
-        <v>11.15234375</v>
+        <v>11.1523447036743</v>
       </c>
       <c r="H273" t="n">
         <v>1905930</v>
@@ -8315,7 +8315,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G274" t="n">
-        <v>11.2848997116089</v>
+        <v>11.2849016189575</v>
       </c>
       <c r="H274" t="n">
         <v>2010090</v>
@@ -8344,7 +8344,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G275" t="n">
-        <v>11.3555955886841</v>
+        <v>11.3555965423584</v>
       </c>
       <c r="H275" t="n">
         <v>2289321</v>
@@ -8373,7 +8373,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G276" t="n">
-        <v>11.0816478729248</v>
+        <v>11.0816488265991</v>
       </c>
       <c r="H276" t="n">
         <v>2767089</v>
@@ -8402,7 +8402,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G277" t="n">
-        <v>11.0816478729248</v>
+        <v>11.0816488265991</v>
       </c>
       <c r="H277" t="n">
         <v>1148346</v>
@@ -8518,7 +8518,7 @@
         <v>12.5</v>
       </c>
       <c r="G281" t="n">
-        <v>11.0462989807129</v>
+        <v>11.0462999343872</v>
       </c>
       <c r="H281" t="n">
         <v>2794563</v>
@@ -8547,7 +8547,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G282" t="n">
-        <v>11.0109519958496</v>
+        <v>11.0109529495239</v>
       </c>
       <c r="H282" t="n">
         <v>2422990</v>
@@ -8663,7 +8663,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G286" t="n">
-        <v>10.5956106185913</v>
+        <v>10.5956115722656</v>
       </c>
       <c r="H286" t="n">
         <v>3094937</v>
@@ -8750,7 +8750,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G289" t="n">
-        <v>10.5514268875122</v>
+        <v>10.5514249801636</v>
       </c>
       <c r="H289" t="n">
         <v>1582712</v>
@@ -8779,7 +8779,7 @@
         <v>11.75</v>
       </c>
       <c r="G290" t="n">
-        <v>10.3835220336914</v>
+        <v>10.3835229873657</v>
       </c>
       <c r="H290" t="n">
         <v>1641010</v>
@@ -8837,7 +8837,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G292" t="n">
-        <v>10.4542169570923</v>
+        <v>10.4542188644409</v>
       </c>
       <c r="H292" t="n">
         <v>1981713</v>
@@ -8866,7 +8866,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G293" t="n">
-        <v>10.4984045028687</v>
+        <v>10.4984035491943</v>
       </c>
       <c r="H293" t="n">
         <v>1899836</v>
@@ -8895,7 +8895,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G294" t="n">
-        <v>10.4718933105469</v>
+        <v>10.4718923568726</v>
       </c>
       <c r="H294" t="n">
         <v>1857546</v>
@@ -8982,7 +8982,7 @@
         <v>12.25</v>
       </c>
       <c r="G297" t="n">
-        <v>10.8253726959229</v>
+        <v>10.8253746032715</v>
       </c>
       <c r="H297" t="n">
         <v>5453769</v>
@@ -9011,7 +9011,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G298" t="n">
-        <v>11.3555955886841</v>
+        <v>11.3555965423584</v>
       </c>
       <c r="H298" t="n">
         <v>6418081</v>
@@ -9040,7 +9040,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G299" t="n">
-        <v>11.4616394042969</v>
+        <v>11.4616422653198</v>
       </c>
       <c r="H299" t="n">
         <v>4748154</v>
@@ -9069,7 +9069,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G300" t="n">
-        <v>11.8593072891235</v>
+        <v>11.8593063354492</v>
       </c>
       <c r="H300" t="n">
         <v>4231036</v>
@@ -9098,7 +9098,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G301" t="n">
-        <v>12.1244173049927</v>
+        <v>12.1244192123413</v>
       </c>
       <c r="H301" t="n">
         <v>3824740</v>
@@ -9185,7 +9185,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G304" t="n">
-        <v>11.6295433044434</v>
+        <v>11.6295442581177</v>
       </c>
       <c r="H304" t="n">
         <v>3462287</v>
@@ -9214,7 +9214,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G305" t="n">
-        <v>11.6383829116821</v>
+        <v>11.6383810043335</v>
       </c>
       <c r="H305" t="n">
         <v>1938365</v>
@@ -9243,7 +9243,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G306" t="n">
-        <v>11.6383829116821</v>
+        <v>11.6383810043335</v>
       </c>
       <c r="H306" t="n">
         <v>1473970</v>
@@ -9301,7 +9301,7 @@
         <v>13</v>
       </c>
       <c r="G308" t="n">
-        <v>11.4881505966187</v>
+        <v>11.488151550293</v>
       </c>
       <c r="H308" t="n">
         <v>1391142</v>
@@ -9330,7 +9330,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>11.3997812271118</v>
+        <v>11.3997831344604</v>
       </c>
       <c r="H309" t="n">
         <v>1926929</v>
@@ -9417,7 +9417,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>12.0183753967285</v>
+        <v>12.0183744430542</v>
       </c>
       <c r="H312" t="n">
         <v>8328313</v>
@@ -9446,7 +9446,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G313" t="n">
-        <v>11.5853586196899</v>
+        <v>11.5853595733643</v>
       </c>
       <c r="H313" t="n">
         <v>6797589</v>
@@ -9475,7 +9475,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3909454345703</v>
+        <v>11.390944480896</v>
       </c>
       <c r="H314" t="n">
         <v>4226238</v>
@@ -9504,7 +9504,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G315" t="n">
-        <v>11.5765218734741</v>
+        <v>11.5765228271484</v>
       </c>
       <c r="H315" t="n">
         <v>3646441</v>
@@ -9533,7 +9533,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G316" t="n">
-        <v>11.6648941040039</v>
+        <v>11.6648931503296</v>
       </c>
       <c r="H316" t="n">
         <v>2635405</v>
@@ -9562,7 +9562,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G317" t="n">
-        <v>11.6648941040039</v>
+        <v>11.6648931503296</v>
       </c>
       <c r="H317" t="n">
         <v>2060324</v>
@@ -9620,7 +9620,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G319" t="n">
-        <v>11.5411758422852</v>
+        <v>11.5411748886108</v>
       </c>
       <c r="H319" t="n">
         <v>2189083</v>
@@ -9707,7 +9707,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G322" t="n">
-        <v>11.7444257736206</v>
+        <v>11.7444267272949</v>
       </c>
       <c r="H322" t="n">
         <v>1616298</v>
@@ -9736,7 +9736,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>11.726752281189</v>
+        <v>11.7267532348633</v>
       </c>
       <c r="H323" t="n">
         <v>1799305</v>
@@ -9765,7 +9765,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G324" t="n">
-        <v>11.8151235580444</v>
+        <v>11.8151216506958</v>
       </c>
       <c r="H324" t="n">
         <v>1698413</v>
@@ -9794,7 +9794,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G325" t="n">
-        <v>11.6737298965454</v>
+        <v>11.6737289428711</v>
       </c>
       <c r="H325" t="n">
         <v>1436991</v>
@@ -9823,7 +9823,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>11.8858184814453</v>
+        <v>11.8858194351196</v>
       </c>
       <c r="H326" t="n">
         <v>2540234</v>
@@ -9881,7 +9881,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G328" t="n">
-        <v>11.7709369659424</v>
+        <v>11.7709350585938</v>
       </c>
       <c r="H328" t="n">
         <v>1328427</v>
@@ -9910,7 +9910,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G329" t="n">
-        <v>11.7179155349731</v>
+        <v>11.7179136276245</v>
       </c>
       <c r="H329" t="n">
         <v>2169377</v>
@@ -9939,7 +9939,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>11.5765218734741</v>
+        <v>11.5765228271484</v>
       </c>
       <c r="H330" t="n">
         <v>1595987</v>
@@ -9968,7 +9968,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G331" t="n">
-        <v>11.6560554504395</v>
+        <v>11.6560544967651</v>
       </c>
       <c r="H331" t="n">
         <v>1779259</v>
@@ -10026,7 +10026,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G333" t="n">
-        <v>12.2569751739502</v>
+        <v>12.2569742202759</v>
       </c>
       <c r="H333" t="n">
         <v>4164755</v>
@@ -10055,7 +10055,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G334" t="n">
-        <v>12.2569751739502</v>
+        <v>12.2569742202759</v>
       </c>
       <c r="H334" t="n">
         <v>2272932</v>
@@ -10113,7 +10113,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G336" t="n">
-        <v>12.9462623596191</v>
+        <v>12.9462633132935</v>
       </c>
       <c r="H336" t="n">
         <v>4567641</v>
@@ -10142,7 +10142,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G337" t="n">
-        <v>12.8844041824341</v>
+        <v>12.8844051361084</v>
       </c>
       <c r="H337" t="n">
         <v>2030879</v>
@@ -10200,7 +10200,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G339" t="n">
-        <v>12.8844041824341</v>
+        <v>12.8844051361084</v>
       </c>
       <c r="H339" t="n">
         <v>2046076</v>
@@ -10258,7 +10258,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G341" t="n">
-        <v>12.8755674362183</v>
+        <v>12.8755683898926</v>
       </c>
       <c r="H341" t="n">
         <v>2650600</v>
@@ -10316,7 +10316,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G343" t="n">
-        <v>13.6355533599854</v>
+        <v>13.635552406311</v>
       </c>
       <c r="H343" t="n">
         <v>5272302</v>
@@ -10345,7 +10345,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G344" t="n">
-        <v>13.5560188293457</v>
+        <v>13.55601978302</v>
       </c>
       <c r="H344" t="n">
         <v>2947897</v>
@@ -10374,7 +10374,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G345" t="n">
-        <v>13.6709003448486</v>
+        <v>13.6709012985229</v>
       </c>
       <c r="H345" t="n">
         <v>2783669</v>
@@ -10403,7 +10403,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G346" t="n">
-        <v>13.6267166137695</v>
+        <v>13.6267147064209</v>
       </c>
       <c r="H346" t="n">
         <v>3185772</v>
@@ -10461,7 +10461,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G348" t="n">
-        <v>14.0067090988159</v>
+        <v>14.0067081451416</v>
       </c>
       <c r="H348" t="n">
         <v>3030763</v>
@@ -10519,7 +10519,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>13.7857818603516</v>
+        <v>13.7857828140259</v>
       </c>
       <c r="H350" t="n">
         <v>1691678</v>
@@ -10577,7 +10577,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>13.1671876907349</v>
+        <v>13.1671895980835</v>
       </c>
       <c r="H352" t="n">
         <v>2772854</v>
@@ -10606,7 +10606,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G353" t="n">
-        <v>13.158353805542</v>
+        <v>13.1583518981934</v>
       </c>
       <c r="H353" t="n">
         <v>4503125</v>
@@ -10635,7 +10635,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G354" t="n">
-        <v>13.4941596984863</v>
+        <v>13.4941606521606</v>
       </c>
       <c r="H354" t="n">
         <v>2808974</v>
@@ -10693,7 +10693,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G356" t="n">
-        <v>13.3425407409668</v>
+        <v>13.3425397872925</v>
       </c>
       <c r="H356" t="n">
         <v>1364880</v>
@@ -10722,7 +10722,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G357" t="n">
-        <v>13.5476741790771</v>
+        <v>13.5476732254028</v>
       </c>
       <c r="H357" t="n">
         <v>1644823</v>
@@ -10780,7 +10780,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>13.8419942855835</v>
+        <v>13.8419952392578</v>
       </c>
       <c r="H359" t="n">
         <v>2205709</v>
@@ -10809,7 +10809,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G360" t="n">
-        <v>13.6190233230591</v>
+        <v>13.6190242767334</v>
       </c>
       <c r="H360" t="n">
         <v>1789088</v>
@@ -10838,7 +10838,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G361" t="n">
-        <v>13.9222631454468</v>
+        <v>13.9222621917725</v>
       </c>
       <c r="H361" t="n">
         <v>1390700</v>
@@ -10896,7 +10896,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G363" t="n">
-        <v>14.2165832519531</v>
+        <v>14.2165842056274</v>
       </c>
       <c r="H363" t="n">
         <v>2095696</v>
@@ -10954,7 +10954,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G365" t="n">
-        <v>14.0025320053101</v>
+        <v>14.0025329589844</v>
       </c>
       <c r="H365" t="n">
         <v>1464318</v>
@@ -11012,7 +11012,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>13.9133453369141</v>
+        <v>13.9133434295654</v>
       </c>
       <c r="H367" t="n">
         <v>2071899</v>
@@ -11041,7 +11041,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G368" t="n">
-        <v>14.1987457275391</v>
+        <v>14.1987466812134</v>
       </c>
       <c r="H368" t="n">
         <v>1695323</v>
@@ -11070,7 +11070,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G369" t="n">
-        <v>14.3057718276978</v>
+        <v>14.3057737350464</v>
       </c>
       <c r="H369" t="n">
         <v>1383611</v>
@@ -11099,7 +11099,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G370" t="n">
-        <v>13.886589050293</v>
+        <v>13.8865880966187</v>
       </c>
       <c r="H370" t="n">
         <v>2462454</v>
@@ -11186,7 +11186,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G373" t="n">
-        <v>13.6814546585083</v>
+        <v>13.6814556121826</v>
       </c>
       <c r="H373" t="n">
         <v>2068077</v>
@@ -11273,7 +11273,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G376" t="n">
-        <v>13.5119981765747</v>
+        <v>13.5119972229004</v>
       </c>
       <c r="H376" t="n">
         <v>2208324</v>
@@ -11302,7 +11302,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G377" t="n">
-        <v>13.8776693344116</v>
+        <v>13.8776683807373</v>
       </c>
       <c r="H377" t="n">
         <v>2003317</v>
@@ -11360,7 +11360,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G379" t="n">
-        <v>13.6814546585083</v>
+        <v>13.6814556121826</v>
       </c>
       <c r="H379" t="n">
         <v>1051104</v>
@@ -11418,7 +11418,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G381" t="n">
-        <v>13.3514604568481</v>
+        <v>13.3514595031738</v>
       </c>
       <c r="H381" t="n">
         <v>2040539</v>
@@ -11447,7 +11447,7 @@
         <v>15</v>
       </c>
       <c r="G382" t="n">
-        <v>13.3782157897949</v>
+        <v>13.3782148361206</v>
       </c>
       <c r="H382" t="n">
         <v>1369844</v>
@@ -11505,7 +11505,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>12.9768686294556</v>
+        <v>12.9768695831299</v>
       </c>
       <c r="H384" t="n">
         <v>1473295</v>
@@ -11679,7 +11679,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>13.4228105545044</v>
+        <v>13.4228086471558</v>
       </c>
       <c r="H390" t="n">
         <v>881656</v>
@@ -11708,7 +11708,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G391" t="n">
-        <v>13.4763212203979</v>
+        <v>13.4763221740723</v>
       </c>
       <c r="H391" t="n">
         <v>1172805</v>
@@ -11737,7 +11737,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G392" t="n">
-        <v>13.6190233230591</v>
+        <v>13.6190242767334</v>
       </c>
       <c r="H392" t="n">
         <v>1539994</v>
@@ -11766,7 +11766,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G393" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298347473145</v>
       </c>
       <c r="H393" t="n">
         <v>1165777</v>
@@ -11795,7 +11795,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G394" t="n">
-        <v>13.8687515258789</v>
+        <v>13.8687496185303</v>
       </c>
       <c r="H394" t="n">
         <v>3091615</v>
@@ -11824,7 +11824,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G395" t="n">
-        <v>13.8955068588257</v>
+        <v>13.8955059051514</v>
       </c>
       <c r="H395" t="n">
         <v>1276247</v>
@@ -11853,7 +11853,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G396" t="n">
-        <v>13.699291229248</v>
+        <v>13.6992931365967</v>
       </c>
       <c r="H396" t="n">
         <v>972050</v>
@@ -11911,7 +11911,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>13.6457815170288</v>
+        <v>13.6457796096802</v>
       </c>
       <c r="H398" t="n">
         <v>1284758</v>
@@ -11940,7 +11940,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G399" t="n">
-        <v>13.4317283630371</v>
+        <v>13.4317293167114</v>
       </c>
       <c r="H399" t="n">
         <v>1069477</v>
@@ -11969,7 +11969,7 @@
         <v>15</v>
       </c>
       <c r="G400" t="n">
-        <v>13.3782157897949</v>
+        <v>13.3782148361206</v>
       </c>
       <c r="H400" t="n">
         <v>882574</v>
@@ -11998,7 +11998,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G401" t="n">
-        <v>13.8330755233765</v>
+        <v>13.8330745697021</v>
       </c>
       <c r="H401" t="n">
         <v>1558110</v>
@@ -12027,7 +12027,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G402" t="n">
-        <v>13.6814546585083</v>
+        <v>13.6814556121826</v>
       </c>
       <c r="H402" t="n">
         <v>1142327</v>
@@ -12056,7 +12056,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G403" t="n">
-        <v>13.7260494232178</v>
+        <v>13.7260503768921</v>
       </c>
       <c r="H403" t="n">
         <v>1460488</v>
@@ -12085,7 +12085,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>13.396053314209</v>
+        <v>13.3960542678833</v>
       </c>
       <c r="H404" t="n">
         <v>1802070</v>
@@ -12114,7 +12114,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G405" t="n">
-        <v>13.1374082565308</v>
+        <v>13.1374073028564</v>
       </c>
       <c r="H405" t="n">
         <v>3328937</v>
@@ -12172,7 +12172,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G407" t="n">
-        <v>12.9857873916626</v>
+        <v>12.9857883453369</v>
       </c>
       <c r="H407" t="n">
         <v>1108889</v>
@@ -12201,7 +12201,7 @@
         <v>14.5</v>
       </c>
       <c r="G408" t="n">
-        <v>12.9322748184204</v>
+        <v>12.9322738647461</v>
       </c>
       <c r="H408" t="n">
         <v>1544051</v>
@@ -12230,7 +12230,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G409" t="n">
-        <v>13.1195707321167</v>
+        <v>13.1195697784424</v>
       </c>
       <c r="H409" t="n">
         <v>1210092</v>
@@ -12259,7 +12259,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G410" t="n">
-        <v>13.021463394165</v>
+        <v>13.0214643478394</v>
       </c>
       <c r="H410" t="n">
         <v>1439867</v>
@@ -12288,7 +12288,7 @@
         <v>14.5</v>
       </c>
       <c r="G411" t="n">
-        <v>12.9322748184204</v>
+        <v>12.9322738647461</v>
       </c>
       <c r="H411" t="n">
         <v>1309342</v>
@@ -12375,7 +12375,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G414" t="n">
-        <v>12.6914653778076</v>
+        <v>12.6914663314819</v>
       </c>
       <c r="H414" t="n">
         <v>1172770</v>
@@ -12404,7 +12404,7 @@
         <v>14.5</v>
       </c>
       <c r="G415" t="n">
-        <v>12.9322748184204</v>
+        <v>12.9322738647461</v>
       </c>
       <c r="H415" t="n">
         <v>799316</v>
@@ -12462,7 +12462,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G417" t="n">
-        <v>12.9144382476807</v>
+        <v>12.9144372940063</v>
       </c>
       <c r="H417" t="n">
         <v>808214</v>
@@ -12491,7 +12491,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G418" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H418" t="n">
         <v>961936</v>
@@ -12520,7 +12520,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G419" t="n">
-        <v>12.7628192901611</v>
+        <v>12.7628173828125</v>
       </c>
       <c r="H419" t="n">
         <v>752397</v>
@@ -12549,7 +12549,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G420" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H420" t="n">
         <v>1200618</v>
@@ -12607,7 +12607,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G422" t="n">
-        <v>12.8787631988525</v>
+        <v>12.8787612915039</v>
       </c>
       <c r="H422" t="n">
         <v>1174396</v>
@@ -12665,7 +12665,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G424" t="n">
-        <v>12.7360610961914</v>
+        <v>12.7360620498657</v>
       </c>
       <c r="H424" t="n">
         <v>827022</v>
@@ -12723,7 +12723,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5755224227905</v>
+        <v>12.5755214691162</v>
       </c>
       <c r="H426" t="n">
         <v>919261</v>
@@ -12752,7 +12752,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6736288070679</v>
+        <v>12.6736316680908</v>
       </c>
       <c r="H427" t="n">
         <v>1810146</v>
@@ -12781,7 +12781,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G428" t="n">
-        <v>12.7538995742798</v>
+        <v>12.7538986206055</v>
       </c>
       <c r="H428" t="n">
         <v>890230</v>
@@ -12868,7 +12868,7 @@
         <v>14.75</v>
       </c>
       <c r="G431" t="n">
-        <v>13.1552457809448</v>
+        <v>13.1552448272705</v>
       </c>
       <c r="H431" t="n">
         <v>1739536</v>
@@ -12955,7 +12955,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G434" t="n">
-        <v>13.1195707321167</v>
+        <v>13.1195697784424</v>
       </c>
       <c r="H434" t="n">
         <v>1539196</v>
@@ -12984,7 +12984,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G435" t="n">
-        <v>13.2533531188965</v>
+        <v>13.2533521652222</v>
       </c>
       <c r="H435" t="n">
         <v>1643821</v>
@@ -13013,7 +13013,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G436" t="n">
-        <v>13.19983959198</v>
+        <v>13.1998386383057</v>
       </c>
       <c r="H436" t="n">
         <v>1622660</v>
@@ -13042,7 +13042,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G437" t="n">
-        <v>13.1374082565308</v>
+        <v>13.1374073028564</v>
       </c>
       <c r="H437" t="n">
         <v>1475586</v>
@@ -13100,7 +13100,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G439" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298347473145</v>
       </c>
       <c r="H439" t="n">
         <v>1896965</v>
@@ -13129,7 +13129,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G440" t="n">
-        <v>13.5476741790771</v>
+        <v>13.5476732254028</v>
       </c>
       <c r="H440" t="n">
         <v>892732</v>
@@ -13158,7 +13158,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G441" t="n">
-        <v>13.6279430389404</v>
+        <v>13.6279420852661</v>
       </c>
       <c r="H441" t="n">
         <v>1149434</v>
@@ -13187,7 +13187,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G442" t="n">
-        <v>13.699291229248</v>
+        <v>13.6992931365967</v>
       </c>
       <c r="H442" t="n">
         <v>1119754</v>
@@ -13216,7 +13216,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G443" t="n">
-        <v>13.6814546585083</v>
+        <v>13.6814556121826</v>
       </c>
       <c r="H443" t="n">
         <v>1071717</v>
@@ -13245,7 +13245,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G444" t="n">
-        <v>13.7438859939575</v>
+        <v>13.7438869476318</v>
       </c>
       <c r="H444" t="n">
         <v>1246334</v>
@@ -13274,7 +13274,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G445" t="n">
-        <v>13.9490194320679</v>
+        <v>13.9490213394165</v>
       </c>
       <c r="H445" t="n">
         <v>2748282</v>
@@ -13303,7 +13303,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G446" t="n">
-        <v>14.1452341079712</v>
+        <v>14.1452322006226</v>
       </c>
       <c r="H446" t="n">
         <v>2624938</v>
@@ -13332,7 +13332,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G447" t="n">
-        <v>14.2165832519531</v>
+        <v>14.2165842056274</v>
       </c>
       <c r="H447" t="n">
         <v>1949791</v>
@@ -13390,7 +13390,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G449" t="n">
-        <v>14.1630716323853</v>
+        <v>14.1630706787109</v>
       </c>
       <c r="H449" t="n">
         <v>1213953</v>
@@ -13448,7 +13448,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G451" t="n">
-        <v>13.9311809539795</v>
+        <v>13.9311819076538</v>
       </c>
       <c r="H451" t="n">
         <v>1658235</v>
@@ -13477,7 +13477,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G452" t="n">
-        <v>13.8419942855835</v>
+        <v>13.8419952392578</v>
       </c>
       <c r="H452" t="n">
         <v>1439516</v>
@@ -13506,7 +13506,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G453" t="n">
-        <v>13.9311809539795</v>
+        <v>13.9311819076538</v>
       </c>
       <c r="H453" t="n">
         <v>2026054</v>
@@ -13535,7 +13535,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G454" t="n">
-        <v>13.8776693344116</v>
+        <v>13.8776683807373</v>
       </c>
       <c r="H454" t="n">
         <v>1060888</v>
@@ -13622,7 +13622,7 @@
         <v>15.25</v>
       </c>
       <c r="G457" t="n">
-        <v>13.6011867523193</v>
+        <v>13.601185798645</v>
       </c>
       <c r="H457" t="n">
         <v>1029961</v>
@@ -13651,7 +13651,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G458" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298347473145</v>
       </c>
       <c r="H458" t="n">
         <v>1139099</v>
@@ -13680,7 +13680,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G459" t="n">
-        <v>13.6190233230591</v>
+        <v>13.6190242767334</v>
       </c>
       <c r="H459" t="n">
         <v>950220</v>
@@ -13709,7 +13709,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G460" t="n">
-        <v>13.4674053192139</v>
+        <v>13.4674034118652</v>
       </c>
       <c r="H460" t="n">
         <v>1451050</v>
@@ -13738,7 +13738,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G461" t="n">
-        <v>13.4228105545044</v>
+        <v>13.4228086471558</v>
       </c>
       <c r="H461" t="n">
         <v>1461100</v>
@@ -13767,7 +13767,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G462" t="n">
-        <v>13.1195707321167</v>
+        <v>13.1195697784424</v>
       </c>
       <c r="H462" t="n">
         <v>2806347</v>
@@ -13796,7 +13796,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G463" t="n">
-        <v>13.3425407409668</v>
+        <v>13.3425397872925</v>
       </c>
       <c r="H463" t="n">
         <v>1579075</v>
@@ -13883,7 +13883,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G466" t="n">
-        <v>13.5922660827637</v>
+        <v>13.592267036438</v>
       </c>
       <c r="H466" t="n">
         <v>3119148</v>
@@ -13912,7 +13912,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G467" t="n">
-        <v>13.5298357009888</v>
+        <v>13.5298347473145</v>
       </c>
       <c r="H467" t="n">
         <v>2035246</v>
@@ -13970,7 +13970,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>13.1463270187378</v>
+        <v>13.1463260650635</v>
       </c>
       <c r="H469" t="n">
         <v>1545554</v>
@@ -14028,7 +14028,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G471" t="n">
-        <v>13.396053314209</v>
+        <v>13.3960542678833</v>
       </c>
       <c r="H471" t="n">
         <v>1029473</v>
@@ -14057,7 +14057,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G472" t="n">
-        <v>13.2533531188965</v>
+        <v>13.2533521652222</v>
       </c>
       <c r="H472" t="n">
         <v>829370</v>
@@ -14115,7 +14115,7 @@
         <v>14.75</v>
       </c>
       <c r="G474" t="n">
-        <v>13.1552457809448</v>
+        <v>13.1552448272705</v>
       </c>
       <c r="H474" t="n">
         <v>936482</v>
@@ -14173,7 +14173,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G476" t="n">
-        <v>12.7806549072266</v>
+        <v>12.7806558609009</v>
       </c>
       <c r="H476" t="n">
         <v>2665467</v>
@@ -14202,7 +14202,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G477" t="n">
-        <v>12.5844411849976</v>
+        <v>12.5844402313232</v>
       </c>
       <c r="H477" t="n">
         <v>2794404</v>
@@ -14231,7 +14231,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G478" t="n">
-        <v>9.87312316894531</v>
+        <v>9.873122215271</v>
       </c>
       <c r="H478" t="n">
         <v>21175561</v>
@@ -14289,7 +14289,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G480" t="n">
-        <v>8.99016189575195</v>
+        <v>8.99015998840332</v>
       </c>
       <c r="H480" t="n">
         <v>12813008</v>
@@ -14376,7 +14376,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G483" t="n">
-        <v>9.03475570678711</v>
+        <v>9.03475475311279</v>
       </c>
       <c r="H483" t="n">
         <v>6435953</v>
@@ -14434,7 +14434,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>9.2042121887207</v>
+        <v>9.20421123504639</v>
       </c>
       <c r="H485" t="n">
         <v>9191353</v>
@@ -14463,7 +14463,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G486" t="n">
-        <v>9.45393753051758</v>
+        <v>9.45393943786621</v>
       </c>
       <c r="H486" t="n">
         <v>9939606</v>
@@ -14492,7 +14492,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G487" t="n">
-        <v>9.38259029388428</v>
+        <v>9.38258838653564</v>
       </c>
       <c r="H487" t="n">
         <v>4584999</v>
@@ -14579,7 +14579,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G490" t="n">
-        <v>9.07043170928955</v>
+        <v>9.07042980194092</v>
       </c>
       <c r="H490" t="n">
         <v>4790186</v>
@@ -14637,7 +14637,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G492" t="n">
-        <v>8.9544849395752</v>
+        <v>8.95448684692383</v>
       </c>
       <c r="H492" t="n">
         <v>8003564</v>
@@ -14666,7 +14666,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>8.84746074676514</v>
+        <v>8.84745979309082</v>
       </c>
       <c r="H493" t="n">
         <v>4822026</v>
@@ -14695,7 +14695,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G494" t="n">
-        <v>8.78502941131592</v>
+        <v>8.7850284576416</v>
       </c>
       <c r="H494" t="n">
         <v>3373268</v>
@@ -14724,7 +14724,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G495" t="n">
-        <v>8.77610969543457</v>
+        <v>8.77611064910889</v>
       </c>
       <c r="H495" t="n">
         <v>2458161</v>
@@ -14753,7 +14753,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G496" t="n">
-        <v>8.85637760162354</v>
+        <v>8.85637855529785</v>
       </c>
       <c r="H496" t="n">
         <v>3536091</v>
@@ -14811,7 +14811,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>8.90989112854004</v>
+        <v>8.90989303588867</v>
       </c>
       <c r="H498" t="n">
         <v>2806495</v>
@@ -14840,7 +14840,7 @@
         <v>10</v>
       </c>
       <c r="G499" t="n">
-        <v>8.91880989074707</v>
+        <v>8.91881084442139</v>
       </c>
       <c r="H499" t="n">
         <v>13009110</v>
@@ -14869,7 +14869,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G500" t="n">
-        <v>8.99016189575195</v>
+        <v>8.99015998840332</v>
       </c>
       <c r="H500" t="n">
         <v>6595063</v>
@@ -14898,7 +14898,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G501" t="n">
-        <v>8.91435050964355</v>
+        <v>8.91435146331787</v>
       </c>
       <c r="H501" t="n">
         <v>4022185</v>
@@ -14956,7 +14956,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>8.8430004119873</v>
+        <v>8.84300136566162</v>
       </c>
       <c r="H503" t="n">
         <v>3901455</v>
@@ -14985,7 +14985,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G504" t="n">
-        <v>9.10610485076904</v>
+        <v>9.10610580444336</v>
       </c>
       <c r="H504" t="n">
         <v>3493253</v>
@@ -15101,7 +15101,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>8.8430004119873</v>
+        <v>8.84300136566162</v>
       </c>
       <c r="H508" t="n">
         <v>2434687</v>
@@ -15159,7 +15159,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G510" t="n">
-        <v>8.89651298522949</v>
+        <v>8.89651393890381</v>
       </c>
       <c r="H510" t="n">
         <v>1521171</v>
@@ -15188,7 +15188,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G511" t="n">
-        <v>8.84746074676514</v>
+        <v>8.84745979309082</v>
       </c>
       <c r="H511" t="n">
         <v>1755113</v>
@@ -15217,7 +15217,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G512" t="n">
-        <v>8.99016189575195</v>
+        <v>8.99015998840332</v>
       </c>
       <c r="H512" t="n">
         <v>2573923</v>
@@ -15275,7 +15275,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G514" t="n">
-        <v>9.26664352416992</v>
+        <v>9.26664447784424</v>
       </c>
       <c r="H514" t="n">
         <v>6747917</v>
@@ -15304,7 +15304,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>9.27556228637695</v>
+        <v>9.27556133270264</v>
       </c>
       <c r="H515" t="n">
         <v>4945914</v>
@@ -15362,7 +15362,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G517" t="n">
-        <v>9.64123439788818</v>
+        <v>9.6412353515625</v>
       </c>
       <c r="H517" t="n">
         <v>5689408</v>
@@ -15391,7 +15391,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G518" t="n">
-        <v>9.72150421142578</v>
+        <v>9.72150325775146</v>
       </c>
       <c r="H518" t="n">
         <v>5821433</v>
@@ -15420,7 +15420,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G519" t="n">
-        <v>9.69474792480469</v>
+        <v>9.69474601745605</v>
       </c>
       <c r="H519" t="n">
         <v>3495085</v>
@@ -15478,7 +15478,7 @@
         <v>11</v>
       </c>
       <c r="G521" t="n">
-        <v>9.81069183349609</v>
+        <v>9.81068992614746</v>
       </c>
       <c r="H521" t="n">
         <v>4088060</v>
@@ -15507,7 +15507,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G522" t="n">
-        <v>9.87312316894531</v>
+        <v>9.873122215271</v>
       </c>
       <c r="H522" t="n">
         <v>5938827</v>
@@ -15565,7 +15565,7 @@
         <v>11.25</v>
       </c>
       <c r="G524" t="n">
-        <v>10.0336618423462</v>
+        <v>10.0336608886719</v>
       </c>
       <c r="H524" t="n">
         <v>3876046</v>
@@ -15594,7 +15594,7 @@
         <v>11.25</v>
       </c>
       <c r="G525" t="n">
-        <v>10.0336618423462</v>
+        <v>10.0336608886719</v>
       </c>
       <c r="H525" t="n">
         <v>4050673</v>
@@ -15623,7 +15623,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G526" t="n">
-        <v>10.0693368911743</v>
+        <v>10.0693387985229</v>
       </c>
       <c r="H526" t="n">
         <v>2760848</v>
@@ -15652,7 +15652,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G527" t="n">
-        <v>9.95339202880859</v>
+        <v>9.95339393615723</v>
       </c>
       <c r="H527" t="n">
         <v>5070746</v>
@@ -15681,7 +15681,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G528" t="n">
-        <v>9.77501583099365</v>
+        <v>9.77501678466797</v>
       </c>
       <c r="H528" t="n">
         <v>3334666</v>
@@ -15739,7 +15739,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>9.89988040924072</v>
+        <v>9.89987945556641</v>
       </c>
       <c r="H530" t="n">
         <v>4313672</v>
@@ -15797,7 +15797,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G532" t="n">
-        <v>8.84924221038818</v>
+        <v>8.84924411773682</v>
       </c>
       <c r="H532" t="n">
         <v>28012157</v>
@@ -15913,7 +15913,7 @@
         <v>9.16199970245361</v>
       </c>
       <c r="G536" t="n">
-        <v>8.17141532897949</v>
+        <v>8.17141437530518</v>
       </c>
       <c r="H536" t="n">
         <v>9673761</v>
@@ -15942,7 +15942,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>7.94665956497192</v>
+        <v>7.94666004180908</v>
       </c>
       <c r="H537" t="n">
         <v>9729894</v>
@@ -15971,7 +15971,7 @@
         <v>9.05599975585938</v>
       </c>
       <c r="G538" t="n">
-        <v>8.07687377929688</v>
+        <v>8.07687473297119</v>
       </c>
       <c r="H538" t="n">
         <v>4594941</v>
@@ -16029,7 +16029,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G540" t="n">
-        <v>7.75044536590576</v>
+        <v>7.75044679641724</v>
       </c>
       <c r="H540" t="n">
         <v>5162861</v>
@@ -16058,7 +16058,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G541" t="n">
-        <v>7.70585203170776</v>
+        <v>7.70585346221924</v>
       </c>
       <c r="H541" t="n">
         <v>4115086</v>
@@ -16087,7 +16087,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G542" t="n">
-        <v>7.50071954727173</v>
+        <v>7.50072002410889</v>
       </c>
       <c r="H542" t="n">
         <v>5780128</v>
@@ -16116,7 +16116,7 @@
         <v>8.80200004577637</v>
       </c>
       <c r="G543" t="n">
-        <v>7.85033750534058</v>
+        <v>7.8503360748291</v>
       </c>
       <c r="H543" t="n">
         <v>6134066</v>
@@ -16174,7 +16174,7 @@
         <v>9.0620002746582</v>
       </c>
       <c r="G545" t="n">
-        <v>8.08222675323486</v>
+        <v>8.08222579956055</v>
       </c>
       <c r="H545" t="n">
         <v>3191785</v>
@@ -16290,7 +16290,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G549" t="n">
-        <v>7.85747289657593</v>
+        <v>7.85747194290161</v>
       </c>
       <c r="H549" t="n">
         <v>4758272</v>
@@ -16319,7 +16319,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G550" t="n">
-        <v>7.92882204055786</v>
+        <v>7.92882394790649</v>
       </c>
       <c r="H550" t="n">
         <v>2441477</v>
@@ -16377,7 +16377,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G552" t="n">
-        <v>7.85747289657593</v>
+        <v>7.85747194290161</v>
       </c>
       <c r="H552" t="n">
         <v>3339024</v>
@@ -16406,7 +16406,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G553" t="n">
-        <v>7.89314842224121</v>
+        <v>7.89314746856689</v>
       </c>
       <c r="H553" t="n">
         <v>4193139</v>
@@ -16435,7 +16435,7 @@
         <v>8.83800029754639</v>
       </c>
       <c r="G554" t="n">
-        <v>7.88244485855103</v>
+        <v>7.88244438171387</v>
       </c>
       <c r="H554" t="n">
         <v>3631493</v>
@@ -16464,7 +16464,7 @@
         <v>8.58199977874756</v>
       </c>
       <c r="G555" t="n">
-        <v>7.65412378311157</v>
+        <v>7.6541223526001</v>
       </c>
       <c r="H555" t="n">
         <v>4425706</v>
@@ -16493,7 +16493,7 @@
         <v>8.63399982452393</v>
       </c>
       <c r="G556" t="n">
-        <v>7.70050191879272</v>
+        <v>7.70049953460693</v>
       </c>
       <c r="H556" t="n">
         <v>3573812</v>
@@ -16522,7 +16522,7 @@
         <v>8.79800033569336</v>
       </c>
       <c r="G557" t="n">
-        <v>7.84677028656006</v>
+        <v>7.84676885604858</v>
       </c>
       <c r="H557" t="n">
         <v>4340632</v>
@@ -16551,7 +16551,7 @@
         <v>8.8120002746582</v>
       </c>
       <c r="G558" t="n">
-        <v>7.85925722122192</v>
+        <v>7.85925483703613</v>
       </c>
       <c r="H558" t="n">
         <v>2984819</v>
@@ -16580,7 +16580,7 @@
         <v>8.98200035095215</v>
       </c>
       <c r="G559" t="n">
-        <v>8.01087665557861</v>
+        <v>8.0108757019043</v>
       </c>
       <c r="H559" t="n">
         <v>4147169</v>
@@ -16638,7 +16638,7 @@
         <v>9.25800037384033</v>
       </c>
       <c r="G561" t="n">
-        <v>8.25703525543213</v>
+        <v>8.25703430175781</v>
       </c>
       <c r="H561" t="n">
         <v>4323346</v>
@@ -16667,7 +16667,7 @@
         <v>9.1540002822876</v>
       </c>
       <c r="G562" t="n">
-        <v>8.16427993774414</v>
+        <v>8.16427898406982</v>
       </c>
       <c r="H562" t="n">
         <v>5619320</v>
@@ -16696,7 +16696,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G563" t="n">
-        <v>8.30341243743896</v>
+        <v>8.30341339111328</v>
       </c>
       <c r="H563" t="n">
         <v>8780937</v>
@@ -16725,7 +16725,7 @@
         <v>9.5319995880127</v>
       </c>
       <c r="G564" t="n">
-        <v>8.50140857696533</v>
+        <v>8.50141048431396</v>
       </c>
       <c r="H564" t="n">
         <v>8941584</v>
@@ -16783,7 +16783,7 @@
         <v>9.41800022125244</v>
       </c>
       <c r="G566" t="n">
-        <v>8.39973545074463</v>
+        <v>8.39973449707031</v>
       </c>
       <c r="H566" t="n">
         <v>3478216</v>
@@ -16812,7 +16812,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>8.43719387054443</v>
+        <v>8.43719482421875</v>
       </c>
       <c r="H567" t="n">
         <v>3835013</v>
@@ -16841,7 +16841,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G568" t="n">
-        <v>8.37476444244385</v>
+        <v>8.37476348876953</v>
       </c>
       <c r="H568" t="n">
         <v>3306888</v>
@@ -16870,7 +16870,7 @@
         <v>9.21399974822998</v>
       </c>
       <c r="G569" t="n">
-        <v>8.2177906036377</v>
+        <v>8.21779155731201</v>
       </c>
       <c r="H569" t="n">
         <v>3965117</v>
@@ -16899,7 +16899,7 @@
         <v>9.40200042724609</v>
       </c>
       <c r="G570" t="n">
-        <v>8.38546562194824</v>
+        <v>8.38546657562256</v>
       </c>
       <c r="H570" t="n">
         <v>5271863</v>
@@ -16928,7 +16928,7 @@
         <v>9.33600044250488</v>
       </c>
       <c r="G571" t="n">
-        <v>8.3266019821167</v>
+        <v>8.32660293579102</v>
       </c>
       <c r="H571" t="n">
         <v>4722488</v>
@@ -16957,7 +16957,7 @@
         <v>9.51599979400635</v>
       </c>
       <c r="G572" t="n">
-        <v>8.48714065551758</v>
+        <v>8.48713970184326</v>
       </c>
       <c r="H572" t="n">
         <v>7114474</v>
@@ -16986,7 +16986,7 @@
         <v>9.39599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>8.38011360168457</v>
+        <v>8.38011455535889</v>
       </c>
       <c r="H573" t="n">
         <v>3926210</v>
@@ -17073,7 +17073,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G576" t="n">
-        <v>8.10719966888428</v>
+        <v>8.10719776153564</v>
       </c>
       <c r="H576" t="n">
         <v>3501842</v>
@@ -17160,7 +17160,7 @@
         <v>9.43200016021729</v>
       </c>
       <c r="G579" t="n">
-        <v>8.41222286224365</v>
+        <v>8.41222190856934</v>
       </c>
       <c r="H579" t="n">
         <v>3334097</v>
@@ -17189,7 +17189,7 @@
         <v>9.52400016784668</v>
       </c>
       <c r="G580" t="n">
-        <v>8.49427700042725</v>
+        <v>8.49427509307861</v>
       </c>
       <c r="H580" t="n">
         <v>3785569</v>
@@ -17247,7 +17247,7 @@
         <v>9.44200038909912</v>
       </c>
       <c r="G582" t="n">
-        <v>8.42114162445068</v>
+        <v>8.42114067077637</v>
       </c>
       <c r="H582" t="n">
         <v>2590090</v>
@@ -17276,7 +17276,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G583" t="n">
-        <v>8.36941051483154</v>
+        <v>8.36941146850586</v>
       </c>
       <c r="H583" t="n">
         <v>2171988</v>
@@ -17363,7 +17363,7 @@
         <v>9.76599979400635</v>
       </c>
       <c r="G586" t="n">
-        <v>8.71011066436768</v>
+        <v>8.71010971069336</v>
       </c>
       <c r="H586" t="n">
         <v>5913671</v>
@@ -17392,7 +17392,7 @@
         <v>9.91600036621094</v>
       </c>
       <c r="G587" t="n">
-        <v>8.84389400482178</v>
+        <v>8.84389114379883</v>
       </c>
       <c r="H587" t="n">
         <v>6716654</v>
@@ -17537,7 +17537,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G592" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H592" t="n">
         <v>2804373</v>
@@ -17566,7 +17566,7 @@
         <v>9.5</v>
       </c>
       <c r="G593" t="n">
-        <v>8.47286891937256</v>
+        <v>8.47286987304688</v>
       </c>
       <c r="H593" t="n">
         <v>5164546</v>
@@ -17595,7 +17595,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G594" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H594" t="n">
         <v>3333128</v>
@@ -17624,7 +17624,7 @@
         <v>9.77799987792969</v>
       </c>
       <c r="G595" t="n">
-        <v>8.7208137512207</v>
+        <v>8.72081184387207</v>
       </c>
       <c r="H595" t="n">
         <v>5731605</v>
@@ -17682,7 +17682,7 @@
         <v>9.71399974822998</v>
       </c>
       <c r="G597" t="n">
-        <v>8.66373157501221</v>
+        <v>8.66373348236084</v>
       </c>
       <c r="H597" t="n">
         <v>3019517</v>
@@ -17740,7 +17740,7 @@
         <v>9.65200042724609</v>
       </c>
       <c r="G599" t="n">
-        <v>8.60843658447266</v>
+        <v>8.60843753814697</v>
       </c>
       <c r="H599" t="n">
         <v>7238113</v>
@@ -17769,7 +17769,7 @@
         <v>9.94400024414062</v>
       </c>
       <c r="G600" t="n">
-        <v>8.86886596679688</v>
+        <v>8.86886501312256</v>
       </c>
       <c r="H600" t="n">
         <v>12698570</v>
@@ -17798,7 +17798,7 @@
         <v>9.61200046539307</v>
       </c>
       <c r="G601" t="n">
-        <v>8.57276058197021</v>
+        <v>8.57276153564453</v>
       </c>
       <c r="H601" t="n">
         <v>5273474</v>
@@ -17827,7 +17827,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G602" t="n">
-        <v>8.57097625732422</v>
+        <v>8.57097721099854</v>
       </c>
       <c r="H602" t="n">
         <v>3968018</v>
@@ -17914,7 +17914,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G605" t="n">
-        <v>8.23919677734375</v>
+        <v>8.23919868469238</v>
       </c>
       <c r="H605" t="n">
         <v>5821027</v>
@@ -17943,7 +17943,7 @@
         <v>9.2480001449585</v>
       </c>
       <c r="G606" t="n">
-        <v>8.24811553955078</v>
+        <v>8.2481164932251</v>
       </c>
       <c r="H606" t="n">
         <v>3610072</v>
@@ -17972,7 +17972,7 @@
         <v>9.05599975585938</v>
       </c>
       <c r="G607" t="n">
-        <v>8.07687377929688</v>
+        <v>8.07687473297119</v>
       </c>
       <c r="H607" t="n">
         <v>5168239</v>
@@ -18030,7 +18030,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G609" t="n">
-        <v>8.09499359130859</v>
+        <v>8.09499168395996</v>
       </c>
       <c r="H609" t="n">
         <v>3993457</v>
@@ -18088,7 +18088,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G611" t="n">
-        <v>7.98991012573242</v>
+        <v>7.98990917205811</v>
       </c>
       <c r="H611" t="n">
         <v>3600020</v>
@@ -18117,7 +18117,7 @@
         <v>9.01200008392334</v>
       </c>
       <c r="G612" t="n">
-        <v>8.16383934020996</v>
+        <v>8.16383838653564</v>
       </c>
       <c r="H612" t="n">
         <v>5803732</v>
@@ -18146,7 +18146,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G613" t="n">
-        <v>7.96273422241211</v>
+        <v>7.96273326873779</v>
       </c>
       <c r="H613" t="n">
         <v>4828970</v>
@@ -18204,7 +18204,7 @@
         <v>8.55799961090088</v>
       </c>
       <c r="G615" t="n">
-        <v>7.75256776809692</v>
+        <v>7.75256729125977</v>
       </c>
       <c r="H615" t="n">
         <v>4986220</v>
@@ -18233,7 +18233,7 @@
         <v>8.72399997711182</v>
       </c>
       <c r="G616" t="n">
-        <v>7.90294408798218</v>
+        <v>7.90294599533081</v>
       </c>
       <c r="H616" t="n">
         <v>5006653</v>
@@ -18262,7 +18262,7 @@
         <v>8.98400020599365</v>
       </c>
       <c r="G617" t="n">
-        <v>8.1384744644165</v>
+        <v>8.13847351074219</v>
       </c>
       <c r="H617" t="n">
         <v>5092406</v>
@@ -18291,7 +18291,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G618" t="n">
-        <v>7.99715566635132</v>
+        <v>7.99715757369995</v>
       </c>
       <c r="H618" t="n">
         <v>2487892</v>
@@ -18320,7 +18320,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G619" t="n">
-        <v>7.97179317474365</v>
+        <v>7.97179269790649</v>
       </c>
       <c r="H619" t="n">
         <v>2900796</v>
@@ -18378,7 +18378,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G621" t="n">
-        <v>7.99715566635132</v>
+        <v>7.99715757369995</v>
       </c>
       <c r="H621" t="n">
         <v>2178737</v>
@@ -18407,7 +18407,7 @@
         <v>8.63799953460693</v>
       </c>
       <c r="G622" t="n">
-        <v>7.82503843307495</v>
+        <v>7.82503795623779</v>
       </c>
       <c r="H622" t="n">
         <v>2831931</v>
@@ -18436,7 +18436,7 @@
         <v>8.9680004119873</v>
       </c>
       <c r="G623" t="n">
-        <v>8.12398052215576</v>
+        <v>8.12398147583008</v>
       </c>
       <c r="H623" t="n">
         <v>3185635</v>
@@ -18465,7 +18465,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G624" t="n">
-        <v>8.17108726501465</v>
+        <v>8.17108631134033</v>
       </c>
       <c r="H624" t="n">
         <v>2679842</v>
@@ -18494,7 +18494,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G625" t="n">
-        <v>8.02070999145508</v>
+        <v>8.02071094512939</v>
       </c>
       <c r="H625" t="n">
         <v>3853950</v>
@@ -18523,7 +18523,7 @@
         <v>8.9980001449585</v>
       </c>
       <c r="G626" t="n">
-        <v>8.15115833282471</v>
+        <v>8.15115642547607</v>
       </c>
       <c r="H626" t="n">
         <v>3079935</v>
@@ -18610,7 +18610,7 @@
         <v>8.91800022125244</v>
       </c>
       <c r="G629" t="n">
-        <v>8.07868671417236</v>
+        <v>8.07868766784668</v>
       </c>
       <c r="H629" t="n">
         <v>1915648</v>
@@ -18639,7 +18639,7 @@
         <v>8.82400035858154</v>
       </c>
       <c r="G630" t="n">
-        <v>7.99353265762329</v>
+        <v>7.99353313446045</v>
       </c>
       <c r="H630" t="n">
         <v>1756558</v>
@@ -18726,7 +18726,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G633" t="n">
-        <v>7.72539043426514</v>
+        <v>7.72539138793945</v>
       </c>
       <c r="H633" t="n">
         <v>2314709</v>
@@ -18755,7 +18755,7 @@
         <v>8.35599994659424</v>
       </c>
       <c r="G634" t="n">
-        <v>7.56957817077637</v>
+        <v>7.56957864761353</v>
       </c>
       <c r="H634" t="n">
         <v>3989447</v>
@@ -18784,7 +18784,7 @@
         <v>8.4060001373291</v>
       </c>
       <c r="G635" t="n">
-        <v>7.61487340927124</v>
+        <v>7.61487293243408</v>
       </c>
       <c r="H635" t="n">
         <v>4986757</v>
@@ -18813,7 +18813,7 @@
         <v>8.35400009155273</v>
       </c>
       <c r="G636" t="n">
-        <v>7.56776809692383</v>
+        <v>7.56776762008667</v>
       </c>
       <c r="H636" t="n">
         <v>1819879</v>
@@ -18842,7 +18842,7 @@
         <v>8.46599960327148</v>
       </c>
       <c r="G637" t="n">
-        <v>7.66922616958618</v>
+        <v>7.66922664642334</v>
       </c>
       <c r="H637" t="n">
         <v>2273678</v>
@@ -18871,7 +18871,7 @@
         <v>8.36800003051758</v>
       </c>
       <c r="G638" t="n">
-        <v>7.58044958114624</v>
+        <v>7.58045053482056</v>
       </c>
       <c r="H638" t="n">
         <v>1802642</v>
@@ -18900,7 +18900,7 @@
         <v>8.59200000762939</v>
       </c>
       <c r="G639" t="n">
-        <v>7.78336906433105</v>
+        <v>7.7833685874939</v>
       </c>
       <c r="H639" t="n">
         <v>2776244</v>
@@ -18929,7 +18929,7 @@
         <v>8.55200004577637</v>
       </c>
       <c r="G640" t="n">
-        <v>7.74713182449341</v>
+        <v>7.74713230133057</v>
       </c>
       <c r="H640" t="n">
         <v>2228785</v>
@@ -18958,7 +18958,7 @@
         <v>8.62600040435791</v>
       </c>
       <c r="G641" t="n">
-        <v>7.81416749954224</v>
+        <v>7.81416845321655</v>
       </c>
       <c r="H641" t="n">
         <v>2218841</v>
@@ -18987,7 +18987,7 @@
         <v>8.57600021362305</v>
       </c>
       <c r="G642" t="n">
-        <v>7.76887369155884</v>
+        <v>7.76887464523315</v>
       </c>
       <c r="H642" t="n">
         <v>1760620</v>
@@ -19045,7 +19045,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>7.7724986076355</v>
+        <v>7.77249717712402</v>
       </c>
       <c r="H644" t="n">
         <v>1848109</v>
@@ -19074,7 +19074,7 @@
         <v>8.61400032043457</v>
       </c>
       <c r="G645" t="n">
-        <v>7.80329704284668</v>
+        <v>7.80329656600952</v>
       </c>
       <c r="H645" t="n">
         <v>2087020</v>
@@ -19103,7 +19103,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G646" t="n">
-        <v>7.79967403411865</v>
+        <v>7.79967308044434</v>
       </c>
       <c r="H646" t="n">
         <v>1396494</v>
@@ -19161,7 +19161,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G648" t="n">
-        <v>8.26711177825928</v>
+        <v>8.26711082458496</v>
       </c>
       <c r="H648" t="n">
         <v>4721642</v>
@@ -19219,7 +19219,7 @@
         <v>9.32600021362305</v>
       </c>
       <c r="G650" t="n">
-        <v>8.44828701019287</v>
+        <v>8.4482889175415</v>
       </c>
       <c r="H650" t="n">
         <v>3503864</v>
@@ -19248,7 +19248,7 @@
         <v>9.25399971008301</v>
       </c>
       <c r="G651" t="n">
-        <v>8.38306522369385</v>
+        <v>8.38306427001953</v>
       </c>
       <c r="H651" t="n">
         <v>2098527</v>
@@ -19306,7 +19306,7 @@
         <v>9.19799995422363</v>
       </c>
       <c r="G653" t="n">
-        <v>8.3323335647583</v>
+        <v>8.33233451843262</v>
       </c>
       <c r="H653" t="n">
         <v>1793417</v>
@@ -19364,7 +19364,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G655" t="n">
-        <v>8.3160285949707</v>
+        <v>8.31603050231934</v>
       </c>
       <c r="H655" t="n">
         <v>1925179</v>
@@ -19393,7 +19393,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>8.30696868896484</v>
+        <v>8.30696964263916</v>
       </c>
       <c r="H656" t="n">
         <v>1596274</v>
@@ -19480,7 +19480,7 @@
         <v>10.25</v>
       </c>
       <c r="G659" t="n">
-        <v>9.28532600402832</v>
+        <v>9.285325050354</v>
       </c>
       <c r="H659" t="n">
         <v>22838051</v>
@@ -19509,7 +19509,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G660" t="n">
-        <v>9.41667938232422</v>
+        <v>9.41668033599854</v>
       </c>
       <c r="H660" t="n">
         <v>10747679</v>
@@ -19567,7 +19567,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G662" t="n">
-        <v>9.49368000030518</v>
+        <v>9.49367904663086</v>
       </c>
       <c r="H662" t="n">
         <v>4563503</v>
@@ -19625,7 +19625,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G664" t="n">
-        <v>9.66579818725586</v>
+        <v>9.66579914093018</v>
       </c>
       <c r="H664" t="n">
         <v>2538552</v>
@@ -19683,7 +19683,7 @@
         <v>10.4849996566772</v>
       </c>
       <c r="G666" t="n">
-        <v>9.49820804595947</v>
+        <v>9.49820899963379</v>
       </c>
       <c r="H666" t="n">
         <v>3018997</v>
@@ -19799,7 +19799,7 @@
         <v>9.92199993133545</v>
       </c>
       <c r="G670" t="n">
-        <v>8.98819446563721</v>
+        <v>8.98819637298584</v>
       </c>
       <c r="H670" t="n">
         <v>2885745</v>
@@ -19886,7 +19886,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>8.96826648712158</v>
+        <v>8.96826553344727</v>
       </c>
       <c r="H673" t="n">
         <v>2141975</v>
@@ -19915,7 +19915,7 @@
         <v>9.8439998626709</v>
       </c>
       <c r="G674" t="n">
-        <v>8.91753578186035</v>
+        <v>8.91753673553467</v>
       </c>
       <c r="H674" t="n">
         <v>1706812</v>
@@ -19944,7 +19944,7 @@
         <v>9.77400016784668</v>
       </c>
       <c r="G675" t="n">
-        <v>8.85412406921387</v>
+        <v>8.85412502288818</v>
       </c>
       <c r="H675" t="n">
         <v>1344847</v>
@@ -20060,7 +20060,7 @@
         <v>10.0550003051758</v>
       </c>
       <c r="G679" t="n">
-        <v>9.10867881774902</v>
+        <v>9.10867786407471</v>
       </c>
       <c r="H679" t="n">
         <v>1802420</v>
@@ -20118,7 +20118,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G681" t="n">
-        <v>8.74179458618164</v>
+        <v>8.74179553985596</v>
       </c>
       <c r="H681" t="n">
         <v>1971830</v>
@@ -20147,7 +20147,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G682" t="n">
-        <v>8.76716041564941</v>
+        <v>8.76716136932373</v>
       </c>
       <c r="H682" t="n">
         <v>938438</v>
@@ -20176,7 +20176,7 @@
         <v>9.74600028991699</v>
       </c>
       <c r="G683" t="n">
-        <v>8.82876014709473</v>
+        <v>8.82875919342041</v>
       </c>
       <c r="H683" t="n">
         <v>2319787</v>
@@ -20234,7 +20234,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G685" t="n">
-        <v>8.84869003295898</v>
+        <v>8.84868907928467</v>
       </c>
       <c r="H685" t="n">
         <v>1981231</v>
@@ -20263,7 +20263,7 @@
         <v>9.73200035095215</v>
       </c>
       <c r="G686" t="n">
-        <v>8.81607818603516</v>
+        <v>8.81607723236084</v>
       </c>
       <c r="H686" t="n">
         <v>2305920</v>
@@ -20292,7 +20292,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G687" t="n">
-        <v>9.44838714599609</v>
+        <v>9.44838523864746</v>
       </c>
       <c r="H687" t="n">
         <v>7234743</v>
@@ -20350,7 +20350,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G689" t="n">
-        <v>9.4393253326416</v>
+        <v>9.43932628631592</v>
       </c>
       <c r="H689" t="n">
         <v>2744958</v>
@@ -20379,7 +20379,7 @@
         <v>10.2849998474121</v>
       </c>
       <c r="G690" t="n">
-        <v>9.31703186035156</v>
+        <v>9.31703090667725</v>
       </c>
       <c r="H690" t="n">
         <v>1963989</v>
@@ -20408,7 +20408,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G691" t="n">
-        <v>9.29438591003418</v>
+        <v>9.29438495635986</v>
       </c>
       <c r="H691" t="n">
         <v>2028089</v>
@@ -20466,7 +20466,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G693" t="n">
-        <v>9.47556114196777</v>
+        <v>9.47556209564209</v>
       </c>
       <c r="H693" t="n">
         <v>3031050</v>
@@ -20524,7 +20524,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G695" t="n">
-        <v>9.69750308990479</v>
+        <v>9.69750499725342</v>
       </c>
       <c r="H695" t="n">
         <v>4577729</v>
@@ -20553,7 +20553,7 @@
         <v>10.6450004577637</v>
       </c>
       <c r="G696" t="n">
-        <v>9.64315032958984</v>
+        <v>9.64315223693848</v>
       </c>
       <c r="H696" t="n">
         <v>2913264</v>
@@ -20640,7 +20640,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>9.78356266021729</v>
+        <v>9.7835636138916</v>
       </c>
       <c r="H699" t="n">
         <v>2814547</v>
@@ -20669,7 +20669,7 @@
         <v>10.7650003433228</v>
       </c>
       <c r="G700" t="n">
-        <v>9.75185680389404</v>
+        <v>9.75185775756836</v>
       </c>
       <c r="H700" t="n">
         <v>3227727</v>
@@ -20698,7 +20698,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G701" t="n">
-        <v>9.40309143066406</v>
+        <v>9.40309047698975</v>
       </c>
       <c r="H701" t="n">
         <v>5041512</v>
@@ -20814,7 +20814,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G705" t="n">
-        <v>9.69750308990479</v>
+        <v>9.69750499725342</v>
       </c>
       <c r="H705" t="n">
         <v>3067747</v>
@@ -20843,7 +20843,7 @@
         <v>10.3649997711182</v>
       </c>
       <c r="G706" t="n">
-        <v>9.38950252532959</v>
+        <v>9.38950157165527</v>
       </c>
       <c r="H706" t="n">
         <v>4405879</v>
@@ -20872,7 +20872,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G707" t="n">
-        <v>9.22644329071045</v>
+        <v>9.22644424438477</v>
       </c>
       <c r="H707" t="n">
         <v>3415947</v>
@@ -20930,7 +20930,7 @@
         <v>10.0649995803833</v>
       </c>
       <c r="G709" t="n">
-        <v>9.11773681640625</v>
+        <v>9.11773777008057</v>
       </c>
       <c r="H709" t="n">
         <v>1917820</v>
@@ -20959,7 +20959,7 @@
         <v>9.79800033569336</v>
       </c>
       <c r="G710" t="n">
-        <v>8.87586688995361</v>
+        <v>8.87586784362793</v>
       </c>
       <c r="H710" t="n">
         <v>4086616</v>
@@ -21017,7 +21017,7 @@
         <v>9.81400012969971</v>
       </c>
       <c r="G712" t="n">
-        <v>8.89036178588867</v>
+        <v>8.89035987854004</v>
       </c>
       <c r="H712" t="n">
         <v>1752282</v>
@@ -21075,7 +21075,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G714" t="n">
-        <v>9.31250286102295</v>
+        <v>9.31250095367432</v>
       </c>
       <c r="H714" t="n">
         <v>2308211</v>
@@ -21104,7 +21104,7 @@
         <v>10.0550003051758</v>
       </c>
       <c r="G715" t="n">
-        <v>9.10867881774902</v>
+        <v>9.10867786407471</v>
       </c>
       <c r="H715" t="n">
         <v>3702185</v>
@@ -21191,7 +21191,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G718" t="n">
-        <v>8.9048547744751</v>
+        <v>8.90485382080078</v>
       </c>
       <c r="H718" t="n">
         <v>3071768</v>
@@ -21220,7 +21220,7 @@
         <v>9.76799964904785</v>
       </c>
       <c r="G719" t="n">
-        <v>8.84869003295898</v>
+        <v>8.84868907928467</v>
       </c>
       <c r="H719" t="n">
         <v>2361462</v>
@@ -21249,7 +21249,7 @@
         <v>9.97599983215332</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03711223602295</v>
+        <v>9.03711318969727</v>
       </c>
       <c r="H720" t="n">
         <v>1979478</v>
@@ -21336,7 +21336,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G723" t="n">
-        <v>8.50082969665527</v>
+        <v>8.50082874298096</v>
       </c>
       <c r="H723" t="n">
         <v>6554136</v>
@@ -21394,7 +21394,7 @@
         <v>9.52200031280518</v>
       </c>
       <c r="G725" t="n">
-        <v>8.62584209442139</v>
+        <v>8.62584018707275</v>
       </c>
       <c r="H725" t="n">
         <v>2372344</v>
@@ -21423,7 +21423,7 @@
         <v>9.62600040435791</v>
       </c>
       <c r="G726" t="n">
-        <v>8.72005367279053</v>
+        <v>8.72005462646484</v>
       </c>
       <c r="H726" t="n">
         <v>2518578</v>
@@ -21452,7 +21452,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G727" t="n">
-        <v>8.65120506286621</v>
+        <v>8.65120601654053</v>
       </c>
       <c r="H727" t="n">
         <v>3252784</v>
@@ -21626,7 +21626,7 @@
         <v>9.06400012969971</v>
       </c>
       <c r="G733" t="n">
-        <v>8.21094512939453</v>
+        <v>8.21094608306885</v>
       </c>
       <c r="H733" t="n">
         <v>2998346</v>
@@ -21684,7 +21684,7 @@
         <v>8.60799980163574</v>
       </c>
       <c r="G735" t="n">
-        <v>7.7978630065918</v>
+        <v>7.79786205291748</v>
       </c>
       <c r="H735" t="n">
         <v>4239880</v>
@@ -21771,7 +21771,7 @@
         <v>8.22799968719482</v>
       </c>
       <c r="G738" t="n">
-        <v>7.45362567901611</v>
+        <v>7.45362520217896</v>
       </c>
       <c r="H738" t="n">
         <v>3779114</v>
@@ -21858,7 +21858,7 @@
         <v>8.39599990844727</v>
       </c>
       <c r="G741" t="n">
-        <v>7.6058144569397</v>
+        <v>7.60581493377686</v>
       </c>
       <c r="H741" t="n">
         <v>2355797</v>
@@ -21887,7 +21887,7 @@
         <v>8.56400012969971</v>
       </c>
       <c r="G742" t="n">
-        <v>7.75800323486328</v>
+        <v>7.75800275802612</v>
       </c>
       <c r="H742" t="n">
         <v>3764279</v>
@@ -21916,7 +21916,7 @@
         <v>8.61800003051758</v>
       </c>
       <c r="G743" t="n">
-        <v>7.80692052841187</v>
+        <v>7.80692195892334</v>
       </c>
       <c r="H743" t="n">
         <v>2413922</v>
@@ -21945,7 +21945,7 @@
         <v>8.53600025177002</v>
       </c>
       <c r="G744" t="n">
-        <v>7.73263740539551</v>
+        <v>7.73263883590698</v>
       </c>
       <c r="H744" t="n">
         <v>2387331</v>
@@ -21974,7 +21974,7 @@
         <v>8.65799999237061</v>
       </c>
       <c r="G745" t="n">
-        <v>7.8431568145752</v>
+        <v>7.84315586090088</v>
       </c>
       <c r="H745" t="n">
         <v>2320465</v>
@@ -22032,7 +22032,7 @@
         <v>8.9379997253418</v>
       </c>
       <c r="G747" t="n">
-        <v>8.09680461883545</v>
+        <v>8.09680366516113</v>
       </c>
       <c r="H747" t="n">
         <v>3198664</v>
@@ -22061,7 +22061,7 @@
         <v>8.75599956512451</v>
       </c>
       <c r="G748" t="n">
-        <v>7.93193244934082</v>
+        <v>7.93193340301514</v>
       </c>
       <c r="H748" t="n">
         <v>2812260</v>
@@ -22090,7 +22090,7 @@
         <v>8.66199970245361</v>
       </c>
       <c r="G749" t="n">
-        <v>7.84677934646606</v>
+        <v>7.84677982330322</v>
       </c>
       <c r="H749" t="n">
         <v>1424450</v>
@@ -22119,7 +22119,7 @@
         <v>8.28400039672852</v>
       </c>
       <c r="G750" t="n">
-        <v>7.50435495376587</v>
+        <v>7.50435638427734</v>
       </c>
       <c r="H750" t="n">
         <v>3458850</v>
@@ -22206,7 +22206,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G753" t="n">
-        <v>7.44094324111938</v>
+        <v>7.44094276428223</v>
       </c>
       <c r="H753" t="n">
         <v>2194306</v>
@@ -22235,7 +22235,7 @@
         <v>8.25599956512451</v>
       </c>
       <c r="G754" t="n">
-        <v>7.47899007797241</v>
+        <v>7.47899103164673</v>
       </c>
       <c r="H754" t="n">
         <v>2608803</v>
@@ -22264,7 +22264,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G755" t="n">
-        <v>7.41014337539673</v>
+        <v>7.41014385223389</v>
       </c>
       <c r="H755" t="n">
         <v>2607995</v>
@@ -22293,7 +22293,7 @@
         <v>8.16800022125244</v>
       </c>
       <c r="G756" t="n">
-        <v>7.39927291870117</v>
+        <v>7.39927244186401</v>
       </c>
       <c r="H756" t="n">
         <v>1951695</v>
@@ -22351,7 +22351,7 @@
         <v>8.14200019836426</v>
       </c>
       <c r="G758" t="n">
-        <v>7.37572002410889</v>
+        <v>7.37571954727173</v>
       </c>
       <c r="H758" t="n">
         <v>2303762</v>
@@ -22380,7 +22380,7 @@
         <v>8.25599956512451</v>
       </c>
       <c r="G759" t="n">
-        <v>7.47899007797241</v>
+        <v>7.47899103164673</v>
       </c>
       <c r="H759" t="n">
         <v>2442376</v>
@@ -22467,7 +22467,7 @@
         <v>7.58400011062622</v>
       </c>
       <c r="G762" t="n">
-        <v>6.87023544311523</v>
+        <v>6.87023591995239</v>
       </c>
       <c r="H762" t="n">
         <v>2216271</v>
@@ -22496,7 +22496,7 @@
         <v>7.67799997329712</v>
       </c>
       <c r="G763" t="n">
-        <v>6.95538806915283</v>
+        <v>6.95538854598999</v>
       </c>
       <c r="H763" t="n">
         <v>2149642</v>
@@ -22525,7 +22525,7 @@
         <v>7.68200016021729</v>
       </c>
       <c r="G764" t="n">
-        <v>6.95901250839233</v>
+        <v>6.95901203155518</v>
       </c>
       <c r="H764" t="n">
         <v>1573973</v>
@@ -22554,7 +22554,7 @@
         <v>7.50799989700317</v>
       </c>
       <c r="G765" t="n">
-        <v>6.80138731002808</v>
+        <v>6.80138826370239</v>
       </c>
       <c r="H765" t="n">
         <v>1747951</v>
@@ -22583,7 +22583,7 @@
         <v>7.81599998474121</v>
       </c>
       <c r="G766" t="n">
-        <v>7.08039999008179</v>
+        <v>7.08040046691895</v>
       </c>
       <c r="H766" t="n">
         <v>2365562</v>
@@ -22612,7 +22612,7 @@
         <v>7.81599998474121</v>
       </c>
       <c r="G767" t="n">
-        <v>7.08039999008179</v>
+        <v>7.08040046691895</v>
       </c>
       <c r="H767" t="n">
         <v>1496810</v>
@@ -22641,7 +22641,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G768" t="n">
-        <v>7.18004846572876</v>
+        <v>7.1800479888916</v>
       </c>
       <c r="H768" t="n">
         <v>3294614</v>
@@ -22728,7 +22728,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G771" t="n">
-        <v>7.20178937911987</v>
+        <v>7.20178890228271</v>
       </c>
       <c r="H771" t="n">
         <v>2210836</v>
@@ -22757,7 +22757,7 @@
         <v>7.76200008392334</v>
       </c>
       <c r="G772" t="n">
-        <v>7.0314826965332</v>
+        <v>7.03148221969604</v>
       </c>
       <c r="H772" t="n">
         <v>3369223</v>
@@ -22815,7 +22815,7 @@
         <v>7.62200021743774</v>
       </c>
       <c r="G774" t="n">
-        <v>6.90465927124023</v>
+        <v>6.90465879440308</v>
       </c>
       <c r="H774" t="n">
         <v>5108767</v>
@@ -22844,7 +22844,7 @@
         <v>7.59200000762939</v>
       </c>
       <c r="G775" t="n">
-        <v>6.87748146057129</v>
+        <v>6.87748241424561</v>
       </c>
       <c r="H775" t="n">
         <v>3293042</v>
@@ -22873,7 +22873,7 @@
         <v>7.89400005340576</v>
       </c>
       <c r="G776" t="n">
-        <v>7.15105962753296</v>
+        <v>7.15106010437012</v>
       </c>
       <c r="H776" t="n">
         <v>4776911</v>
@@ -22931,7 +22931,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G778" t="n">
-        <v>7.23440074920654</v>
+        <v>7.2344012260437</v>
       </c>
       <c r="H778" t="n">
         <v>2188156</v>
@@ -22960,7 +22960,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G779" t="n">
-        <v>7.22715425491333</v>
+        <v>7.22715330123901</v>
       </c>
       <c r="H779" t="n">
         <v>1886094</v>
@@ -22989,7 +22989,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G780" t="n">
-        <v>7.41014337539673</v>
+        <v>7.41014385223389</v>
       </c>
       <c r="H780" t="n">
         <v>2861698</v>
@@ -23018,7 +23018,7 @@
         <v>8.25399971008301</v>
       </c>
       <c r="G781" t="n">
-        <v>7.47717809677124</v>
+        <v>7.4771785736084</v>
       </c>
       <c r="H781" t="n">
         <v>2283036</v>
@@ -23047,7 +23047,7 @@
         <v>8.29800033569336</v>
       </c>
       <c r="G782" t="n">
-        <v>7.5170373916626</v>
+        <v>7.51703786849976</v>
       </c>
       <c r="H782" t="n">
         <v>1972278</v>
@@ -23076,7 +23076,7 @@
         <v>8.31799983978271</v>
       </c>
       <c r="G783" t="n">
-        <v>7.53515481948853</v>
+        <v>7.53515529632568</v>
       </c>
       <c r="H783" t="n">
         <v>1755442</v>
@@ -23192,7 +23192,7 @@
         <v>8.65200042724609</v>
       </c>
       <c r="G787" t="n">
-        <v>7.83772134780884</v>
+        <v>7.83772039413452</v>
       </c>
       <c r="H787" t="n">
         <v>2475916</v>
@@ -23221,7 +23221,7 @@
         <v>8.74199962615967</v>
       </c>
       <c r="G788" t="n">
-        <v>7.91925001144409</v>
+        <v>7.91925048828125</v>
       </c>
       <c r="H788" t="n">
         <v>2274975</v>
@@ -23250,7 +23250,7 @@
         <v>8.82800006866455</v>
       </c>
       <c r="G789" t="n">
-        <v>7.99715566635132</v>
+        <v>7.99715757369995</v>
       </c>
       <c r="H789" t="n">
         <v>1880027</v>
@@ -23279,7 +23279,7 @@
         <v>8.52799987792969</v>
       </c>
       <c r="G790" t="n">
-        <v>7.72539043426514</v>
+        <v>7.72539138793945</v>
       </c>
       <c r="H790" t="n">
         <v>3056968</v>
@@ -23308,7 +23308,7 @@
         <v>8.55200004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>7.74713182449341</v>
+        <v>7.74713230133057</v>
       </c>
       <c r="H791" t="n">
         <v>2848784</v>
@@ -23337,7 +23337,7 @@
         <v>8.66600036621094</v>
       </c>
       <c r="G792" t="n">
-        <v>7.85040473937988</v>
+        <v>7.85040330886841</v>
       </c>
       <c r="H792" t="n">
         <v>2619811</v>
@@ -23366,7 +23366,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G793" t="n">
-        <v>7.93555688858032</v>
+        <v>7.93555593490601</v>
       </c>
       <c r="H793" t="n">
         <v>2007671</v>
@@ -23424,7 +23424,7 @@
         <v>8.77400016784668</v>
       </c>
       <c r="G795" t="n">
-        <v>7.94823837280273</v>
+        <v>7.94823884963989</v>
       </c>
       <c r="H795" t="n">
         <v>1660764</v>
@@ -23453,7 +23453,7 @@
         <v>8.9040002822876</v>
       </c>
       <c r="G796" t="n">
-        <v>8.06600475311279</v>
+        <v>8.06600570678711</v>
       </c>
       <c r="H796" t="n">
         <v>2132260</v>
@@ -23482,7 +23482,7 @@
         <v>8.93200016021729</v>
       </c>
       <c r="G797" t="n">
-        <v>8.09136772155762</v>
+        <v>8.09136962890625</v>
       </c>
       <c r="H797" t="n">
         <v>1345983</v>
@@ -23511,7 +23511,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G798" t="n">
-        <v>7.97179317474365</v>
+        <v>7.97179269790649</v>
       </c>
       <c r="H798" t="n">
         <v>2156012</v>
@@ -23540,7 +23540,7 @@
         <v>8.91800022125244</v>
       </c>
       <c r="G799" t="n">
-        <v>8.07868671417236</v>
+        <v>8.07868766784668</v>
       </c>
       <c r="H799" t="n">
         <v>1599327</v>
@@ -23598,7 +23598,7 @@
         <v>8.75800037384033</v>
       </c>
       <c r="G801" t="n">
-        <v>7.93374586105347</v>
+        <v>7.93374490737915</v>
       </c>
       <c r="H801" t="n">
         <v>1519689</v>
@@ -23743,7 +23743,7 @@
         <v>8.8120002746582</v>
       </c>
       <c r="G806" t="n">
-        <v>7.98266220092773</v>
+        <v>7.98266315460205</v>
       </c>
       <c r="H806" t="n">
         <v>1977479</v>
@@ -23772,7 +23772,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G807" t="n">
-        <v>7.88120412826538</v>
+        <v>7.88120269775391</v>
       </c>
       <c r="H807" t="n">
         <v>2388161</v>
@@ -23801,7 +23801,7 @@
         <v>8.77600002288818</v>
       </c>
       <c r="G808" t="n">
-        <v>7.95004940032959</v>
+        <v>7.95005035400391</v>
       </c>
       <c r="H808" t="n">
         <v>1810253</v>
@@ -23859,7 +23859,7 @@
         <v>8.63000011444092</v>
       </c>
       <c r="G810" t="n">
-        <v>7.81779098510742</v>
+        <v>7.81779193878174</v>
       </c>
       <c r="H810" t="n">
         <v>2953314</v>
@@ -23888,7 +23888,7 @@
         <v>8.48200035095215</v>
       </c>
       <c r="G811" t="n">
-        <v>7.68372106552124</v>
+        <v>7.6837215423584</v>
       </c>
       <c r="H811" t="n">
         <v>2667919</v>
@@ -23917,7 +23917,7 @@
         <v>8.63599967956543</v>
       </c>
       <c r="G812" t="n">
-        <v>7.8232274055481</v>
+        <v>7.82322692871094</v>
       </c>
       <c r="H812" t="n">
         <v>1939953</v>
@@ -23946,7 +23946,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G813" t="n">
-        <v>7.89932107925415</v>
+        <v>7.89932155609131</v>
       </c>
       <c r="H813" t="n">
         <v>3220130</v>
@@ -23975,7 +23975,7 @@
         <v>8.63399982452393</v>
       </c>
       <c r="G814" t="n">
-        <v>7.82141542434692</v>
+        <v>7.82141447067261</v>
       </c>
       <c r="H814" t="n">
         <v>2142908</v>
@@ -24004,7 +24004,7 @@
         <v>9.77600002288818</v>
       </c>
       <c r="G815" t="n">
-        <v>8.85593605041504</v>
+        <v>8.85593700408936</v>
       </c>
       <c r="H815" t="n">
         <v>17311172</v>
@@ -24091,7 +24091,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>9.42120933532715</v>
+        <v>9.42120742797852</v>
       </c>
       <c r="H818" t="n">
         <v>5762220</v>
@@ -24120,7 +24120,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G819" t="n">
-        <v>9.41214942932129</v>
+        <v>9.41215038299561</v>
       </c>
       <c r="H819" t="n">
         <v>4344178</v>
@@ -24149,7 +24149,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G820" t="n">
-        <v>9.40309143066406</v>
+        <v>9.40309047698975</v>
       </c>
       <c r="H820" t="n">
         <v>4791452</v>
@@ -24178,7 +24178,7 @@
         <v>10.1350002288818</v>
       </c>
       <c r="G821" t="n">
-        <v>9.18114852905273</v>
+        <v>9.18114948272705</v>
       </c>
       <c r="H821" t="n">
         <v>3935500</v>
@@ -24207,7 +24207,7 @@
         <v>10.0950002670288</v>
       </c>
       <c r="G822" t="n">
-        <v>9.14491367340088</v>
+        <v>9.14491271972656</v>
       </c>
       <c r="H822" t="n">
         <v>2998963</v>
@@ -24236,7 +24236,7 @@
         <v>10.2349996566772</v>
       </c>
       <c r="G823" t="n">
-        <v>9.27173709869385</v>
+        <v>9.27173805236816</v>
       </c>
       <c r="H823" t="n">
         <v>3124532</v>
@@ -24294,7 +24294,7 @@
         <v>10.2550001144409</v>
       </c>
       <c r="G825" t="n">
-        <v>9.28985500335693</v>
+        <v>9.28985595703125</v>
       </c>
       <c r="H825" t="n">
         <v>2562283</v>
@@ -24323,7 +24323,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G826" t="n">
-        <v>9.38497257232666</v>
+        <v>9.38497447967529</v>
       </c>
       <c r="H826" t="n">
         <v>2333448</v>
@@ -24352,7 +24352,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G827" t="n">
-        <v>9.43479633331299</v>
+        <v>9.4347972869873</v>
       </c>
       <c r="H827" t="n">
         <v>3023327</v>
@@ -24439,7 +24439,7 @@
         <v>10.5050001144409</v>
       </c>
       <c r="G830" t="n">
-        <v>9.51632785797119</v>
+        <v>9.51632690429688</v>
       </c>
       <c r="H830" t="n">
         <v>2603548</v>
@@ -24468,7 +24468,7 @@
         <v>10.5450000762939</v>
       </c>
       <c r="G831" t="n">
-        <v>9.55256271362305</v>
+        <v>9.55256175994873</v>
       </c>
       <c r="H831" t="n">
         <v>2352732</v>
@@ -24526,7 +24526,7 @@
         <v>10.2749996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>9.3079719543457</v>
+        <v>9.30797290802002</v>
       </c>
       <c r="H833" t="n">
         <v>2893441</v>
@@ -24787,7 +24787,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G842" t="n">
-        <v>9.55709171295166</v>
+        <v>9.55709266662598</v>
       </c>
       <c r="H842" t="n">
         <v>1394980</v>
@@ -24845,7 +24845,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G844" t="n">
-        <v>9.49368000030518</v>
+        <v>9.49367904663086</v>
       </c>
       <c r="H844" t="n">
         <v>1649102</v>
@@ -24874,7 +24874,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G845" t="n">
-        <v>9.43479633331299</v>
+        <v>9.4347972869873</v>
       </c>
       <c r="H845" t="n">
         <v>1765657</v>
@@ -25019,7 +25019,7 @@
         <v>9.77400016784668</v>
       </c>
       <c r="G850" t="n">
-        <v>8.85412406921387</v>
+        <v>8.85412502288818</v>
       </c>
       <c r="H850" t="n">
         <v>3379906</v>
@@ -25048,7 +25048,7 @@
         <v>9.75599956512451</v>
       </c>
       <c r="G851" t="n">
-        <v>8.83781814575195</v>
+        <v>8.83781909942627</v>
       </c>
       <c r="H851" t="n">
         <v>2375624</v>
@@ -25106,7 +25106,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G853" t="n">
-        <v>9.10414886474609</v>
+        <v>9.10414981842041</v>
       </c>
       <c r="H853" t="n">
         <v>3037048</v>
@@ -25164,7 +25164,7 @@
         <v>9.67599964141846</v>
       </c>
       <c r="G855" t="n">
-        <v>8.76534748077393</v>
+        <v>8.76534652709961</v>
       </c>
       <c r="H855" t="n">
         <v>2279152</v>
@@ -25193,7 +25193,7 @@
         <v>9.85599994659424</v>
       </c>
       <c r="G856" t="n">
-        <v>8.92840766906738</v>
+        <v>8.92840671539307</v>
       </c>
       <c r="H856" t="n">
         <v>2884623</v>
@@ -25251,7 +25251,7 @@
         <v>10.0249996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>9.08150196075439</v>
+        <v>9.08150100708008</v>
       </c>
       <c r="H858" t="n">
         <v>2014582</v>
@@ -25309,7 +25309,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G860" t="n">
-        <v>9.27902507781982</v>
+        <v>9.27902603149414</v>
       </c>
       <c r="H860" t="n">
         <v>2259546</v>
@@ -25338,7 +25338,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G861" t="n">
-        <v>9.36170959472656</v>
+        <v>9.36171054840088</v>
       </c>
       <c r="H861" t="n">
         <v>2531488</v>
@@ -25396,7 +25396,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G863" t="n">
-        <v>9.26983833312988</v>
+        <v>9.26983737945557</v>
       </c>
       <c r="H863" t="n">
         <v>2548437</v>
@@ -25425,7 +25425,7 @@
         <v>9.87600040435791</v>
       </c>
       <c r="G864" t="n">
-        <v>9.07323360443115</v>
+        <v>9.07323265075684</v>
       </c>
       <c r="H864" t="n">
         <v>1045042</v>
@@ -25454,7 +25454,7 @@
         <v>9.65799999237061</v>
       </c>
       <c r="G865" t="n">
-        <v>8.87295341491699</v>
+        <v>8.87295436859131</v>
       </c>
       <c r="H865" t="n">
         <v>4307467</v>
@@ -25512,7 +25512,7 @@
         <v>9.78600025177002</v>
       </c>
       <c r="G867" t="n">
-        <v>8.9905481338501</v>
+        <v>8.99054908752441</v>
       </c>
       <c r="H867" t="n">
         <v>6119753</v>
@@ -25570,7 +25570,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G869" t="n">
-        <v>9.34792995452881</v>
+        <v>9.34792900085449</v>
       </c>
       <c r="H869" t="n">
         <v>2902797</v>
@@ -25599,7 +25599,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>9.50870418548584</v>
+        <v>9.50870513916016</v>
       </c>
       <c r="H870" t="n">
         <v>3374533</v>
@@ -25628,7 +25628,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G871" t="n">
-        <v>9.50870418548584</v>
+        <v>9.50870513916016</v>
       </c>
       <c r="H871" t="n">
         <v>3001551</v>
@@ -25657,7 +25657,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G872" t="n">
-        <v>9.56382656097412</v>
+        <v>9.56382751464844</v>
       </c>
       <c r="H872" t="n">
         <v>2729845</v>
@@ -25686,7 +25686,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H873" t="n">
         <v>1970515</v>
@@ -25744,7 +25744,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G875" t="n">
-        <v>9.86700344085693</v>
+        <v>9.86700248718262</v>
       </c>
       <c r="H875" t="n">
         <v>2064126</v>
@@ -25773,7 +25773,7 @@
         <v>10.6549997329712</v>
       </c>
       <c r="G876" t="n">
-        <v>9.78891277313232</v>
+        <v>9.78891181945801</v>
       </c>
       <c r="H876" t="n">
         <v>1820197</v>
@@ -25831,7 +25831,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G878" t="n">
-        <v>9.9037504196167</v>
+        <v>9.90375137329102</v>
       </c>
       <c r="H878" t="n">
         <v>1719391</v>
@@ -26092,7 +26092,7 @@
         <v>11.0550003051758</v>
       </c>
       <c r="G887" t="n">
-        <v>10.156397819519</v>
+        <v>10.1563997268677</v>
       </c>
       <c r="H887" t="n">
         <v>1609931</v>
@@ -26179,7 +26179,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G890" t="n">
-        <v>10.280424118042</v>
+        <v>10.2804250717163</v>
       </c>
       <c r="H890" t="n">
         <v>1258425</v>
@@ -26324,7 +26324,7 @@
         <v>11.335000038147</v>
       </c>
       <c r="G895" t="n">
-        <v>10.4136400222778</v>
+        <v>10.4136390686035</v>
       </c>
       <c r="H895" t="n">
         <v>1628415</v>
@@ -26353,7 +26353,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G896" t="n">
-        <v>10.5606336593628</v>
+        <v>10.5606327056885</v>
       </c>
       <c r="H896" t="n">
         <v>1941086</v>
@@ -26440,7 +26440,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G899" t="n">
-        <v>10.6387233734131</v>
+        <v>10.6387243270874</v>
       </c>
       <c r="H899" t="n">
         <v>1772409</v>
@@ -26498,7 +26498,7 @@
         <v>11.5550003051758</v>
       </c>
       <c r="G901" t="n">
-        <v>10.6157560348511</v>
+        <v>10.6157569885254</v>
       </c>
       <c r="H901" t="n">
         <v>873979</v>
@@ -26527,7 +26527,7 @@
         <v>11.4949998855591</v>
       </c>
       <c r="G902" t="n">
-        <v>10.5606336593628</v>
+        <v>10.5606327056885</v>
       </c>
       <c r="H902" t="n">
         <v>1203017</v>
@@ -26556,7 +26556,7 @@
         <v>11.3050003051758</v>
       </c>
       <c r="G903" t="n">
-        <v>10.3860769271851</v>
+        <v>10.3860778808594</v>
       </c>
       <c r="H903" t="n">
         <v>2251516</v>
@@ -26614,7 +26614,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G905" t="n">
-        <v>10.6892538070679</v>
+        <v>10.6892547607422</v>
       </c>
       <c r="H905" t="n">
         <v>2555423</v>
@@ -26643,7 +26643,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G906" t="n">
-        <v>10.748969078064</v>
+        <v>10.7489700317383</v>
       </c>
       <c r="H906" t="n">
         <v>1443961</v>
@@ -26672,7 +26672,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G907" t="n">
-        <v>10.6662855148315</v>
+        <v>10.6662845611572</v>
       </c>
       <c r="H907" t="n">
         <v>1747593</v>
@@ -26701,7 +26701,7 @@
         <v>11.6850004196167</v>
       </c>
       <c r="G908" t="n">
-        <v>10.7351884841919</v>
+        <v>10.7351894378662</v>
       </c>
       <c r="H908" t="n">
         <v>1328213</v>
@@ -26730,7 +26730,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G909" t="n">
-        <v>10.510103225708</v>
+        <v>10.5101051330566</v>
       </c>
       <c r="H909" t="n">
         <v>2054061</v>
@@ -26846,7 +26846,7 @@
         <v>10.7150001525879</v>
       </c>
       <c r="G913" t="n">
-        <v>9.84403514862061</v>
+        <v>9.84403610229492</v>
       </c>
       <c r="H913" t="n">
         <v>2835727</v>
@@ -26962,7 +26962,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G917" t="n">
-        <v>9.58220291137695</v>
+        <v>9.58220195770264</v>
       </c>
       <c r="H917" t="n">
         <v>1743461</v>
@@ -27020,7 +27020,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G919" t="n">
-        <v>9.09528255462646</v>
+        <v>9.09528160095215</v>
       </c>
       <c r="H919" t="n">
         <v>1753725</v>
@@ -27078,7 +27078,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G921" t="n">
-        <v>9.01259899139404</v>
+        <v>9.01259994506836</v>
       </c>
       <c r="H921" t="n">
         <v>3283934</v>
@@ -27136,7 +27136,7 @@
         <v>10.1750001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>9.34792995452881</v>
+        <v>9.34792900085449</v>
       </c>
       <c r="H923" t="n">
         <v>1365222</v>
@@ -27165,7 +27165,7 @@
         <v>9.97799968719482</v>
       </c>
       <c r="G924" t="n">
-        <v>9.16694164276123</v>
+        <v>9.16694068908691</v>
       </c>
       <c r="H924" t="n">
         <v>1551334</v>
@@ -27194,7 +27194,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G925" t="n">
-        <v>9.46736145019531</v>
+        <v>9.46736240386963</v>
       </c>
       <c r="H925" t="n">
         <v>1797823</v>
@@ -27252,7 +27252,7 @@
         <v>9.99400043487549</v>
       </c>
       <c r="G927" t="n">
-        <v>9.18164253234863</v>
+        <v>9.18164157867432</v>
       </c>
       <c r="H927" t="n">
         <v>1291455</v>
@@ -27281,7 +27281,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G928" t="n">
-        <v>9.21930885314941</v>
+        <v>9.2193078994751</v>
       </c>
       <c r="H928" t="n">
         <v>1033794</v>
@@ -27339,7 +27339,7 @@
         <v>10.7250003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>9.85322189331055</v>
+        <v>9.85322284698486</v>
       </c>
       <c r="H930" t="n">
         <v>8786533</v>
@@ -27455,7 +27455,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G934" t="n">
-        <v>10.1380243301392</v>
+        <v>10.1380252838135</v>
       </c>
       <c r="H934" t="n">
         <v>2159929</v>
@@ -27513,7 +27513,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G936" t="n">
-        <v>10.3079872131348</v>
+        <v>10.3079862594604</v>
       </c>
       <c r="H936" t="n">
         <v>3494472</v>
@@ -27600,7 +27600,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G939" t="n">
-        <v>10.5560388565063</v>
+        <v>10.5560398101807</v>
       </c>
       <c r="H939" t="n">
         <v>1775821</v>
@@ -27687,7 +27687,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G942" t="n">
-        <v>10.9051513671875</v>
+        <v>10.9051523208618</v>
       </c>
       <c r="H942" t="n">
         <v>1817532</v>
@@ -27716,7 +27716,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G943" t="n">
-        <v>10.7214088439941</v>
+        <v>10.7214078903198</v>
       </c>
       <c r="H943" t="n">
         <v>1727969</v>
@@ -27745,7 +27745,7 @@
         <v>11.3249998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>10.4044504165649</v>
+        <v>10.4044513702393</v>
       </c>
       <c r="H944" t="n">
         <v>2015681</v>
@@ -27774,7 +27774,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G945" t="n">
-        <v>10.2436761856079</v>
+        <v>10.2436771392822</v>
       </c>
       <c r="H945" t="n">
         <v>2656432</v>
@@ -28064,7 +28064,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G955" t="n">
-        <v>9.50870418548584</v>
+        <v>9.50870513916016</v>
       </c>
       <c r="H955" t="n">
         <v>2421675</v>
@@ -28093,7 +28093,7 @@
         <v>10.3050003051758</v>
       </c>
       <c r="G956" t="n">
-        <v>9.46736145019531</v>
+        <v>9.46736240386963</v>
       </c>
       <c r="H956" t="n">
         <v>1751724</v>
@@ -28180,7 +28180,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G959" t="n">
-        <v>9.26065063476562</v>
+        <v>9.26065158843994</v>
       </c>
       <c r="H959" t="n">
         <v>2791390</v>
@@ -28267,7 +28267,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>9.60057544708252</v>
+        <v>9.60057640075684</v>
       </c>
       <c r="H962" t="n">
         <v>5940837</v>
@@ -28296,7 +28296,7 @@
         <v>10.3950004577637</v>
       </c>
       <c r="G963" t="n">
-        <v>9.55004692077637</v>
+        <v>9.55004596710205</v>
       </c>
       <c r="H963" t="n">
         <v>1717105</v>
@@ -28499,7 +28499,7 @@
         <v>10.1850004196167</v>
       </c>
       <c r="G970" t="n">
-        <v>9.35711574554443</v>
+        <v>9.35711669921875</v>
       </c>
       <c r="H970" t="n">
         <v>1439909</v>
@@ -28557,7 +28557,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G972" t="n">
-        <v>9.674072265625</v>
+        <v>9.67407321929932</v>
       </c>
       <c r="H972" t="n">
         <v>2515163</v>
@@ -28615,7 +28615,7 @@
         <v>10.585000038147</v>
       </c>
       <c r="G974" t="n">
-        <v>9.72460269927979</v>
+        <v>9.72460174560547</v>
       </c>
       <c r="H974" t="n">
         <v>1290841</v>
@@ -28644,7 +28644,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G975" t="n">
-        <v>9.62813758850098</v>
+        <v>9.62813663482666</v>
       </c>
       <c r="H975" t="n">
         <v>1682785</v>
@@ -28673,7 +28673,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G976" t="n">
-        <v>9.56382656097412</v>
+        <v>9.56382751464844</v>
       </c>
       <c r="H976" t="n">
         <v>1685292</v>
@@ -28702,7 +28702,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G977" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H977" t="n">
         <v>1183168</v>
@@ -28789,7 +28789,7 @@
         <v>11.1049995422363</v>
       </c>
       <c r="G980" t="n">
-        <v>10.2023334503174</v>
+        <v>10.2023344039917</v>
       </c>
       <c r="H980" t="n">
         <v>2748864</v>
@@ -28818,7 +28818,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>10.3171739578247</v>
+        <v>10.3171730041504</v>
       </c>
       <c r="H981" t="n">
         <v>4316150</v>
@@ -28847,7 +28847,7 @@
         <v>11.2550001144409</v>
       </c>
       <c r="G982" t="n">
-        <v>10.3401403427124</v>
+        <v>10.3401412963867</v>
       </c>
       <c r="H982" t="n">
         <v>7007121</v>
@@ -28934,7 +28934,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G985" t="n">
-        <v>10.4457941055298</v>
+        <v>10.4457931518555</v>
       </c>
       <c r="H985" t="n">
         <v>2030668</v>
@@ -29137,7 +29137,7 @@
         <v>10.8950004577637</v>
       </c>
       <c r="G992" t="n">
-        <v>10.0094041824341</v>
+        <v>10.0094051361084</v>
       </c>
       <c r="H992" t="n">
         <v>1247702</v>
@@ -29224,7 +29224,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G995" t="n">
-        <v>9.86700344085693</v>
+        <v>9.86700248718262</v>
       </c>
       <c r="H995" t="n">
         <v>2257786</v>
@@ -29253,7 +29253,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G996" t="n">
-        <v>9.86700344085693</v>
+        <v>9.86700248718262</v>
       </c>
       <c r="H996" t="n">
         <v>1305042</v>
@@ -29340,7 +29340,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G999" t="n">
-        <v>9.38927173614502</v>
+        <v>9.3892707824707</v>
       </c>
       <c r="H999" t="n">
         <v>2631643</v>
@@ -29398,7 +29398,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G1001" t="n">
-        <v>9.66488742828369</v>
+        <v>9.66488647460938</v>
       </c>
       <c r="H1001" t="n">
         <v>2690625</v>
@@ -29456,7 +29456,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1003" t="n">
-        <v>9.5362663269043</v>
+        <v>9.53626537322998</v>
       </c>
       <c r="H1003" t="n">
         <v>2315800</v>
@@ -29514,7 +29514,7 @@
         <v>10.4650001525879</v>
       </c>
       <c r="G1005" t="n">
-        <v>9.61435604095459</v>
+        <v>9.61435699462891</v>
       </c>
       <c r="H1005" t="n">
         <v>1606752</v>
@@ -29543,7 +29543,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.73378944396973</v>
+        <v>9.73379039764404</v>
       </c>
       <c r="H1006" t="n">
         <v>1904641</v>
@@ -29572,7 +29572,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H1007" t="n">
         <v>2678565</v>
@@ -29630,7 +29630,7 @@
         <v>10.5950002670288</v>
       </c>
       <c r="G1009" t="n">
-        <v>9.73378944396973</v>
+        <v>9.73379039764404</v>
       </c>
       <c r="H1009" t="n">
         <v>1654305</v>
@@ -29659,7 +29659,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1010" t="n">
-        <v>9.79350471496582</v>
+        <v>9.79350566864014</v>
       </c>
       <c r="H1010" t="n">
         <v>1336538</v>
@@ -29717,7 +29717,7 @@
         <v>10.6549997329712</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.78891277313232</v>
+        <v>9.78891181945801</v>
       </c>
       <c r="H1012" t="n">
         <v>4493622</v>
@@ -29775,7 +29775,7 @@
         <v>10.5349998474121</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.67866706848145</v>
+        <v>9.67866611480713</v>
       </c>
       <c r="H1014" t="n">
         <v>1548491</v>
@@ -29804,7 +29804,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1015" t="n">
-        <v>9.60057544708252</v>
+        <v>9.60057640075684</v>
       </c>
       <c r="H1015" t="n">
         <v>1183696</v>
@@ -29920,7 +29920,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G1019" t="n">
-        <v>10.1242446899414</v>
+        <v>10.1242437362671</v>
       </c>
       <c r="H1019" t="n">
         <v>3649794</v>
@@ -29949,7 +29949,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G1020" t="n">
-        <v>10.4274206161499</v>
+        <v>10.4274187088013</v>
       </c>
       <c r="H1020" t="n">
         <v>4011434</v>
@@ -29978,7 +29978,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1021" t="n">
-        <v>10.3722972869873</v>
+        <v>10.372296333313</v>
       </c>
       <c r="H1021" t="n">
         <v>3381519</v>
@@ -30007,7 +30007,7 @@
         <v>11.3450002670288</v>
       </c>
       <c r="G1022" t="n">
-        <v>10.4228258132935</v>
+        <v>10.4228267669678</v>
       </c>
       <c r="H1022" t="n">
         <v>2533019</v>
@@ -30094,7 +30094,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1025" t="n">
-        <v>10.1609935760498</v>
+        <v>10.1609926223755</v>
       </c>
       <c r="H1025" t="n">
         <v>1822748</v>
@@ -30152,7 +30152,7 @@
         <v>11.1149997711182</v>
       </c>
       <c r="G1027" t="n">
-        <v>10.2115211486816</v>
+        <v>10.2115201950073</v>
       </c>
       <c r="H1027" t="n">
         <v>1753657</v>
@@ -30500,7 +30500,7 @@
         <v>11.5</v>
       </c>
       <c r="G1039" t="n">
-        <v>10.5652275085449</v>
+        <v>10.5652265548706</v>
       </c>
       <c r="H1039" t="n">
         <v>3225373</v>
@@ -30529,7 +30529,7 @@
         <v>11.4849996566772</v>
       </c>
       <c r="G1040" t="n">
-        <v>10.5514469146729</v>
+        <v>10.5514459609985</v>
       </c>
       <c r="H1040" t="n">
         <v>3141350</v>
@@ -30587,7 +30587,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1042" t="n">
-        <v>10.8592147827148</v>
+        <v>10.8592157363892</v>
       </c>
       <c r="H1042" t="n">
         <v>4090242</v>
@@ -30703,7 +30703,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1046" t="n">
-        <v>10.6892538070679</v>
+        <v>10.6892547607422</v>
       </c>
       <c r="H1046" t="n">
         <v>1947389</v>
@@ -30732,7 +30732,7 @@
         <v>11.4750003814697</v>
       </c>
       <c r="G1047" t="n">
-        <v>10.5422592163086</v>
+        <v>10.5422582626343</v>
       </c>
       <c r="H1047" t="n">
         <v>1572341</v>
@@ -30790,7 +30790,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G1049" t="n">
-        <v>10.4641695022583</v>
+        <v>10.4641675949097</v>
       </c>
       <c r="H1049" t="n">
         <v>1993430</v>
@@ -30819,7 +30819,7 @@
         <v>11.2550001144409</v>
       </c>
       <c r="G1050" t="n">
-        <v>10.3401403427124</v>
+        <v>10.3401412963867</v>
       </c>
       <c r="H1050" t="n">
         <v>2238795</v>
@@ -30906,7 +30906,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1053" t="n">
-        <v>9.45358085632324</v>
+        <v>9.45358180999756</v>
       </c>
       <c r="H1053" t="n">
         <v>5363025</v>
@@ -30935,7 +30935,7 @@
         <v>10</v>
       </c>
       <c r="G1054" t="n">
-        <v>9.18715286254883</v>
+        <v>9.18715476989746</v>
       </c>
       <c r="H1054" t="n">
         <v>3810871</v>
@@ -30993,7 +30993,7 @@
         <v>9.63599967956543</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.85274028778076</v>
+        <v>8.85273933410645</v>
       </c>
       <c r="H1056" t="n">
         <v>5042891</v>
@@ -31022,7 +31022,7 @@
         <v>9.23799991607666</v>
       </c>
       <c r="G1057" t="n">
-        <v>8.48709297180176</v>
+        <v>8.48709201812744</v>
       </c>
       <c r="H1057" t="n">
         <v>6501413</v>
@@ -31138,7 +31138,7 @@
         <v>8.88799953460693</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.16554164886475</v>
+        <v>8.16554260253906</v>
       </c>
       <c r="H1061" t="n">
         <v>4847322</v>
@@ -31167,7 +31167,7 @@
         <v>8.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>7.80908060073853</v>
+        <v>7.80908107757568</v>
       </c>
       <c r="H1062" t="n">
         <v>4836531</v>
@@ -31254,7 +31254,7 @@
         <v>7.38600015640259</v>
       </c>
       <c r="G1065" t="n">
-        <v>6.78563261032104</v>
+        <v>6.78563213348389</v>
       </c>
       <c r="H1065" t="n">
         <v>3240208</v>
@@ -31283,7 +31283,7 @@
         <v>5.75</v>
       </c>
       <c r="G1066" t="n">
-        <v>5.28261375427246</v>
+        <v>5.2826132774353</v>
       </c>
       <c r="H1066" t="n">
         <v>7207434</v>
@@ -31399,7 +31399,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G1070" t="n">
-        <v>4.33541822433472</v>
+        <v>4.33541774749756</v>
       </c>
       <c r="H1070" t="n">
         <v>6327854</v>
@@ -31457,7 +31457,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1072" t="n">
-        <v>4.31979990005493</v>
+        <v>4.31980037689209</v>
       </c>
       <c r="H1072" t="n">
         <v>10485567</v>
@@ -31515,7 +31515,7 @@
         <v>5.25</v>
       </c>
       <c r="G1074" t="n">
-        <v>4.82325601577759</v>
+        <v>4.82325553894043</v>
       </c>
       <c r="H1074" t="n">
         <v>7153528</v>
@@ -31544,7 +31544,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.36713552474976</v>
+        <v>5.36713457107544</v>
       </c>
       <c r="H1075" t="n">
         <v>9729174</v>
@@ -31631,7 +31631,7 @@
         <v>5.96400022506714</v>
       </c>
       <c r="G1078" t="n">
-        <v>5.47921800613403</v>
+        <v>5.47921848297119</v>
       </c>
       <c r="H1078" t="n">
         <v>3493133</v>
@@ -31660,7 +31660,7 @@
         <v>6.07200002670288</v>
       </c>
       <c r="G1079" t="n">
-        <v>5.57844018936157</v>
+        <v>5.57843971252441</v>
       </c>
       <c r="H1079" t="n">
         <v>6950483</v>
@@ -31689,7 +31689,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.38183403015137</v>
+        <v>5.38183450698853</v>
       </c>
       <c r="H1080" t="n">
         <v>2932110</v>
@@ -31747,7 +31747,7 @@
         <v>6.31400012969971</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.80076932907104</v>
+        <v>5.80076885223389</v>
       </c>
       <c r="H1082" t="n">
         <v>6906098</v>
@@ -31805,7 +31805,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.39425945281982</v>
+        <v>6.39425897598267</v>
       </c>
       <c r="H1084" t="n">
         <v>5548890</v>
@@ -31834,7 +31834,7 @@
         <v>7.03599977493286</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.46408081054688</v>
+        <v>6.46408128738403</v>
       </c>
       <c r="H1085" t="n">
         <v>5531159</v>
@@ -31863,7 +31863,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1086" t="n">
-        <v>6.56881475448608</v>
+        <v>6.5688157081604</v>
       </c>
       <c r="H1086" t="n">
         <v>4941288</v>
@@ -31892,7 +31892,7 @@
         <v>7.08400011062622</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.50817966461182</v>
+        <v>6.50818014144897</v>
       </c>
       <c r="H1087" t="n">
         <v>3946138</v>
@@ -31950,7 +31950,7 @@
         <v>6.62200021743774</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.08373308181763</v>
+        <v>6.08373355865479</v>
       </c>
       <c r="H1089" t="n">
         <v>3843956</v>
@@ -31979,7 +31979,7 @@
         <v>6.66200017929077</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.12048196792603</v>
+        <v>6.12048244476318</v>
       </c>
       <c r="H1090" t="n">
         <v>3646868</v>
@@ -32037,7 +32037,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1092" t="n">
-        <v>5.69603490829468</v>
+        <v>5.69603538513184</v>
       </c>
       <c r="H1092" t="n">
         <v>3810499</v>
@@ -32066,7 +32066,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>5.47554397583008</v>
+        <v>5.47554445266724</v>
       </c>
       <c r="H1093" t="n">
         <v>7587985</v>
@@ -32095,7 +32095,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.73278379440308</v>
+        <v>5.73278331756592</v>
       </c>
       <c r="H1094" t="n">
         <v>4215181</v>
@@ -32153,7 +32153,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.64642477035522</v>
+        <v>5.64642429351807</v>
       </c>
       <c r="H1096" t="n">
         <v>3784567</v>
@@ -32182,7 +32182,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.61702537536621</v>
+        <v>5.61702585220337</v>
       </c>
       <c r="H1097" t="n">
         <v>3942956</v>
@@ -32240,7 +32240,7 @@
         <v>6.29400014877319</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.78239488601685</v>
+        <v>5.78239440917969</v>
       </c>
       <c r="H1099" t="n">
         <v>4931099</v>
@@ -32298,7 +32298,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.40755891799927</v>
+        <v>5.40755939483643</v>
       </c>
       <c r="H1101" t="n">
         <v>4958505</v>
@@ -32356,7 +32356,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.50310468673706</v>
+        <v>5.50310516357422</v>
       </c>
       <c r="H1103" t="n">
         <v>2523146</v>
@@ -32385,7 +32385,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1104" t="n">
-        <v>5.604163646698</v>
+        <v>5.60416316986084</v>
       </c>
       <c r="H1104" t="n">
         <v>4891796</v>
@@ -32414,7 +32414,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1105" t="n">
-        <v>5.42960739135742</v>
+        <v>5.42960786819458</v>
       </c>
       <c r="H1105" t="n">
         <v>4948172</v>
@@ -32472,7 +32472,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1107" t="n">
-        <v>5.23667669296265</v>
+        <v>5.2366771697998</v>
       </c>
       <c r="H1107" t="n">
         <v>4445122</v>
@@ -32646,7 +32646,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.81958103179932</v>
+        <v>4.81958055496216</v>
       </c>
       <c r="H1113" t="n">
         <v>3903101</v>
@@ -32675,7 +32675,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.76078367233276</v>
+        <v>4.76078319549561</v>
       </c>
       <c r="H1114" t="n">
         <v>3896866</v>
@@ -32704,7 +32704,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1115" t="n">
-        <v>5.04374742507935</v>
+        <v>5.04374694824219</v>
       </c>
       <c r="H1115" t="n">
         <v>3922889</v>
@@ -32733,7 +32733,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G1116" t="n">
-        <v>5.38183403015137</v>
+        <v>5.38183450698853</v>
       </c>
       <c r="H1116" t="n">
         <v>6358485</v>
@@ -32791,7 +32791,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.3561110496521</v>
+        <v>5.35611057281494</v>
       </c>
       <c r="H1118" t="n">
         <v>5170625</v>
@@ -32849,7 +32849,7 @@
         <v>5.91200017929077</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.43144559860229</v>
+        <v>5.43144512176514</v>
       </c>
       <c r="H1120" t="n">
         <v>4888153</v>
@@ -32878,7 +32878,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.6684741973877</v>
+        <v>5.66847372055054</v>
       </c>
       <c r="H1121" t="n">
         <v>6451492</v>
@@ -32965,7 +32965,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.50450468063354</v>
+        <v>6.50450420379639</v>
       </c>
       <c r="H1124" t="n">
         <v>9201653</v>
@@ -33023,7 +33023,7 @@
         <v>6.84600019454956</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.28952550888062</v>
+        <v>6.28952598571777</v>
       </c>
       <c r="H1126" t="n">
         <v>8478872</v>
@@ -33052,7 +33052,7 @@
         <v>6.66800022125244</v>
       </c>
       <c r="G1127" t="n">
-        <v>6.1259937286377</v>
+        <v>6.12599420547485</v>
       </c>
       <c r="H1127" t="n">
         <v>5511804</v>
@@ -33081,7 +33081,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.72175979614258</v>
+        <v>5.72175931930542</v>
       </c>
       <c r="H1128" t="n">
         <v>8175889</v>
@@ -33139,7 +33139,7 @@
         <v>6.21400022506714</v>
       </c>
       <c r="G1130" t="n">
-        <v>5.70889759063721</v>
+        <v>5.70889711380005</v>
       </c>
       <c r="H1130" t="n">
         <v>4946362</v>
@@ -33168,7 +33168,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1131" t="n">
-        <v>6.01207304000854</v>
+        <v>6.0120735168457</v>
       </c>
       <c r="H1131" t="n">
         <v>7213944</v>
@@ -33342,7 +33342,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1137" t="n">
-        <v>5.66315746307373</v>
+        <v>5.66315793991089</v>
       </c>
       <c r="H1137" t="n">
         <v>7358674</v>
@@ -33371,7 +33371,7 @@
         <v>5.95800018310547</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.5955376625061</v>
+        <v>5.59553718566895</v>
       </c>
       <c r="H1138" t="n">
         <v>5720673</v>
@@ -33400,7 +33400,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1139" t="n">
-        <v>5.49410724639893</v>
+        <v>5.49410772323608</v>
       </c>
       <c r="H1139" t="n">
         <v>4364497</v>
@@ -33429,7 +33429,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.62183427810669</v>
+        <v>5.62183380126953</v>
       </c>
       <c r="H1140" t="n">
         <v>4855021</v>
@@ -33487,7 +33487,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G1142" t="n">
-        <v>5.47908163070679</v>
+        <v>5.47908115386963</v>
       </c>
       <c r="H1142" t="n">
         <v>3632339</v>
@@ -33574,7 +33574,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.62559032440186</v>
+        <v>5.62559080123901</v>
       </c>
       <c r="H1145" t="n">
         <v>5771544</v>
@@ -33603,7 +33603,7 @@
         <v>5.91200017929077</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.5523362159729</v>
+        <v>5.55233573913574</v>
       </c>
       <c r="H1146" t="n">
         <v>3944122</v>
@@ -33661,7 +33661,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.26683044433594</v>
+        <v>5.26682996749878</v>
       </c>
       <c r="H1148" t="n">
         <v>6733034</v>
@@ -33719,7 +33719,7 @@
         <v>6.01200008392334</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.64625310897827</v>
+        <v>5.64625215530396</v>
       </c>
       <c r="H1150" t="n">
         <v>8062909</v>
@@ -33748,7 +33748,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1151" t="n">
-        <v>5.66315746307373</v>
+        <v>5.66315793991089</v>
       </c>
       <c r="H1151" t="n">
         <v>6210634</v>
@@ -33835,7 +33835,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1154" t="n">
-        <v>6.01064825057983</v>
+        <v>6.01064729690552</v>
       </c>
       <c r="H1154" t="n">
         <v>4225832</v>
@@ -33864,7 +33864,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1155" t="n">
-        <v>6.0576057434082</v>
+        <v>6.05760669708252</v>
       </c>
       <c r="H1155" t="n">
         <v>6013730</v>
@@ -33893,7 +33893,7 @@
         <v>6.30200004577637</v>
       </c>
       <c r="G1156" t="n">
-        <v>5.91861009597778</v>
+        <v>5.91860961914062</v>
       </c>
       <c r="H1156" t="n">
         <v>7613731</v>
@@ -33922,7 +33922,7 @@
         <v>6.22200012207031</v>
       </c>
       <c r="G1157" t="n">
-        <v>5.84347677230835</v>
+        <v>5.84347629547119</v>
       </c>
       <c r="H1157" t="n">
         <v>7499874</v>
@@ -33980,7 +33980,7 @@
         <v>6.14400005340576</v>
       </c>
       <c r="G1159" t="n">
-        <v>5.77022171020508</v>
+        <v>5.77022218704224</v>
       </c>
       <c r="H1159" t="n">
         <v>3315707</v>
@@ -34009,7 +34009,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1160" t="n">
-        <v>5.56924104690552</v>
+        <v>5.56924057006836</v>
       </c>
       <c r="H1160" t="n">
         <v>4563612</v>
@@ -34038,7 +34038,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G1161" t="n">
-        <v>5.53355312347412</v>
+        <v>5.53355264663696</v>
       </c>
       <c r="H1161" t="n">
         <v>4557703</v>
@@ -34067,7 +34067,7 @@
         <v>5.83599996566772</v>
       </c>
       <c r="G1162" t="n">
-        <v>5.48095941543579</v>
+        <v>5.48095893859863</v>
       </c>
       <c r="H1162" t="n">
         <v>3213093</v>
@@ -34154,7 +34154,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1165" t="n">
-        <v>5.20108842849731</v>
+        <v>5.20108890533447</v>
       </c>
       <c r="H1165" t="n">
         <v>6952379</v>
@@ -34183,7 +34183,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.45090627670288</v>
+        <v>5.45090579986572</v>
       </c>
       <c r="H1166" t="n">
         <v>6733566</v>
@@ -34212,7 +34212,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.52979612350464</v>
+        <v>5.52979564666748</v>
       </c>
       <c r="H1167" t="n">
         <v>4133048</v>
@@ -34328,7 +34328,7 @@
         <v>6.25400018692017</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.87352991104126</v>
+        <v>5.87353038787842</v>
       </c>
       <c r="H1171" t="n">
         <v>5993176</v>
@@ -34386,7 +34386,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.7664647102356</v>
+        <v>5.76646566390991</v>
       </c>
       <c r="H1173" t="n">
         <v>3094436</v>
@@ -34415,7 +34415,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.62371206283569</v>
+        <v>5.62371253967285</v>
       </c>
       <c r="H1174" t="n">
         <v>4516947</v>
@@ -34473,7 +34473,7 @@
         <v>5.88399982452393</v>
       </c>
       <c r="G1176" t="n">
-        <v>5.52603912353516</v>
+        <v>5.526038646698</v>
       </c>
       <c r="H1176" t="n">
         <v>3091230</v>
@@ -34560,7 +34560,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.4527850151062</v>
+        <v>5.45278453826904</v>
       </c>
       <c r="H1179" t="n">
         <v>3017484</v>
@@ -34589,7 +34589,7 @@
         <v>6.00799989700317</v>
       </c>
       <c r="G1180" t="n">
-        <v>5.64249563217163</v>
+        <v>5.64249515533447</v>
       </c>
       <c r="H1180" t="n">
         <v>2679231</v>
@@ -34618,7 +34618,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1181" t="n">
-        <v>5.62183427810669</v>
+        <v>5.62183380126953</v>
       </c>
       <c r="H1181" t="n">
         <v>3576700</v>
@@ -34647,7 +34647,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G1182" t="n">
-        <v>5.56924104690552</v>
+        <v>5.56924057006836</v>
       </c>
       <c r="H1182" t="n">
         <v>2851658</v>
@@ -34676,7 +34676,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G1183" t="n">
-        <v>5.53730869293213</v>
+        <v>5.53730916976929</v>
       </c>
       <c r="H1183" t="n">
         <v>3454375</v>
@@ -34705,7 +34705,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G1184" t="n">
-        <v>5.47908163070679</v>
+        <v>5.47908115386963</v>
       </c>
       <c r="H1184" t="n">
         <v>2659149</v>
@@ -34763,7 +34763,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G1186" t="n">
-        <v>5.29124784469604</v>
+        <v>5.2912483215332</v>
       </c>
       <c r="H1186" t="n">
         <v>4555335</v>
@@ -34850,7 +34850,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>5.31566667556763</v>
+        <v>5.31566715240479</v>
       </c>
       <c r="H1189" t="n">
         <v>3893570</v>
@@ -34937,7 +34937,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1192" t="n">
-        <v>5.18042755126953</v>
+        <v>5.18042659759521</v>
       </c>
       <c r="H1192" t="n">
         <v>8242592</v>
@@ -34995,7 +34995,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.13534688949585</v>
+        <v>5.13534641265869</v>
       </c>
       <c r="H1194" t="n">
         <v>6427343</v>
@@ -35024,7 +35024,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1195" t="n">
-        <v>5.18042755126953</v>
+        <v>5.18042659759521</v>
       </c>
       <c r="H1195" t="n">
         <v>5883114</v>
@@ -35053,7 +35053,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.23865556716919</v>
+        <v>5.23865509033203</v>
       </c>
       <c r="H1196" t="n">
         <v>8126480</v>
@@ -35111,7 +35111,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1198" t="n">
-        <v>5.37201595306396</v>
+        <v>5.37201690673828</v>
       </c>
       <c r="H1198" t="n">
         <v>4200410</v>
@@ -35169,7 +35169,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.81791019439697</v>
+        <v>4.81790924072266</v>
       </c>
       <c r="H1200" t="n">
         <v>11653918</v>
@@ -35227,7 +35227,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.54179573059082</v>
+        <v>4.54179525375366</v>
       </c>
       <c r="H1202" t="n">
         <v>10382293</v>
@@ -35285,7 +35285,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.68173170089722</v>
+        <v>4.68173122406006</v>
       </c>
       <c r="H1204" t="n">
         <v>7333996</v>
@@ -35343,7 +35343,7 @@
         <v>5</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.6958179473877</v>
+        <v>4.69581890106201</v>
       </c>
       <c r="H1206" t="n">
         <v>5342293</v>
@@ -35372,7 +35372,7 @@
         <v>5</v>
       </c>
       <c r="G1207" t="n">
-        <v>4.6958179473877</v>
+        <v>4.69581890106201</v>
       </c>
       <c r="H1207" t="n">
         <v>3889582</v>
@@ -35401,7 +35401,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.5812406539917</v>
+        <v>4.58124017715454</v>
       </c>
       <c r="H1208" t="n">
         <v>6943168</v>
@@ -35430,7 +35430,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.53146505355835</v>
+        <v>4.53146457672119</v>
       </c>
       <c r="H1209" t="n">
         <v>7018733</v>
@@ -35459,7 +35459,7 @@
         <v>4.90100002288818</v>
       </c>
       <c r="G1210" t="n">
-        <v>4.60284090042114</v>
+        <v>4.6028413772583</v>
       </c>
       <c r="H1210" t="n">
         <v>6235868</v>
@@ -35517,7 +35517,7 @@
         <v>5.13399982452393</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.82166576385498</v>
+        <v>4.82166624069214</v>
       </c>
       <c r="H1212" t="n">
         <v>5515901</v>
@@ -35546,7 +35546,7 @@
         <v>5.23400020599365</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.91558313369751</v>
+        <v>4.91558265686035</v>
       </c>
       <c r="H1213" t="n">
         <v>6812988</v>
@@ -35691,7 +35691,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.38495588302612</v>
+        <v>4.38495540618896</v>
       </c>
       <c r="H1218" t="n">
         <v>7369648</v>
@@ -35720,7 +35720,7 @@
         <v>4.76399993896484</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.47417593002319</v>
+        <v>4.47417640686035</v>
       </c>
       <c r="H1219" t="n">
         <v>12255098</v>
@@ -35807,7 +35807,7 @@
         <v>4.68699979782104</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.40186023712158</v>
+        <v>4.40185976028442</v>
       </c>
       <c r="H1222" t="n">
         <v>5553631</v>
@@ -35836,7 +35836,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.3765025138855</v>
+        <v>4.37650299072266</v>
       </c>
       <c r="H1223" t="n">
         <v>5625336</v>
@@ -35923,7 +35923,7 @@
         <v>4.42700004577637</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.15767765045166</v>
+        <v>4.15767812728882</v>
       </c>
       <c r="H1226" t="n">
         <v>8790487</v>
@@ -35952,7 +35952,7 @@
         <v>4.25</v>
       </c>
       <c r="G1227" t="n">
-        <v>3.99144577980042</v>
+        <v>3.99144601821899</v>
       </c>
       <c r="H1227" t="n">
         <v>12289643</v>
@@ -36039,7 +36039,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G1230" t="n">
-        <v>3.98393225669861</v>
+        <v>3.98393273353577</v>
       </c>
       <c r="H1230" t="n">
         <v>5874403</v>
@@ -36126,7 +36126,7 @@
         <v>4.67799997329712</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.39340734481812</v>
+        <v>4.39340782165527</v>
       </c>
       <c r="H1233" t="n">
         <v>7925482</v>
@@ -36155,7 +36155,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.07597064971924</v>
+        <v>4.0759711265564</v>
       </c>
       <c r="H1234" t="n">
         <v>28147182</v>
@@ -36184,7 +36184,7 @@
         <v>5.0460000038147</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.73901987075806</v>
+        <v>4.73902082443237</v>
       </c>
       <c r="H1235" t="n">
         <v>31511062</v>
@@ -36213,7 +36213,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>5.09026718139648</v>
+        <v>5.09026765823364</v>
       </c>
       <c r="H1236" t="n">
         <v>32344656</v>
@@ -36242,7 +36242,7 @@
         <v>5.35599994659424</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.03016090393066</v>
+        <v>5.03016042709351</v>
       </c>
       <c r="H1237" t="n">
         <v>13864461</v>
@@ -36416,7 +36416,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1243" t="n">
-        <v>5.34008502960205</v>
+        <v>5.34008455276489</v>
       </c>
       <c r="H1243" t="n">
         <v>8725756</v>
@@ -36445,7 +36445,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1244" t="n">
-        <v>5.38328647613525</v>
+        <v>5.3832859992981</v>
       </c>
       <c r="H1244" t="n">
         <v>8692380</v>
@@ -36503,7 +36503,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G1246" t="n">
-        <v>5.84911203384399</v>
+        <v>5.84911155700684</v>
       </c>
       <c r="H1246" t="n">
         <v>15099797</v>
@@ -36532,7 +36532,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1247" t="n">
-        <v>5.84159803390503</v>
+        <v>5.84159755706787</v>
       </c>
       <c r="H1247" t="n">
         <v>13064619</v>
@@ -36561,7 +36561,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1248" t="n">
-        <v>5.71762847900391</v>
+        <v>5.71762895584106</v>
       </c>
       <c r="H1248" t="n">
         <v>8570401</v>
@@ -36590,7 +36590,7 @@
         <v>5.98600006103516</v>
       </c>
       <c r="G1249" t="n">
-        <v>5.62183427810669</v>
+        <v>5.62183380126953</v>
       </c>
       <c r="H1249" t="n">
         <v>10511976</v>
@@ -36648,7 +36648,7 @@
         <v>6.08599996566772</v>
       </c>
       <c r="G1251" t="n">
-        <v>5.7157506942749</v>
+        <v>5.71575021743774</v>
       </c>
       <c r="H1251" t="n">
         <v>9365658</v>
@@ -36677,7 +36677,7 @@
         <v>6.14400005340576</v>
       </c>
       <c r="G1252" t="n">
-        <v>5.77022171020508</v>
+        <v>5.77022218704224</v>
       </c>
       <c r="H1252" t="n">
         <v>8413896</v>
@@ -36735,7 +36735,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.14213085174561</v>
+        <v>6.14213037490845</v>
       </c>
       <c r="H1254" t="n">
         <v>16686198</v>
@@ -36851,7 +36851,7 @@
         <v>6.15399980545044</v>
       </c>
       <c r="G1258" t="n">
-        <v>5.77961301803589</v>
+        <v>5.77961349487305</v>
       </c>
       <c r="H1258" t="n">
         <v>10929218</v>
@@ -36880,7 +36880,7 @@
         <v>5.93599987030029</v>
       </c>
       <c r="G1259" t="n">
-        <v>5.57487535476685</v>
+        <v>5.574875831604</v>
       </c>
       <c r="H1259" t="n">
         <v>12939617</v>
@@ -36909,7 +36909,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G1260" t="n">
-        <v>5.4959864616394</v>
+        <v>5.49598598480225</v>
       </c>
       <c r="H1260" t="n">
         <v>9810275</v>
@@ -36938,7 +36938,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1261" t="n">
-        <v>5.66315746307373</v>
+        <v>5.66315793991089</v>
       </c>
       <c r="H1261" t="n">
         <v>5804500</v>
@@ -37199,7 +37199,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1270" t="n">
-        <v>5.55045700073242</v>
+        <v>5.55045747756958</v>
       </c>
       <c r="H1270" t="n">
         <v>4341706</v>
@@ -37228,7 +37228,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1271" t="n">
-        <v>5.4753246307373</v>
+        <v>5.47532415390015</v>
       </c>
       <c r="H1271" t="n">
         <v>8852824</v>
@@ -37257,7 +37257,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G1272" t="n">
-        <v>5.6105637550354</v>
+        <v>5.61056423187256</v>
       </c>
       <c r="H1272" t="n">
         <v>6958267</v>
@@ -37286,7 +37286,7 @@
         <v>6.06199979782104</v>
       </c>
       <c r="G1273" t="n">
-        <v>5.69320964813232</v>
+        <v>5.69321012496948</v>
       </c>
       <c r="H1273" t="n">
         <v>7978146</v>
@@ -37315,7 +37315,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1274" t="n">
-        <v>5.64437389373779</v>
+        <v>5.64437437057495</v>
       </c>
       <c r="H1274" t="n">
         <v>8066145</v>
@@ -37344,7 +37344,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G1275" t="n">
-        <v>5.55609273910522</v>
+        <v>5.55609226226807</v>
       </c>
       <c r="H1275" t="n">
         <v>9019694</v>
@@ -37373,7 +37373,7 @@
         <v>5.87599992752075</v>
       </c>
       <c r="G1276" t="n">
-        <v>5.51852560043335</v>
+        <v>5.51852607727051</v>
       </c>
       <c r="H1276" t="n">
         <v>7876768</v>
@@ -37518,7 +37518,7 @@
         <v>5.84800004959106</v>
       </c>
       <c r="G1281" t="n">
-        <v>5.49222993850708</v>
+        <v>5.49222946166992</v>
       </c>
       <c r="H1281" t="n">
         <v>3705231</v>
@@ -37576,7 +37576,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G1283" t="n">
-        <v>5.74016857147217</v>
+        <v>5.74016904830933</v>
       </c>
       <c r="H1283" t="n">
         <v>9155694</v>
@@ -37605,7 +37605,7 @@
         <v>5.86600017547607</v>
       </c>
       <c r="G1284" t="n">
-        <v>5.5091347694397</v>
+        <v>5.50913429260254</v>
       </c>
       <c r="H1284" t="n">
         <v>11295438</v>
@@ -37663,7 +37663,7 @@
         <v>5.48600006103516</v>
       </c>
       <c r="G1286" t="n">
-        <v>5.15225219726562</v>
+        <v>5.15225172042847</v>
       </c>
       <c r="H1286" t="n">
         <v>12634812</v>
@@ -37750,7 +37750,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G1289" t="n">
-        <v>5.36074638366699</v>
+        <v>5.36074686050415</v>
       </c>
       <c r="H1289" t="n">
         <v>5505589</v>
@@ -37779,7 +37779,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>5.38704299926758</v>
+        <v>5.38704347610474</v>
       </c>
       <c r="H1290" t="n">
         <v>12216275</v>
@@ -37808,7 +37808,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1291" t="n">
-        <v>5.37201595306396</v>
+        <v>5.37201690673828</v>
       </c>
       <c r="H1291" t="n">
         <v>5054223</v>
@@ -37866,7 +37866,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1293" t="n">
-        <v>5.54482221603394</v>
+        <v>5.54482269287109</v>
       </c>
       <c r="H1293" t="n">
         <v>8723177</v>
@@ -37924,7 +37924,7 @@
         <v>6.03200006484985</v>
       </c>
       <c r="G1295" t="n">
-        <v>5.66503572463989</v>
+        <v>5.66503524780273</v>
       </c>
       <c r="H1295" t="n">
         <v>8073936</v>
@@ -37953,7 +37953,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1296" t="n">
-        <v>5.78524827957153</v>
+        <v>5.78524780273438</v>
       </c>
       <c r="H1296" t="n">
         <v>10896236</v>
@@ -38011,7 +38011,7 @@
         <v>6.13399982452393</v>
       </c>
       <c r="G1298" t="n">
-        <v>5.76082992553711</v>
+        <v>5.76083040237427</v>
       </c>
       <c r="H1298" t="n">
         <v>7590693</v>
@@ -38040,7 +38040,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1299" t="n">
-        <v>5.67630624771118</v>
+        <v>5.67630577087402</v>
       </c>
       <c r="H1299" t="n">
         <v>8268739</v>
@@ -38098,7 +38098,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G1301" t="n">
-        <v>5.8303279876709</v>
+        <v>5.83032846450806</v>
       </c>
       <c r="H1301" t="n">
         <v>8345836</v>
@@ -38185,7 +38185,7 @@
         <v>5.98799991607666</v>
       </c>
       <c r="G1304" t="n">
-        <v>5.62371206283569</v>
+        <v>5.62371253967285</v>
       </c>
       <c r="H1304" t="n">
         <v>7130489</v>
@@ -38243,7 +38243,7 @@
         <v>6.58599996566772</v>
       </c>
       <c r="G1306" t="n">
-        <v>6.18533182144165</v>
+        <v>6.18533229827881</v>
       </c>
       <c r="H1306" t="n">
         <v>10236317</v>
@@ -38272,7 +38272,7 @@
         <v>6.66200017929077</v>
       </c>
       <c r="G1307" t="n">
-        <v>6.25670862197876</v>
+        <v>6.25670909881592</v>
       </c>
       <c r="H1307" t="n">
         <v>15827501</v>
@@ -38359,7 +38359,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1310" t="n">
-        <v>6.22665548324585</v>
+        <v>6.22665596008301</v>
       </c>
       <c r="H1310" t="n">
         <v>9135192</v>
@@ -38388,7 +38388,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1311" t="n">
-        <v>6.47083806991577</v>
+        <v>6.47083711624146</v>
       </c>
       <c r="H1311" t="n">
         <v>9532487</v>
@@ -38446,7 +38446,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1313" t="n">
-        <v>6.43327140808105</v>
+        <v>6.43327188491821</v>
       </c>
       <c r="H1313" t="n">
         <v>6639771</v>
@@ -38475,7 +38475,7 @@
         <v>6.88800001144409</v>
       </c>
       <c r="G1314" t="n">
-        <v>6.46896028518677</v>
+        <v>6.46895980834961</v>
       </c>
       <c r="H1314" t="n">
         <v>5233316</v>
@@ -38533,7 +38533,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1316" t="n">
-        <v>6.48022985458374</v>
+        <v>6.48022937774658</v>
       </c>
       <c r="H1316" t="n">
         <v>7748403</v>
@@ -38620,7 +38620,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1319" t="n">
-        <v>6.98737764358521</v>
+        <v>6.98737812042236</v>
       </c>
       <c r="H1319" t="n">
         <v>13286117</v>
@@ -38678,7 +38678,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1321" t="n">
-        <v>7.269127368927</v>
+        <v>7.26912689208984</v>
       </c>
       <c r="H1321" t="n">
         <v>14306039</v>
@@ -38939,7 +38939,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1330" t="n">
-        <v>6.38631343841553</v>
+        <v>6.38631391525269</v>
       </c>
       <c r="H1330" t="n">
         <v>6334005</v>
@@ -38997,7 +38997,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1332" t="n">
-        <v>6.59292936325073</v>
+        <v>6.59292888641357</v>
       </c>
       <c r="H1332" t="n">
         <v>10297494</v>
@@ -39026,7 +39026,7 @@
         <v>6.90399980545044</v>
       </c>
       <c r="G1333" t="n">
-        <v>6.48398637771606</v>
+        <v>6.48398590087891</v>
       </c>
       <c r="H1333" t="n">
         <v>8951623</v>
@@ -39200,7 +39200,7 @@
         <v>7.0479998588562</v>
       </c>
       <c r="G1339" t="n">
-        <v>6.61922597885132</v>
+        <v>6.61922550201416</v>
       </c>
       <c r="H1339" t="n">
         <v>5777535</v>
@@ -39374,7 +39374,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G1345" t="n">
-        <v>6.45393371582031</v>
+        <v>6.453932762146</v>
       </c>
       <c r="H1345" t="n">
         <v>11532875</v>
@@ -39403,7 +39403,7 @@
         <v>6.90399980545044</v>
       </c>
       <c r="G1346" t="n">
-        <v>6.48398637771606</v>
+        <v>6.48398590087891</v>
       </c>
       <c r="H1346" t="n">
         <v>6357876</v>
@@ -39432,7 +39432,7 @@
         <v>6.94600009918213</v>
       </c>
       <c r="G1347" t="n">
-        <v>6.52343130111694</v>
+        <v>6.52343082427979</v>
       </c>
       <c r="H1347" t="n">
         <v>3462904</v>
@@ -39461,7 +39461,7 @@
         <v>6.93400001525879</v>
       </c>
       <c r="G1348" t="n">
-        <v>6.51216173171997</v>
+        <v>6.51216125488281</v>
       </c>
       <c r="H1348" t="n">
         <v>3303705</v>
@@ -39519,7 +39519,7 @@
         <v>6.65399980545044</v>
       </c>
       <c r="G1350" t="n">
-        <v>6.24919557571411</v>
+        <v>6.24919509887695</v>
       </c>
       <c r="H1350" t="n">
         <v>8344827</v>
@@ -39577,7 +39577,7 @@
         <v>6.64400005340576</v>
       </c>
       <c r="G1352" t="n">
-        <v>6.2398042678833</v>
+        <v>6.23980379104614</v>
       </c>
       <c r="H1352" t="n">
         <v>5472464</v>
@@ -39635,7 +39635,7 @@
         <v>6.87599992752075</v>
       </c>
       <c r="G1354" t="n">
-        <v>6.45768976211548</v>
+        <v>6.45768928527832</v>
       </c>
       <c r="H1354" t="n">
         <v>3470349</v>
@@ -39693,7 +39693,7 @@
         <v>6.9060001373291</v>
       </c>
       <c r="G1356" t="n">
-        <v>6.48586416244507</v>
+        <v>6.48586463928223</v>
       </c>
       <c r="H1356" t="n">
         <v>5674199</v>
@@ -39751,7 +39751,7 @@
         <v>6.90799999237061</v>
       </c>
       <c r="G1358" t="n">
-        <v>6.48774290084839</v>
+        <v>6.48774242401123</v>
       </c>
       <c r="H1358" t="n">
         <v>11335955</v>
@@ -39838,7 +39838,7 @@
         <v>6.86199998855591</v>
       </c>
       <c r="G1361" t="n">
-        <v>6.44454193115234</v>
+        <v>6.44454097747803</v>
       </c>
       <c r="H1361" t="n">
         <v>4579364</v>
@@ -39867,7 +39867,7 @@
         <v>6.80800008773804</v>
       </c>
       <c r="G1362" t="n">
-        <v>6.39382648468018</v>
+        <v>6.39382696151733</v>
       </c>
       <c r="H1362" t="n">
         <v>5855550</v>
@@ -39983,7 +39983,7 @@
         <v>6.82200002670288</v>
       </c>
       <c r="G1366" t="n">
-        <v>6.40697526931763</v>
+        <v>6.40697479248047</v>
       </c>
       <c r="H1366" t="n">
         <v>5891330</v>
@@ -40041,7 +40041,7 @@
         <v>6.93599987030029</v>
       </c>
       <c r="G1368" t="n">
-        <v>6.51403951644897</v>
+        <v>6.51403903961182</v>
       </c>
       <c r="H1368" t="n">
         <v>4544668</v>
@@ -40070,7 +40070,7 @@
         <v>7.02400016784668</v>
       </c>
       <c r="G1369" t="n">
-        <v>6.59668636322021</v>
+        <v>6.59668588638306</v>
       </c>
       <c r="H1369" t="n">
         <v>3923136</v>
@@ -40128,7 +40128,7 @@
         <v>6.89400005340576</v>
       </c>
       <c r="G1371" t="n">
-        <v>6.47459554672241</v>
+        <v>6.4745945930481</v>
       </c>
       <c r="H1371" t="n">
         <v>4078249</v>
@@ -40157,7 +40157,7 @@
         <v>7.07200002670288</v>
       </c>
       <c r="G1372" t="n">
-        <v>6.64176559448242</v>
+        <v>6.64176607131958</v>
       </c>
       <c r="H1372" t="n">
         <v>9340178</v>
@@ -40186,7 +40186,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1373" t="n">
-        <v>6.73380374908447</v>
+        <v>6.73380422592163</v>
       </c>
       <c r="H1373" t="n">
         <v>8674934</v>
@@ -40215,7 +40215,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1374" t="n">
-        <v>6.67745399475098</v>
+        <v>6.67745447158813</v>
       </c>
       <c r="H1374" t="n">
         <v>2999942</v>
@@ -40273,7 +40273,7 @@
         <v>7.25</v>
       </c>
       <c r="G1376" t="n">
-        <v>6.80893707275391</v>
+        <v>6.80893659591675</v>
       </c>
       <c r="H1376" t="n">
         <v>3239315</v>
@@ -40418,7 +40418,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1381" t="n">
-        <v>6.78076219558716</v>
+        <v>6.78076171875</v>
       </c>
       <c r="H1381" t="n">
         <v>2941030</v>
@@ -40447,7 +40447,7 @@
         <v>7.20599985122681</v>
       </c>
       <c r="G1382" t="n">
-        <v>6.76761341094971</v>
+        <v>6.76761388778687</v>
       </c>
       <c r="H1382" t="n">
         <v>3420450</v>
@@ -40505,7 +40505,7 @@
         <v>7.21400022506714</v>
       </c>
       <c r="G1384" t="n">
-        <v>6.77512741088867</v>
+        <v>6.77512693405151</v>
       </c>
       <c r="H1384" t="n">
         <v>2210695</v>
@@ -40534,7 +40534,7 @@
         <v>7.11600017547607</v>
       </c>
       <c r="G1385" t="n">
-        <v>6.68308925628662</v>
+        <v>6.68308877944946</v>
       </c>
       <c r="H1385" t="n">
         <v>3533757</v>
@@ -40563,7 +40563,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1386" t="n">
-        <v>6.74319553375244</v>
+        <v>6.7431960105896</v>
       </c>
       <c r="H1386" t="n">
         <v>2775207</v>
@@ -40592,7 +40592,7 @@
         <v>7.1560001373291</v>
       </c>
       <c r="G1387" t="n">
-        <v>6.72065544128418</v>
+        <v>6.72065591812134</v>
       </c>
       <c r="H1387" t="n">
         <v>4374246</v>
@@ -40650,7 +40650,7 @@
         <v>7.05800008773804</v>
       </c>
       <c r="G1389" t="n">
-        <v>6.62861728668213</v>
+        <v>6.62861776351929</v>
       </c>
       <c r="H1389" t="n">
         <v>3057274</v>
@@ -40737,7 +40737,7 @@
         <v>6.94600009918213</v>
       </c>
       <c r="G1392" t="n">
-        <v>6.52343130111694</v>
+        <v>6.52343082427979</v>
       </c>
       <c r="H1392" t="n">
         <v>3665868</v>
@@ -40766,7 +40766,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G1393" t="n">
-        <v>6.54784917831421</v>
+        <v>6.54784965515137</v>
       </c>
       <c r="H1393" t="n">
         <v>2608265</v>
@@ -41114,7 +41114,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1405" t="n">
-        <v>6.17969751358032</v>
+        <v>6.17969703674316</v>
       </c>
       <c r="H1405" t="n">
         <v>5997488</v>
@@ -41259,7 +41259,7 @@
         <v>6.16800022125244</v>
       </c>
       <c r="G1410" t="n">
-        <v>5.79276180267334</v>
+        <v>5.7927622795105</v>
       </c>
       <c r="H1410" t="n">
         <v>4013785</v>
@@ -41288,7 +41288,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1411" t="n">
-        <v>6.01064825057983</v>
+        <v>6.01064729690552</v>
       </c>
       <c r="H1411" t="n">
         <v>5214200</v>
@@ -41346,7 +41346,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1413" t="n">
-        <v>6.01064825057983</v>
+        <v>6.01064729690552</v>
       </c>
       <c r="H1413" t="n">
         <v>2792688</v>
@@ -41433,7 +41433,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1416" t="n">
-        <v>6.14588689804077</v>
+        <v>6.14588737487793</v>
       </c>
       <c r="H1416" t="n">
         <v>3244239</v>
@@ -41462,7 +41462,7 @@
         <v>6.56199979782104</v>
       </c>
       <c r="G1417" t="n">
-        <v>6.16279220581055</v>
+        <v>6.16279172897339</v>
       </c>
       <c r="H1417" t="n">
         <v>3244656</v>
@@ -41520,7 +41520,7 @@
         <v>6.78800010681152</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.37504291534424</v>
+        <v>6.3750433921814</v>
       </c>
       <c r="H1419" t="n">
         <v>5083195</v>
@@ -41636,7 +41636,7 @@
         <v>6.81599998474121</v>
       </c>
       <c r="G1423" t="n">
-        <v>6.40134048461914</v>
+        <v>6.40133953094482</v>
       </c>
       <c r="H1423" t="n">
         <v>4261603</v>
@@ -41665,7 +41665,7 @@
         <v>6.80600023269653</v>
       </c>
       <c r="G1424" t="n">
-        <v>6.39194822311401</v>
+        <v>6.39194869995117</v>
       </c>
       <c r="H1424" t="n">
         <v>2351560</v>
@@ -41723,7 +41723,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1426" t="n">
-        <v>6.53658008575439</v>
+        <v>6.53657960891724</v>
       </c>
       <c r="H1426" t="n">
         <v>5034136</v>
@@ -41752,7 +41752,7 @@
         <v>6.9060001373291</v>
       </c>
       <c r="G1427" t="n">
-        <v>6.48586416244507</v>
+        <v>6.48586463928223</v>
       </c>
       <c r="H1427" t="n">
         <v>3514588</v>
@@ -41839,7 +41839,7 @@
         <v>6.7979998588562</v>
       </c>
       <c r="G1430" t="n">
-        <v>6.38443517684937</v>
+        <v>6.38443470001221</v>
       </c>
       <c r="H1430" t="n">
         <v>4301042</v>
@@ -41926,7 +41926,7 @@
         <v>6.69199991226196</v>
       </c>
       <c r="G1433" t="n">
-        <v>6.28488397598267</v>
+        <v>6.28488349914551</v>
       </c>
       <c r="H1433" t="n">
         <v>3152004</v>
@@ -41955,7 +41955,7 @@
         <v>6.77199983596802</v>
       </c>
       <c r="G1434" t="n">
-        <v>6.36001634597778</v>
+        <v>6.36001682281494</v>
       </c>
       <c r="H1434" t="n">
         <v>2404832</v>
@@ -42013,7 +42013,7 @@
         <v>6.92600011825562</v>
       </c>
       <c r="G1436" t="n">
-        <v>6.50464773178101</v>
+        <v>6.50464820861816</v>
       </c>
       <c r="H1436" t="n">
         <v>3538529</v>
@@ -42071,7 +42071,7 @@
         <v>6.9060001373291</v>
       </c>
       <c r="G1438" t="n">
-        <v>6.48586416244507</v>
+        <v>6.48586463928223</v>
       </c>
       <c r="H1438" t="n">
         <v>2149964</v>
@@ -42100,7 +42100,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1439" t="n">
-        <v>6.4614462852478</v>
+        <v>6.46144676208496</v>
       </c>
       <c r="H1439" t="n">
         <v>2686812</v>
@@ -42187,7 +42187,7 @@
         <v>7.02799987792969</v>
       </c>
       <c r="G1442" t="n">
-        <v>6.60044288635254</v>
+        <v>6.60044240951538</v>
       </c>
       <c r="H1442" t="n">
         <v>4006940</v>
@@ -42245,7 +42245,7 @@
         <v>7.11800003051758</v>
       </c>
       <c r="G1444" t="n">
-        <v>6.68496751785278</v>
+        <v>6.68496704101562</v>
       </c>
       <c r="H1444" t="n">
         <v>5772560</v>
@@ -42332,7 +42332,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1447" t="n">
-        <v>6.48022985458374</v>
+        <v>6.48022937774658</v>
       </c>
       <c r="H1447" t="n">
         <v>4761887</v>
@@ -42361,7 +42361,7 @@
         <v>6.77799987792969</v>
       </c>
       <c r="G1448" t="n">
-        <v>6.36565113067627</v>
+        <v>6.36565160751343</v>
       </c>
       <c r="H1448" t="n">
         <v>3779562</v>
@@ -42390,7 +42390,7 @@
         <v>6.87200021743774</v>
       </c>
       <c r="G1449" t="n">
-        <v>6.45393371582031</v>
+        <v>6.453932762146</v>
       </c>
       <c r="H1449" t="n">
         <v>2368779</v>
@@ -42419,7 +42419,7 @@
         <v>6.83199977874756</v>
       </c>
       <c r="G1450" t="n">
-        <v>6.41636610031128</v>
+        <v>6.41636657714844</v>
       </c>
       <c r="H1450" t="n">
         <v>2639284</v>
@@ -42477,7 +42477,7 @@
         <v>6.77199983596802</v>
       </c>
       <c r="G1452" t="n">
-        <v>6.36001634597778</v>
+        <v>6.36001682281494</v>
       </c>
       <c r="H1452" t="n">
         <v>2558279</v>
@@ -42535,7 +42535,7 @@
         <v>6.64599990844727</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.24168252944946</v>
+        <v>6.24168157577515</v>
       </c>
       <c r="H1454" t="n">
         <v>4741366</v>
@@ -42709,7 +42709,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1460" t="n">
-        <v>6.53658008575439</v>
+        <v>6.53657960891724</v>
       </c>
       <c r="H1460" t="n">
         <v>5445468</v>
@@ -42767,7 +42767,7 @@
         <v>7.11399984359741</v>
       </c>
       <c r="G1462" t="n">
-        <v>6.6812105178833</v>
+        <v>6.68121099472046</v>
       </c>
       <c r="H1462" t="n">
         <v>7175363</v>
@@ -42796,7 +42796,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>6.71502017974854</v>
+        <v>6.71502113342285</v>
       </c>
       <c r="H1463" t="n">
         <v>3235474</v>
@@ -42912,7 +42912,7 @@
         <v>7.12799978256226</v>
       </c>
       <c r="G1467" t="n">
-        <v>6.69435882568359</v>
+        <v>6.69435930252075</v>
       </c>
       <c r="H1467" t="n">
         <v>4590008</v>
@@ -42970,7 +42970,7 @@
         <v>7.16800022125244</v>
       </c>
       <c r="G1469" t="n">
-        <v>6.73192548751831</v>
+        <v>6.73192596435547</v>
       </c>
       <c r="H1469" t="n">
         <v>3749077</v>
@@ -43028,7 +43028,7 @@
         <v>7.17399978637695</v>
       </c>
       <c r="G1471" t="n">
-        <v>6.7375602722168</v>
+        <v>6.73756074905396</v>
       </c>
       <c r="H1471" t="n">
         <v>2541649</v>
@@ -43057,7 +43057,7 @@
         <v>6.66800022125244</v>
       </c>
       <c r="G1472" t="n">
-        <v>6.26234340667725</v>
+        <v>6.2623438835144</v>
       </c>
       <c r="H1472" t="n">
         <v>23844570</v>
@@ -43086,7 +43086,7 @@
         <v>6.72599983215332</v>
       </c>
       <c r="G1473" t="n">
-        <v>6.31681489944458</v>
+        <v>6.31681537628174</v>
       </c>
       <c r="H1473" t="n">
         <v>22941337</v>
@@ -43115,7 +43115,7 @@
         <v>6.66800022125244</v>
       </c>
       <c r="G1474" t="n">
-        <v>6.26234340667725</v>
+        <v>6.2623438835144</v>
       </c>
       <c r="H1474" t="n">
         <v>7379278</v>
@@ -43173,7 +43173,7 @@
         <v>6.62400007247925</v>
       </c>
       <c r="G1476" t="n">
-        <v>6.22102117538452</v>
+        <v>6.22102069854736</v>
       </c>
       <c r="H1476" t="n">
         <v>7043961</v>
@@ -43231,7 +43231,7 @@
         <v>6.54400014877319</v>
       </c>
       <c r="G1478" t="n">
-        <v>6.14588689804077</v>
+        <v>6.14588737487793</v>
       </c>
       <c r="H1478" t="n">
         <v>4036120</v>
@@ -43260,7 +43260,7 @@
         <v>6.53399991989136</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.13649559020996</v>
+        <v>6.1364951133728</v>
       </c>
       <c r="H1479" t="n">
         <v>5593079</v>
@@ -43318,7 +43318,7 @@
         <v>6.5019998550415</v>
       </c>
       <c r="G1481" t="n">
-        <v>6.10644197463989</v>
+        <v>6.10644245147705</v>
       </c>
       <c r="H1481" t="n">
         <v>8098208</v>
@@ -43347,7 +43347,7 @@
         <v>6.43800020217896</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.04633569717407</v>
+        <v>6.04633617401123</v>
       </c>
       <c r="H1482" t="n">
         <v>5591997</v>
@@ -43405,7 +43405,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G1484" t="n">
-        <v>6.04257917404175</v>
+        <v>6.04257965087891</v>
       </c>
       <c r="H1484" t="n">
         <v>4166663</v>
@@ -43434,7 +43434,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1485" t="n">
-        <v>6.0576057434082</v>
+        <v>6.05760669708252</v>
       </c>
       <c r="H1485" t="n">
         <v>4069267</v>
@@ -43463,7 +43463,7 @@
         <v>6.61600017547607</v>
       </c>
       <c r="G1486" t="n">
-        <v>6.21350717544556</v>
+        <v>6.21350765228271</v>
       </c>
       <c r="H1486" t="n">
         <v>7324227</v>
@@ -43492,7 +43492,7 @@
         <v>6.61600017547607</v>
       </c>
       <c r="G1487" t="n">
-        <v>6.21350717544556</v>
+        <v>6.21350765228271</v>
       </c>
       <c r="H1487" t="n">
         <v>6115456</v>
@@ -43521,7 +43521,7 @@
         <v>6.52199983596802</v>
       </c>
       <c r="G1488" t="n">
-        <v>6.12522554397583</v>
+        <v>6.12522506713867</v>
       </c>
       <c r="H1488" t="n">
         <v>16855746</v>
@@ -43550,7 +43550,7 @@
         <v>6.55800008773804</v>
       </c>
       <c r="G1489" t="n">
-        <v>6.15903568267822</v>
+        <v>6.15903520584106</v>
       </c>
       <c r="H1489" t="n">
         <v>8792266</v>
@@ -43840,7 +43840,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1499" t="n">
-        <v>5.83220720291138</v>
+        <v>5.83220672607422</v>
       </c>
       <c r="H1499" t="n">
         <v>5815206</v>
@@ -43869,7 +43869,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1500" t="n">
-        <v>5.84159803390503</v>
+        <v>5.84159755706787</v>
       </c>
       <c r="H1500" t="n">
         <v>4932967</v>
@@ -43927,7 +43927,7 @@
         <v>6.35200023651123</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.96556806564331</v>
+        <v>5.96556854248047</v>
       </c>
       <c r="H1502" t="n">
         <v>3842450</v>
@@ -43985,7 +43985,7 @@
         <v>6.04400014877319</v>
       </c>
       <c r="G1504" t="n">
-        <v>5.67630624771118</v>
+        <v>5.67630577087402</v>
       </c>
       <c r="H1504" t="n">
         <v>5315162</v>
@@ -44043,7 +44043,7 @@
         <v>6.10799980163574</v>
       </c>
       <c r="G1506" t="n">
-        <v>5.73641109466553</v>
+        <v>5.73641204833984</v>
       </c>
       <c r="H1506" t="n">
         <v>4650030</v>
@@ -44072,7 +44072,7 @@
         <v>6.02799987792969</v>
       </c>
       <c r="G1507" t="n">
-        <v>5.66127872467041</v>
+        <v>5.66127920150757</v>
       </c>
       <c r="H1507" t="n">
         <v>4231227</v>
@@ -44159,7 +44159,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1510" t="n">
-        <v>5.74204635620117</v>
+        <v>5.74204683303833</v>
       </c>
       <c r="H1510" t="n">
         <v>4785474</v>
@@ -44188,7 +44188,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1511" t="n">
-        <v>5.71950817108154</v>
+        <v>5.71950769424438</v>
       </c>
       <c r="H1511" t="n">
         <v>5599569</v>
@@ -44217,7 +44217,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G1512" t="n">
-        <v>5.66879177093506</v>
+        <v>5.66879224777222</v>
       </c>
       <c r="H1512" t="n">
         <v>3994330</v>
@@ -44275,7 +44275,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G1514" t="n">
-        <v>5.52979612350464</v>
+        <v>5.52979564666748</v>
       </c>
       <c r="H1514" t="n">
         <v>4750983</v>
@@ -44304,7 +44304,7 @@
         <v>5.99399995803833</v>
       </c>
       <c r="G1515" t="n">
-        <v>5.62934732437134</v>
+        <v>5.62934684753418</v>
       </c>
       <c r="H1515" t="n">
         <v>4358061</v>
@@ -44333,7 +44333,7 @@
         <v>5.96600008010864</v>
       </c>
       <c r="G1516" t="n">
-        <v>5.60305118560791</v>
+        <v>5.60305070877075</v>
       </c>
       <c r="H1516" t="n">
         <v>3839414</v>
@@ -44362,7 +44362,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1517" t="n">
-        <v>5.6669135093689</v>
+        <v>5.66691398620605</v>
       </c>
       <c r="H1517" t="n">
         <v>4413168</v>
@@ -44449,7 +44449,7 @@
         <v>6.11399984359741</v>
       </c>
       <c r="G1520" t="n">
-        <v>5.74204635620117</v>
+        <v>5.74204683303833</v>
       </c>
       <c r="H1520" t="n">
         <v>3932734</v>
@@ -44536,7 +44536,7 @@
         <v>6.35400009155273</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.96744680404663</v>
+        <v>5.96744632720947</v>
       </c>
       <c r="H1523" t="n">
         <v>3087435</v>
@@ -44623,7 +44623,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1526" t="n">
-        <v>5.91673135757446</v>
+        <v>5.91673183441162</v>
       </c>
       <c r="H1526" t="n">
         <v>1762125</v>
@@ -44681,7 +44681,7 @@
         <v>6.43400001525879</v>
       </c>
       <c r="G1528" t="n">
-        <v>6.04257917404175</v>
+        <v>6.04257965087891</v>
       </c>
       <c r="H1528" t="n">
         <v>7813867</v>
@@ -44739,7 +44739,7 @@
         <v>6.31199979782104</v>
       </c>
       <c r="G1530" t="n">
-        <v>5.92800140380859</v>
+        <v>5.92800092697144</v>
       </c>
       <c r="H1530" t="n">
         <v>4793580</v>
@@ -44797,7 +44797,7 @@
         <v>6.46799993515015</v>
       </c>
       <c r="G1532" t="n">
-        <v>6.07451105117798</v>
+        <v>6.07451057434082</v>
       </c>
       <c r="H1532" t="n">
         <v>8941952</v>
@@ -44826,7 +44826,7 @@
         <v>6.56599998474121</v>
       </c>
       <c r="G1533" t="n">
-        <v>6.16654920578003</v>
+        <v>6.16654872894287</v>
       </c>
       <c r="H1533" t="n">
         <v>4811027</v>
@@ -44942,7 +44942,7 @@
         <v>6.77799987792969</v>
       </c>
       <c r="G1537" t="n">
-        <v>6.36565113067627</v>
+        <v>6.36565160751343</v>
       </c>
       <c r="H1537" t="n">
         <v>6863876</v>
@@ -45029,7 +45029,7 @@
         <v>6.91400003433228</v>
       </c>
       <c r="G1540" t="n">
-        <v>6.49337816238403</v>
+        <v>6.49337768554688</v>
       </c>
       <c r="H1540" t="n">
         <v>4711784</v>
@@ -45058,7 +45058,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1541" t="n">
-        <v>6.38631343841553</v>
+        <v>6.38631391525269</v>
       </c>
       <c r="H1541" t="n">
         <v>5076979</v>
@@ -45087,7 +45087,7 @@
         <v>6.60200023651123</v>
       </c>
       <c r="G1542" t="n">
-        <v>6.20035886764526</v>
+        <v>6.20035934448242</v>
       </c>
       <c r="H1542" t="n">
         <v>6055391</v>
@@ -45145,7 +45145,7 @@
         <v>6.33599996566772</v>
       </c>
       <c r="G1544" t="n">
-        <v>5.95054149627686</v>
+        <v>5.9505410194397</v>
       </c>
       <c r="H1544" t="n">
         <v>7901493</v>
@@ -45232,7 +45232,7 @@
         <v>6.38199996948242</v>
       </c>
       <c r="G1547" t="n">
-        <v>5.99374294281006</v>
+        <v>5.9937424659729</v>
       </c>
       <c r="H1547" t="n">
         <v>5036911</v>
@@ -45290,7 +45290,7 @@
         <v>6.40399980545044</v>
       </c>
       <c r="G1549" t="n">
-        <v>6.014404296875</v>
+        <v>6.01440477371216</v>
       </c>
       <c r="H1549" t="n">
         <v>3828431</v>
@@ -45319,7 +45319,7 @@
         <v>6.34600019454956</v>
       </c>
       <c r="G1550" t="n">
-        <v>5.95993280410767</v>
+        <v>5.95993375778198</v>
       </c>
       <c r="H1550" t="n">
         <v>2817248</v>
@@ -45348,7 +45348,7 @@
         <v>6.14599990844727</v>
       </c>
       <c r="G1551" t="n">
-        <v>5.7721004486084</v>
+        <v>5.77209997177124</v>
       </c>
       <c r="H1551" t="n">
         <v>6442990</v>
@@ -45406,7 +45406,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1553" t="n">
-        <v>5.85099029541016</v>
+        <v>5.850989818573</v>
       </c>
       <c r="H1553" t="n">
         <v>3842770</v>
@@ -45522,7 +45522,7 @@
         <v>6.46199989318848</v>
       </c>
       <c r="G1557" t="n">
-        <v>6.06887531280518</v>
+        <v>6.06887578964233</v>
       </c>
       <c r="H1557" t="n">
         <v>4800902</v>
@@ -45609,7 +45609,7 @@
         <v>6.64599990844727</v>
       </c>
       <c r="G1560" t="n">
-        <v>6.24168252944946</v>
+        <v>6.24168157577515</v>
       </c>
       <c r="H1560" t="n">
         <v>3268461</v>
@@ -45638,7 +45638,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1561" t="n">
-        <v>6.1984806060791</v>
+        <v>6.19848012924194</v>
       </c>
       <c r="H1561" t="n">
         <v>3330592</v>
@@ -45725,7 +45725,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1564" t="n">
-        <v>6.01064825057983</v>
+        <v>6.01064729690552</v>
       </c>
       <c r="H1564" t="n">
         <v>2100998</v>
@@ -45783,7 +45783,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1566" t="n">
-        <v>6.52718782424927</v>
+        <v>6.52718734741211</v>
       </c>
       <c r="H1566" t="n">
         <v>14190682</v>
@@ -45870,7 +45870,7 @@
         <v>7.99399995803833</v>
       </c>
       <c r="G1569" t="n">
-        <v>7.50767469406128</v>
+        <v>7.50767421722412</v>
       </c>
       <c r="H1569" t="n">
         <v>14183288</v>
@@ -45928,7 +45928,7 @@
         <v>7.55800008773804</v>
       </c>
       <c r="G1571" t="n">
-        <v>7.09819936752319</v>
+        <v>7.09819984436035</v>
       </c>
       <c r="H1571" t="n">
         <v>10670608</v>
@@ -45986,7 +45986,7 @@
         <v>8.02600002288818</v>
       </c>
       <c r="G1573" t="n">
-        <v>7.53772830963135</v>
+        <v>7.53772783279419</v>
       </c>
       <c r="H1573" t="n">
         <v>12127201</v>
@@ -46015,7 +46015,7 @@
         <v>8.06799983978271</v>
       </c>
       <c r="G1574" t="n">
-        <v>7.57717275619507</v>
+        <v>7.57717227935791</v>
       </c>
       <c r="H1574" t="n">
         <v>11799310</v>
@@ -46131,7 +46131,7 @@
         <v>9.12800025939941</v>
       </c>
       <c r="G1578" t="n">
-        <v>8.57268524169922</v>
+        <v>8.57268619537354</v>
       </c>
       <c r="H1578" t="n">
         <v>6110167</v>
@@ -46160,7 +46160,7 @@
         <v>8.68400001525879</v>
       </c>
       <c r="G1579" t="n">
-        <v>8.1556978225708</v>
+        <v>8.15569877624512</v>
       </c>
       <c r="H1579" t="n">
         <v>10857974</v>
@@ -46189,7 +46189,7 @@
         <v>8.81599998474121</v>
       </c>
       <c r="G1580" t="n">
-        <v>8.27966690063477</v>
+        <v>8.27966785430908</v>
       </c>
       <c r="H1580" t="n">
         <v>7177964</v>
@@ -46218,7 +46218,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G1581" t="n">
-        <v>8.22707462310791</v>
+        <v>8.22707557678223</v>
       </c>
       <c r="H1581" t="n">
         <v>5689347</v>
@@ -46334,7 +46334,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1585" t="n">
-        <v>8.753005027771</v>
+        <v>8.75300598144531</v>
       </c>
       <c r="H1585" t="n">
         <v>4959973</v>
@@ -46363,7 +46363,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1586" t="n">
-        <v>8.88448810577393</v>
+        <v>8.88448905944824</v>
       </c>
       <c r="H1586" t="n">
         <v>5415946</v>
@@ -46392,7 +46392,7 @@
         <v>9.18599987030029</v>
       </c>
       <c r="G1587" t="n">
-        <v>8.62715816497803</v>
+        <v>8.62715721130371</v>
       </c>
       <c r="H1587" t="n">
         <v>6218966</v>
@@ -46508,7 +46508,7 @@
         <v>9.08600044250488</v>
       </c>
       <c r="G1591" t="n">
-        <v>8.53324127197266</v>
+        <v>8.53324222564697</v>
       </c>
       <c r="H1591" t="n">
         <v>2837046</v>
@@ -46566,7 +46566,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1593" t="n">
-        <v>8.753005027771</v>
+        <v>8.75300598144531</v>
       </c>
       <c r="H1593" t="n">
         <v>3819850</v>
@@ -46624,7 +46624,7 @@
         <v>9.03600025177002</v>
       </c>
       <c r="G1595" t="n">
-        <v>8.48628234863281</v>
+        <v>8.48628425598145</v>
       </c>
       <c r="H1595" t="n">
         <v>2711571</v>
@@ -46653,7 +46653,7 @@
         <v>9.06599998474121</v>
       </c>
       <c r="G1596" t="n">
-        <v>8.5144567489624</v>
+        <v>8.51445865631104</v>
       </c>
       <c r="H1596" t="n">
         <v>3880847</v>
@@ -46740,7 +46740,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1599" t="n">
-        <v>9.31650543212891</v>
+        <v>9.31650447845459</v>
       </c>
       <c r="H1599" t="n">
         <v>5651007</v>
@@ -46856,7 +46856,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G1603" t="n">
-        <v>9.49494552612305</v>
+        <v>9.49494457244873</v>
       </c>
       <c r="H1603" t="n">
         <v>3541597</v>
@@ -46885,7 +46885,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1604" t="n">
-        <v>9.48555374145508</v>
+        <v>9.48555469512939</v>
       </c>
       <c r="H1604" t="n">
         <v>6082766</v>
@@ -46914,7 +46914,7 @@
         <v>10.0050001144409</v>
       </c>
       <c r="G1605" t="n">
-        <v>9.39633369445801</v>
+        <v>9.39633274078369</v>
       </c>
       <c r="H1605" t="n">
         <v>3320199</v>
@@ -46972,7 +46972,7 @@
         <v>9.89200019836426</v>
       </c>
       <c r="G1607" t="n">
-        <v>9.290207862854</v>
+        <v>9.29020690917969</v>
       </c>
       <c r="H1607" t="n">
         <v>4321913</v>
@@ -47030,7 +47030,7 @@
         <v>9.82400035858154</v>
       </c>
       <c r="G1609" t="n">
-        <v>9.22634410858154</v>
+        <v>9.22634506225586</v>
       </c>
       <c r="H1609" t="n">
         <v>1890382</v>
@@ -47088,7 +47088,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1611" t="n">
-        <v>9.36346340179443</v>
+        <v>9.36346244812012</v>
       </c>
       <c r="H1611" t="n">
         <v>2099511</v>
@@ -47175,7 +47175,7 @@
         <v>9.79599952697754</v>
       </c>
       <c r="G1614" t="n">
-        <v>9.20004749298096</v>
+        <v>9.20004844665527</v>
       </c>
       <c r="H1614" t="n">
         <v>6038554</v>
@@ -47204,7 +47204,7 @@
         <v>9.93200016021729</v>
       </c>
       <c r="G1615" t="n">
-        <v>9.32777404785156</v>
+        <v>9.32777500152588</v>
       </c>
       <c r="H1615" t="n">
         <v>5825097</v>
@@ -47233,7 +47233,7 @@
         <v>9.63399982452393</v>
       </c>
       <c r="G1616" t="n">
-        <v>9.0479040145874</v>
+        <v>9.04790306091309</v>
       </c>
       <c r="H1616" t="n">
         <v>4685010</v>
@@ -47291,7 +47291,7 @@
         <v>9.53600025177002</v>
       </c>
       <c r="G1618" t="n">
-        <v>8.95586585998535</v>
+        <v>8.95586490631104</v>
       </c>
       <c r="H1618" t="n">
         <v>3340373</v>
@@ -47320,7 +47320,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>8.99718856811523</v>
+        <v>8.99718761444092</v>
       </c>
       <c r="H1619" t="n">
         <v>2194088</v>
@@ -47494,7 +47494,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1625" t="n">
-        <v>9.29772090911865</v>
+        <v>9.29771995544434</v>
       </c>
       <c r="H1625" t="n">
         <v>1852819</v>
@@ -47668,7 +47668,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1631" t="n">
-        <v>9.41042041778564</v>
+        <v>9.41042137145996</v>
       </c>
       <c r="H1631" t="n">
         <v>2570145</v>
@@ -47755,7 +47755,7 @@
         <v>10.414999961853</v>
       </c>
       <c r="G1634" t="n">
-        <v>9.78139019012451</v>
+        <v>9.7813892364502</v>
       </c>
       <c r="H1634" t="n">
         <v>4048636</v>
@@ -47813,7 +47813,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1636" t="n">
-        <v>10.04905128479</v>
+        <v>10.0490522384644</v>
       </c>
       <c r="H1636" t="n">
         <v>3443518</v>
@@ -47842,7 +47842,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1637" t="n">
-        <v>10.0866184234619</v>
+        <v>10.0866174697876</v>
       </c>
       <c r="H1637" t="n">
         <v>2756700</v>
@@ -47900,7 +47900,7 @@
         <v>10.0349998474121</v>
       </c>
       <c r="G1639" t="n">
-        <v>9.4245080947876</v>
+        <v>9.42450714111328</v>
       </c>
       <c r="H1639" t="n">
         <v>2860497</v>
@@ -47929,7 +47929,7 @@
         <v>9.63599967956543</v>
       </c>
       <c r="G1640" t="n">
-        <v>9.04978084564209</v>
+        <v>9.04977989196777</v>
       </c>
       <c r="H1640" t="n">
         <v>3564898</v>
@@ -47958,7 +47958,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1641" t="n">
-        <v>9.07232189178467</v>
+        <v>9.07232093811035</v>
       </c>
       <c r="H1641" t="n">
         <v>2291401</v>
@@ -48045,7 +48045,7 @@
         <v>9.70199966430664</v>
       </c>
       <c r="G1644" t="n">
-        <v>9.11176586151123</v>
+        <v>9.11176681518555</v>
       </c>
       <c r="H1644" t="n">
         <v>3440484</v>
@@ -48074,7 +48074,7 @@
         <v>9.73799991607666</v>
       </c>
       <c r="G1645" t="n">
-        <v>9.27947902679443</v>
+        <v>9.27947998046875</v>
       </c>
       <c r="H1645" t="n">
         <v>1277754</v>
@@ -48161,7 +48161,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G1648" t="n">
-        <v>9.07174396514893</v>
+        <v>9.07174301147461</v>
       </c>
       <c r="H1648" t="n">
         <v>2667598</v>
@@ -48219,7 +48219,7 @@
         <v>9.5</v>
       </c>
       <c r="G1650" t="n">
-        <v>9.05268478393555</v>
+        <v>9.05268573760986</v>
       </c>
       <c r="H1650" t="n">
         <v>1967035</v>
@@ -48277,7 +48277,7 @@
         <v>9.74199962615967</v>
       </c>
       <c r="G1652" t="n">
-        <v>9.28329086303711</v>
+        <v>9.28328990936279</v>
       </c>
       <c r="H1652" t="n">
         <v>1508822</v>
@@ -48306,7 +48306,7 @@
         <v>9.67800045013428</v>
       </c>
       <c r="G1653" t="n">
-        <v>9.22230434417725</v>
+        <v>9.22230529785156</v>
       </c>
       <c r="H1653" t="n">
         <v>2245762</v>
@@ -48335,7 +48335,7 @@
         <v>9.86200046539307</v>
       </c>
       <c r="G1654" t="n">
-        <v>9.39764022827148</v>
+        <v>9.39763927459717</v>
       </c>
       <c r="H1654" t="n">
         <v>2959376</v>
@@ -48393,7 +48393,7 @@
         <v>9.06599998474121</v>
       </c>
       <c r="G1656" t="n">
-        <v>8.63912010192871</v>
+        <v>8.63912105560303</v>
       </c>
       <c r="H1656" t="n">
         <v>4434832</v>
@@ -48509,7 +48509,7 @@
         <v>10.0050001144409</v>
       </c>
       <c r="G1660" t="n">
-        <v>9.53390789031982</v>
+        <v>9.53390693664551</v>
       </c>
       <c r="H1660" t="n">
         <v>1922850</v>
@@ -48625,7 +48625,7 @@
         <v>9.88399982452393</v>
       </c>
       <c r="G1664" t="n">
-        <v>9.41860389709473</v>
+        <v>9.41860485076904</v>
       </c>
       <c r="H1664" t="n">
         <v>2339247</v>
@@ -48654,7 +48654,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1665" t="n">
-        <v>9.49102592468262</v>
+        <v>9.49102687835693</v>
       </c>
       <c r="H1665" t="n">
         <v>1548608</v>
@@ -48683,7 +48683,7 @@
         <v>10.3549995422363</v>
       </c>
       <c r="G1666" t="n">
-        <v>9.86742687225342</v>
+        <v>9.86742782592773</v>
       </c>
       <c r="H1666" t="n">
         <v>3533078</v>
@@ -48770,7 +48770,7 @@
         <v>9.80200004577637</v>
       </c>
       <c r="G1669" t="n">
-        <v>9.34046459197998</v>
+        <v>9.3404655456543</v>
       </c>
       <c r="H1669" t="n">
         <v>1796401</v>
@@ -48799,7 +48799,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1670" t="n">
-        <v>9.32903003692627</v>
+        <v>9.32903099060059</v>
       </c>
       <c r="H1670" t="n">
         <v>2378564</v>
@@ -48857,7 +48857,7 @@
         <v>9.81799983978271</v>
       </c>
       <c r="G1672" t="n">
-        <v>9.35571098327637</v>
+        <v>9.35571193695068</v>
       </c>
       <c r="H1672" t="n">
         <v>1822131</v>
@@ -49060,7 +49060,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1679" t="n">
-        <v>8.55716896057129</v>
+        <v>8.55716991424561</v>
       </c>
       <c r="H1679" t="n">
         <v>2842374</v>
@@ -49118,7 +49118,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G1681" t="n">
-        <v>8.60481548309326</v>
+        <v>8.60481643676758</v>
       </c>
       <c r="H1681" t="n">
         <v>1533109</v>
@@ -49147,7 +49147,7 @@
         <v>8.98999977111816</v>
       </c>
       <c r="G1682" t="n">
-        <v>8.56669807434082</v>
+        <v>8.56669902801514</v>
       </c>
       <c r="H1682" t="n">
         <v>1779388</v>
@@ -49263,7 +49263,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G1686" t="n">
-        <v>8.54764080047607</v>
+        <v>8.54764175415039</v>
       </c>
       <c r="H1686" t="n">
         <v>1906654</v>
@@ -49321,7 +49321,7 @@
         <v>8.69400024414062</v>
       </c>
       <c r="G1688" t="n">
-        <v>8.28463554382324</v>
+        <v>8.28463649749756</v>
       </c>
       <c r="H1688" t="n">
         <v>1936248</v>
@@ -49350,7 +49350,7 @@
         <v>8.5959997177124</v>
       </c>
       <c r="G1689" t="n">
-        <v>8.19124984741211</v>
+        <v>8.19125080108643</v>
       </c>
       <c r="H1689" t="n">
         <v>1467340</v>
@@ -49379,7 +49379,7 @@
         <v>8.64799976348877</v>
       </c>
       <c r="G1690" t="n">
-        <v>8.24080181121826</v>
+        <v>8.24080276489258</v>
       </c>
       <c r="H1690" t="n">
         <v>2264551</v>
@@ -49466,7 +49466,7 @@
         <v>8.48600006103516</v>
       </c>
       <c r="G1693" t="n">
-        <v>8.08643054962158</v>
+        <v>8.08642959594727</v>
       </c>
       <c r="H1693" t="n">
         <v>1052736</v>
@@ -49495,7 +49495,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G1694" t="n">
-        <v>7.88060188293457</v>
+        <v>7.88060140609741</v>
       </c>
       <c r="H1694" t="n">
         <v>2123614</v>
@@ -49524,7 +49524,7 @@
         <v>8.26200008392334</v>
       </c>
       <c r="G1695" t="n">
-        <v>7.87297821044922</v>
+        <v>7.87297773361206</v>
       </c>
       <c r="H1695" t="n">
         <v>1930992</v>
@@ -49553,7 +49553,7 @@
         <v>8.16600036621094</v>
       </c>
       <c r="G1696" t="n">
-        <v>7.78149795532227</v>
+        <v>7.78149843215942</v>
       </c>
       <c r="H1696" t="n">
         <v>2539328</v>
@@ -49582,7 +49582,7 @@
         <v>7.89200019836426</v>
       </c>
       <c r="G1697" t="n">
-        <v>7.52039909362793</v>
+        <v>7.52039957046509</v>
       </c>
       <c r="H1697" t="n">
         <v>2787138</v>
@@ -49669,7 +49669,7 @@
         <v>7.80399990081787</v>
       </c>
       <c r="G1700" t="n">
-        <v>7.43654298782349</v>
+        <v>7.43654251098633</v>
       </c>
       <c r="H1700" t="n">
         <v>3195442</v>
@@ -49698,7 +49698,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1701" t="n">
-        <v>7.34506368637085</v>
+        <v>7.34506320953369</v>
       </c>
       <c r="H1701" t="n">
         <v>1207494</v>
@@ -49785,7 +49785,7 @@
         <v>7.85599994659424</v>
       </c>
       <c r="G1704" t="n">
-        <v>7.48609399795532</v>
+        <v>7.48609447479248</v>
       </c>
       <c r="H1704" t="n">
         <v>2183556</v>
@@ -49814,7 +49814,7 @@
         <v>7.75799989700317</v>
       </c>
       <c r="G1705" t="n">
-        <v>7.39270877838135</v>
+        <v>7.39270830154419</v>
       </c>
       <c r="H1705" t="n">
         <v>1663394</v>
@@ -49843,7 +49843,7 @@
         <v>7.7020001411438</v>
       </c>
       <c r="G1706" t="n">
-        <v>7.33934640884399</v>
+        <v>7.33934593200684</v>
       </c>
       <c r="H1706" t="n">
         <v>2266817</v>
@@ -49872,7 +49872,7 @@
         <v>7.7039999961853</v>
       </c>
       <c r="G1707" t="n">
-        <v>7.34125089645386</v>
+        <v>7.34125137329102</v>
       </c>
       <c r="H1707" t="n">
         <v>1444942</v>
@@ -49930,7 +49930,7 @@
         <v>7.73799991607666</v>
       </c>
       <c r="G1709" t="n">
-        <v>7.37365102767944</v>
+        <v>7.37365055084229</v>
       </c>
       <c r="H1709" t="n">
         <v>1447073</v>
@@ -50104,7 +50104,7 @@
         <v>7.7480001449585</v>
       </c>
       <c r="G1715" t="n">
-        <v>7.38318014144897</v>
+        <v>7.38317966461182</v>
       </c>
       <c r="H1715" t="n">
         <v>1866946</v>
@@ -50162,7 +50162,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1717" t="n">
-        <v>7.05156517028809</v>
+        <v>7.05156564712524</v>
       </c>
       <c r="H1717" t="n">
         <v>3126658</v>
@@ -50365,7 +50365,7 @@
         <v>7.5</v>
       </c>
       <c r="G1724" t="n">
-        <v>7.14685726165771</v>
+        <v>7.14685678482056</v>
       </c>
       <c r="H1724" t="n">
         <v>1775020</v>
@@ -50452,7 +50452,7 @@
         <v>7.18200016021729</v>
       </c>
       <c r="G1727" t="n">
-        <v>6.84383010864258</v>
+        <v>6.84383058547974</v>
       </c>
       <c r="H1727" t="n">
         <v>3333707</v>
@@ -50510,7 +50510,7 @@
         <v>7.36399984359741</v>
       </c>
       <c r="G1729" t="n">
-        <v>7.01726007461548</v>
+        <v>7.01726055145264</v>
       </c>
       <c r="H1729" t="n">
         <v>1737475</v>
@@ -50655,7 +50655,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G1734" t="n">
-        <v>7.40414381027222</v>
+        <v>7.40414428710938</v>
       </c>
       <c r="H1734" t="n">
         <v>2178484</v>
@@ -50684,7 +50684,7 @@
         <v>7.74200010299683</v>
       </c>
       <c r="G1735" t="n">
-        <v>7.3774619102478</v>
+        <v>7.37746238708496</v>
       </c>
       <c r="H1735" t="n">
         <v>1545986</v>
@@ -50742,7 +50742,7 @@
         <v>7.9520001411438</v>
       </c>
       <c r="G1737" t="n">
-        <v>7.57757425308228</v>
+        <v>7.57757377624512</v>
       </c>
       <c r="H1737" t="n">
         <v>2019070</v>
@@ -50800,7 +50800,7 @@
         <v>8.13199996948242</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.749098777771</v>
+        <v>7.74909830093384</v>
       </c>
       <c r="H1739" t="n">
         <v>2131422</v>
@@ -50829,7 +50829,7 @@
         <v>8.16600036621094</v>
       </c>
       <c r="G1740" t="n">
-        <v>7.78149795532227</v>
+        <v>7.78149843215942</v>
       </c>
       <c r="H1740" t="n">
         <v>2531223</v>
@@ -50858,7 +50858,7 @@
         <v>8.26399993896484</v>
       </c>
       <c r="G1741" t="n">
-        <v>7.87488317489624</v>
+        <v>7.8748836517334</v>
       </c>
       <c r="H1741" t="n">
         <v>2627833</v>
@@ -50974,7 +50974,7 @@
         <v>7.23600006103516</v>
       </c>
       <c r="G1745" t="n">
-        <v>6.89528751373291</v>
+        <v>6.89528703689575</v>
       </c>
       <c r="H1745" t="n">
         <v>6899756</v>
@@ -51148,7 +51148,7 @@
         <v>7.63399982452393</v>
       </c>
       <c r="G1751" t="n">
-        <v>7.2745475769043</v>
+        <v>7.27454710006714</v>
       </c>
       <c r="H1751" t="n">
         <v>6229362</v>
@@ -51177,7 +51177,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1752" t="n">
-        <v>7.05156517028809</v>
+        <v>7.05156564712524</v>
       </c>
       <c r="H1752" t="n">
         <v>4976142</v>
@@ -51293,7 +51293,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1756" t="n">
-        <v>7.17544412612915</v>
+        <v>7.17544460296631</v>
       </c>
       <c r="H1756" t="n">
         <v>1990722</v>
@@ -51322,7 +51322,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G1757" t="n">
-        <v>7.23071336746216</v>
+        <v>7.230712890625</v>
       </c>
       <c r="H1757" t="n">
         <v>1431015</v>
@@ -51351,7 +51351,7 @@
         <v>7.65799999237061</v>
       </c>
       <c r="G1758" t="n">
-        <v>7.29741668701172</v>
+        <v>7.29741716384888</v>
       </c>
       <c r="H1758" t="n">
         <v>1955240</v>
@@ -51496,7 +51496,7 @@
         <v>7.7480001449585</v>
       </c>
       <c r="G1763" t="n">
-        <v>7.38318014144897</v>
+        <v>7.38317966461182</v>
       </c>
       <c r="H1763" t="n">
         <v>2204600</v>
@@ -51525,7 +51525,7 @@
         <v>7.68200016021729</v>
       </c>
       <c r="G1764" t="n">
-        <v>7.32028770446777</v>
+        <v>7.32028722763062</v>
       </c>
       <c r="H1764" t="n">
         <v>1383388</v>
@@ -51554,7 +51554,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1765" t="n">
-        <v>7.37555646896362</v>
+        <v>7.37555599212646</v>
       </c>
       <c r="H1765" t="n">
         <v>3410353</v>
@@ -51583,7 +51583,7 @@
         <v>7.72800016403198</v>
       </c>
       <c r="G1766" t="n">
-        <v>7.36412191390991</v>
+        <v>7.36412143707275</v>
       </c>
       <c r="H1766" t="n">
         <v>2007019</v>
@@ -51641,7 +51641,7 @@
         <v>7.62599992752075</v>
       </c>
       <c r="G1768" t="n">
-        <v>7.2669243812561</v>
+        <v>7.26692390441895</v>
       </c>
       <c r="H1768" t="n">
         <v>3213669</v>
@@ -51670,7 +51670,7 @@
         <v>7.66599988937378</v>
       </c>
       <c r="G1769" t="n">
-        <v>7.30504083633423</v>
+        <v>7.30504035949707</v>
       </c>
       <c r="H1769" t="n">
         <v>2025242</v>
@@ -51699,7 +51699,7 @@
         <v>7.70800018310547</v>
       </c>
       <c r="G1770" t="n">
-        <v>7.34506368637085</v>
+        <v>7.34506320953369</v>
       </c>
       <c r="H1770" t="n">
         <v>4625273</v>
@@ -51728,7 +51728,7 @@
         <v>7.73799991607666</v>
       </c>
       <c r="G1771" t="n">
-        <v>7.37365102767944</v>
+        <v>7.37365055084229</v>
       </c>
       <c r="H1771" t="n">
         <v>2396558</v>
@@ -51757,7 +51757,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1772" t="n">
-        <v>7.37555646896362</v>
+        <v>7.37555599212646</v>
       </c>
       <c r="H1772" t="n">
         <v>3138300</v>
@@ -51786,7 +51786,7 @@
         <v>7.76800012588501</v>
       </c>
       <c r="G1773" t="n">
-        <v>7.40223836898804</v>
+        <v>7.40223789215088</v>
       </c>
       <c r="H1773" t="n">
         <v>2875676</v>
@@ -52047,7 +52047,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1782" t="n">
-        <v>7.6804895401001</v>
+        <v>7.68048906326294</v>
       </c>
       <c r="H1782" t="n">
         <v>1109178</v>
@@ -52134,7 +52134,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>7.70907640457153</v>
+        <v>7.70907688140869</v>
       </c>
       <c r="H1785" t="n">
         <v>5937596</v>
@@ -52192,7 +52192,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1787" t="n">
-        <v>7.76625061035156</v>
+        <v>7.76625108718872</v>
       </c>
       <c r="H1787" t="n">
         <v>2322194</v>
@@ -52250,7 +52250,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G1789" t="n">
-        <v>7.6804895401001</v>
+        <v>7.68048906326294</v>
       </c>
       <c r="H1789" t="n">
         <v>2551242</v>
@@ -52279,7 +52279,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1790" t="n">
-        <v>7.67095994949341</v>
+        <v>7.67095947265625</v>
       </c>
       <c r="H1790" t="n">
         <v>2386356</v>
@@ -52308,7 +52308,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1791" t="n">
-        <v>7.82342624664307</v>
+        <v>7.82342672348022</v>
       </c>
       <c r="H1791" t="n">
         <v>3452084</v>
@@ -52337,7 +52337,7 @@
         <v>8.22599983215332</v>
       </c>
       <c r="G1792" t="n">
-        <v>7.83867216110229</v>
+        <v>7.83867311477661</v>
       </c>
       <c r="H1792" t="n">
         <v>2589739</v>
@@ -52482,7 +52482,7 @@
         <v>8.90999984741211</v>
       </c>
       <c r="G1797" t="n">
-        <v>8.49046611785889</v>
+        <v>8.4904670715332</v>
       </c>
       <c r="H1797" t="n">
         <v>2865831</v>
@@ -52511,7 +52511,7 @@
         <v>9.2180004119873</v>
       </c>
       <c r="G1798" t="n">
-        <v>8.78396415710449</v>
+        <v>8.78396320343018</v>
       </c>
       <c r="H1798" t="n">
         <v>4627920</v>
@@ -52540,7 +52540,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G1799" t="n">
-        <v>8.77633953094482</v>
+        <v>8.77634048461914</v>
       </c>
       <c r="H1799" t="n">
         <v>4822410</v>
@@ -52569,7 +52569,7 @@
         <v>9.44600009918213</v>
       </c>
       <c r="G1800" t="n">
-        <v>9.00122833251953</v>
+        <v>9.00122737884521</v>
       </c>
       <c r="H1800" t="n">
         <v>6866025</v>
@@ -52598,7 +52598,7 @@
         <v>9.56799983978271</v>
       </c>
       <c r="G1801" t="n">
-        <v>9.1174840927124</v>
+        <v>9.11748313903809</v>
       </c>
       <c r="H1801" t="n">
         <v>4803634</v>
@@ -52627,7 +52627,7 @@
         <v>9.54800033569336</v>
       </c>
       <c r="G1802" t="n">
-        <v>9.09842586517334</v>
+        <v>9.09842491149902</v>
       </c>
       <c r="H1802" t="n">
         <v>3172185</v>
@@ -52685,7 +52685,7 @@
         <v>9.45400047302246</v>
       </c>
       <c r="G1804" t="n">
-        <v>9.00885105133057</v>
+        <v>9.00885200500488</v>
       </c>
       <c r="H1804" t="n">
         <v>4619032</v>
@@ -52714,7 +52714,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1805" t="n">
-        <v>9.14797782897949</v>
+        <v>9.14797687530518</v>
       </c>
       <c r="H1805" t="n">
         <v>3428166</v>
@@ -52888,7 +52888,7 @@
         <v>9.76399993896484</v>
       </c>
       <c r="G1811" t="n">
-        <v>9.30425548553467</v>
+        <v>9.30425453186035</v>
       </c>
       <c r="H1811" t="n">
         <v>3784281</v>
@@ -53004,7 +53004,7 @@
         <v>10.2150001525879</v>
       </c>
       <c r="G1815" t="n">
-        <v>9.73401927947998</v>
+        <v>9.7340202331543</v>
       </c>
       <c r="H1815" t="n">
         <v>3585936</v>
@@ -53033,7 +53033,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G1816" t="n">
-        <v>9.9531888961792</v>
+        <v>9.95318984985352</v>
       </c>
       <c r="H1816" t="n">
         <v>4532829</v>
@@ -53062,7 +53062,7 @@
         <v>10.4549999237061</v>
       </c>
       <c r="G1817" t="n">
-        <v>9.96271896362305</v>
+        <v>9.96271800994873</v>
       </c>
       <c r="H1817" t="n">
         <v>3114180</v>
@@ -53178,7 +53178,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G1821" t="n">
-        <v>9.9531888961792</v>
+        <v>9.95318984985352</v>
       </c>
       <c r="H1821" t="n">
         <v>3919897</v>
@@ -53207,7 +53207,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G1822" t="n">
-        <v>9.97701263427734</v>
+        <v>9.97701358795166</v>
       </c>
       <c r="H1822" t="n">
         <v>2855398</v>
@@ -53236,7 +53236,7 @@
         <v>10.625</v>
       </c>
       <c r="G1823" t="n">
-        <v>10.1247148513794</v>
+        <v>10.1247138977051</v>
       </c>
       <c r="H1823" t="n">
         <v>3028552</v>
@@ -53265,7 +53265,7 @@
         <v>10.6149997711182</v>
       </c>
       <c r="G1824" t="n">
-        <v>10.1151847839355</v>
+        <v>10.1151838302612</v>
       </c>
       <c r="H1824" t="n">
         <v>2618641</v>
@@ -53294,7 +53294,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1825" t="n">
-        <v>10.119948387146</v>
+        <v>10.1199493408203</v>
       </c>
       <c r="H1825" t="n">
         <v>2550426</v>
@@ -53323,7 +53323,7 @@
         <v>10.7049999237061</v>
       </c>
       <c r="G1826" t="n">
-        <v>10.2009468078613</v>
+        <v>10.2009477615356</v>
       </c>
       <c r="H1826" t="n">
         <v>3994621</v>
@@ -53381,7 +53381,7 @@
         <v>10.9049997329712</v>
       </c>
       <c r="G1828" t="n">
-        <v>10.3915300369263</v>
+        <v>10.391529083252</v>
       </c>
       <c r="H1828" t="n">
         <v>3065932</v>
@@ -53410,7 +53410,7 @@
         <v>10.8850002288818</v>
       </c>
       <c r="G1829" t="n">
-        <v>10.3724727630615</v>
+        <v>10.3724718093872</v>
       </c>
       <c r="H1829" t="n">
         <v>2551710</v>
@@ -53468,7 +53468,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G1831" t="n">
-        <v>10.2152404785156</v>
+        <v>10.2152414321899</v>
       </c>
       <c r="H1831" t="n">
         <v>2559279</v>
@@ -53497,7 +53497,7 @@
         <v>11.0249996185303</v>
       </c>
       <c r="G1832" t="n">
-        <v>10.5058784484863</v>
+        <v>10.5058794021606</v>
       </c>
       <c r="H1832" t="n">
         <v>8811905</v>
@@ -53526,7 +53526,7 @@
         <v>11.0349998474121</v>
       </c>
       <c r="G1833" t="n">
-        <v>10.5154085159302</v>
+        <v>10.5154094696045</v>
       </c>
       <c r="H1833" t="n">
         <v>6225654</v>
@@ -53613,7 +53613,7 @@
         <v>10.75</v>
       </c>
       <c r="G1836" t="n">
-        <v>10.2438278198242</v>
+        <v>10.2438268661499</v>
       </c>
       <c r="H1836" t="n">
         <v>3460915</v>
@@ -53729,7 +53729,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1840" t="n">
-        <v>10.5106449127197</v>
+        <v>10.5106439590454</v>
       </c>
       <c r="H1840" t="n">
         <v>2177542</v>
@@ -53758,7 +53758,7 @@
         <v>11.0550003051758</v>
       </c>
       <c r="G1841" t="n">
-        <v>10.5344667434692</v>
+        <v>10.5344676971436</v>
       </c>
       <c r="H1841" t="n">
         <v>2333996</v>
@@ -53816,7 +53816,7 @@
         <v>10.9750003814697</v>
       </c>
       <c r="G1843" t="n">
-        <v>10.458233833313</v>
+        <v>10.4582347869873</v>
       </c>
       <c r="H1843" t="n">
         <v>1586398</v>
@@ -53874,7 +53874,7 @@
         <v>10.9250001907349</v>
       </c>
       <c r="G1845" t="n">
-        <v>10.4105892181396</v>
+        <v>10.4105882644653</v>
       </c>
       <c r="H1845" t="n">
         <v>2174469</v>
@@ -53961,7 +53961,7 @@
         <v>10.9549999237061</v>
       </c>
       <c r="G1848" t="n">
-        <v>10.4391756057739</v>
+        <v>10.4391765594482</v>
       </c>
       <c r="H1848" t="n">
         <v>2261122</v>
@@ -53990,7 +53990,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G1849" t="n">
-        <v>10.5297040939331</v>
+        <v>10.5297031402588</v>
       </c>
       <c r="H1849" t="n">
         <v>2401173</v>
@@ -54019,7 +54019,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G1850" t="n">
-        <v>10.4725284576416</v>
+        <v>10.4725275039673</v>
       </c>
       <c r="H1850" t="n">
         <v>2827270</v>
@@ -54048,7 +54048,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1851" t="n">
-        <v>10.7584028244019</v>
+        <v>10.7584018707275</v>
       </c>
       <c r="H1851" t="n">
         <v>3120216</v>
@@ -54106,7 +54106,7 @@
         <v>11.3549995422363</v>
       </c>
       <c r="G1853" t="n">
-        <v>10.8203411102295</v>
+        <v>10.8203401565552</v>
       </c>
       <c r="H1853" t="n">
         <v>4537351</v>
@@ -54135,7 +54135,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1854" t="n">
-        <v>11.168155670166</v>
+        <v>11.1681547164917</v>
       </c>
       <c r="H1854" t="n">
         <v>5784623</v>
@@ -54251,7 +54251,7 @@
         <v>11.4250001907349</v>
       </c>
       <c r="G1858" t="n">
-        <v>10.8870458602905</v>
+        <v>10.8870468139648</v>
       </c>
       <c r="H1858" t="n">
         <v>1999396</v>
@@ -54338,7 +54338,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G1861" t="n">
-        <v>10.5725841522217</v>
+        <v>10.5725831985474</v>
       </c>
       <c r="H1861" t="n">
         <v>2623173</v>
@@ -54483,7 +54483,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1866" t="n">
-        <v>10.1580648422241</v>
+        <v>10.1580657958984</v>
       </c>
       <c r="H1866" t="n">
         <v>1910841</v>
@@ -54541,7 +54541,7 @@
         <v>10.3149995803833</v>
       </c>
       <c r="G1868" t="n">
-        <v>9.82930946350098</v>
+        <v>9.82931041717529</v>
       </c>
       <c r="H1868" t="n">
         <v>8730227</v>
@@ -54570,7 +54570,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G1869" t="n">
-        <v>9.9531888961792</v>
+        <v>9.95318984985352</v>
       </c>
       <c r="H1869" t="n">
         <v>3105562</v>
@@ -54599,7 +54599,7 @@
         <v>10.4449996948242</v>
       </c>
       <c r="G1870" t="n">
-        <v>9.9531888961792</v>
+        <v>9.95318984985352</v>
       </c>
       <c r="H1870" t="n">
         <v>1793865</v>
@@ -54686,7 +54686,7 @@
         <v>10.6350002288818</v>
       </c>
       <c r="G1873" t="n">
-        <v>10.1342439651489</v>
+        <v>10.1342430114746</v>
       </c>
       <c r="H1873" t="n">
         <v>1759274</v>
@@ -54715,7 +54715,7 @@
         <v>11.0649995803833</v>
       </c>
       <c r="G1874" t="n">
-        <v>10.5439958572388</v>
+        <v>10.5439968109131</v>
       </c>
       <c r="H1874" t="n">
         <v>3625374</v>
@@ -54744,7 +54744,7 @@
         <v>11.0550003051758</v>
       </c>
       <c r="G1875" t="n">
-        <v>10.5344667434692</v>
+        <v>10.5344676971436</v>
       </c>
       <c r="H1875" t="n">
         <v>1813297</v>
@@ -54802,7 +54802,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1877" t="n">
-        <v>10.7679309844971</v>
+        <v>10.7679319381714</v>
       </c>
       <c r="H1877" t="n">
         <v>2161220</v>
@@ -54831,7 +54831,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G1878" t="n">
-        <v>10.7869892120361</v>
+        <v>10.7869901657104</v>
       </c>
       <c r="H1878" t="n">
         <v>2201059</v>
@@ -80209,9 +80209,38 @@
         <v>51.810001373291</v>
       </c>
       <c r="H2753" t="n">
-        <v>2527459</v>
+        <v>2528639</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>51.8400001525879</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>51.8400001525879</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>50.8899993896484</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>51.7599983215332</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>51.7599983215332</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>1780668</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
